--- a/languages/ko/output/import/韩语TOPIK1.xlsx
+++ b/languages/ko/output/import/韩语TOPIK1.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠d͡ʑo̞k̚]] 科 (关系)</t>
+          <t>[[ka̠d͡ʑo̞k̚]] 家庭 (关系)</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>科 (关系)</t>
+          <t>家庭 (关系)</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰinna̠da̠]] 期待 期待 (情感)</t>
+          <t>[[ɕʰinna̠da̠]] 兴奋；开心 (形容词)</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>期待 期待 (情感)</t>
+          <t>兴奋；开心 (形容词)</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK1.xlsx
+++ b/languages/ko/output/import/韩语TOPIK1.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯɭpʰɯda̠]] 哀: (情感)</t>
+          <t>[[sʰɯɭpʰɯda̠]] 悲伤；悲哀；难过 (형용사)</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>哀: (情感)</t>
+          <t>悲伤；悲哀；难过 (형용사)</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɦa̠ŋ]] 【2】银行 (旅行)</t>
+          <t>[[ko̞ŋɦa̠ŋ]] 机场 (명사)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>【2】银行 (旅行)</t>
+          <t>机场 (명사)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>[[s͈e̞iɭ]] Sale (购物)</t>
+          <t>[[s͈e̞iɭ]] 打折；降价促销 (명사)</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>Sale (购物)</t>
+          <t>打折；降价促销 (명사)</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ɾɰiɕʰiɭ]] 试衣间 ? (购物)</t>
+          <t>[[tʰa̠ɾɰiɕʰiɭ]] 试衣间；更衣室 (명사)</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>试衣间 ? (购物)</t>
+          <t>试衣间；更衣室 (명사)</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰid͡ʑa̠ŋ]] 传统市场(Traditional Market) (购物)</t>
+          <t>[[ɕʰid͡ʑa̠ŋ]] 传统市场；集市 (명사)</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>传统市场(Traditional Market) (购物)</t>
+          <t>传统市场；集市 (명사)</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>[konutngikat] 传统市场(Traditional Market) (旅游)</t>
+          <t>[konutngikat] 传统市场 (명사)</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t>传统市场(Traditional Market) (旅游)</t>
+          <t>传统市场 (명사)</t>
         </is>
       </c>
       <c r="E300" s="1" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>[[wa̠ipʰa̠i]] WiFi (旅游)</t>
+          <t>[[wa̠ipʰa̠i]] 无线网络；Wi-Fi (명사)</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t>WiFi (旅游)</t>
+          <t>无线网络；Wi-Fi (명사)</t>
         </is>
       </c>
       <c r="E309" s="1" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[momchochy] “远吗？” (旅游)</t>
+          <t>[momchochy] 远吗？；路途远吗？ (구)</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t>“远吗？” (旅游)</t>
+          <t>远吗？；路途远吗？ (구)</t>
         </is>
       </c>
       <c r="E313" s="1" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɛ(ː)ɡjo]] Aegyo (文化)</t>
+          <t>[[ˈɛ(ː)ɡjo]] 撒娇；娇憨 (명사)</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t>Aegyo (文化)</t>
+          <t>撒娇；娇憨 (명사)</t>
         </is>
       </c>
       <c r="E320" s="1" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtɛ(ː)ba̠k̚]] Daebak (文化)</t>
+          <t>[[ˈtɛ(ː)ba̠k̚]] 大发；大赚；太棒了 (명사/감탄사)</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>Daebak (文化)</t>
+          <t>大发；大赚；太棒了 (명사/감탄사)</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹ɭ]] Heol (文化)</t>
+          <t>[[hʌ̹ɭ]] 晕；天哪；天啊 (감탄사)</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>Heol (文化)</t>
+          <t>晕；天哪；天啊 (감탄사)</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɯ(ː)ŋwʌ̹nbo̞ŋ]] Lightstick (文化)</t>
+          <t>[[ˈɯ(ː)ŋwʌ̹nbo̞ŋ]] 应援棒；荧光棒 (명사)</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t>Lightstick (文化)</t>
+          <t>应援棒；荧光棒 (명사)</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)mjʌ̹ndɛ]] Sink (日常生活)</t>
+          <t>[[ˈsʰe̞(ː)mjʌ̹ndɛ]] 洗手台；洗脸池 (명사)</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t>Sink (日常生活)</t>
+          <t>洗手台；洗脸池 (명사)</t>
         </is>
       </c>
       <c r="E344" s="1" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰu(ː)ɡʌ̹n]] Towel (日常生活)</t>
+          <t>[[ˈsʰu(ː)ɡʌ̹n]] 毛巾 (명사)</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t>Towel (日常生活)</t>
+          <t>毛巾 (명사)</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>[[ˈno̞(ː)ŋda̠m]] Joke (人际关系)</t>
+          <t>[[ˈno̞(ː)ŋda̠m]] 玩笑；幽默 (명사)</t>
         </is>
       </c>
       <c r="C470" s="1" t="inlineStr">
@@ -15453,7 +15453,7 @@
       </c>
       <c r="D470" s="1" t="inlineStr">
         <is>
-          <t>Joke (人际关系)</t>
+          <t>玩笑；幽默 (명사)</t>
         </is>
       </c>
       <c r="E470" s="1" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>[chechopichenpi] Airbnb (旅游)</t>
+          <t>[chechopichenpi] 爱彼迎；Airbnb民宿 (명사)</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="D511" s="1" t="inlineStr">
         <is>
-          <t>Airbnb (旅游)</t>
+          <t>爱彼迎；Airbnb民宿 (명사)</t>
         </is>
       </c>
       <c r="E511" s="1" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>[erin] Cloudy (天气)</t>
+          <t>[erin] 阴的；阴沉的；模糊的 (형용사)</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="D744" s="1" t="inlineStr">
         <is>
-          <t>Cloudy (天气)</t>
+          <t>阴的；阴沉的；模糊的 (형용사)</t>
         </is>
       </c>
       <c r="E744" s="1" t="inlineStr">
@@ -30035,7 +30035,7 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>[pangakan] 豆dhal (烹饪)</t>
+          <t>[pangakan] 酥脆的；松脆的 (형용사)</t>
         </is>
       </c>
       <c r="C926" s="1" t="inlineStr">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="D926" s="1" t="inlineStr">
         <is>
-          <t>豆dhal (烹饪)</t>
+          <t>酥脆的；松脆的 (형용사)</t>
         </is>
       </c>
       <c r="E926" s="1" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>[[no̞ɾɛ]] Song (音乐)</t>
+          <t>[[no̞ɾɛ]] 歌曲；歌唱 (명사)</t>
         </is>
       </c>
       <c r="C928" s="1" t="inlineStr">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="D928" s="1" t="inlineStr">
         <is>
-          <t>Song (音乐)</t>
+          <t>歌曲；歌唱 (명사)</t>
         </is>
       </c>
       <c r="E928" s="1" t="inlineStr">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="B935" s="1" t="inlineStr">
         <is>
-          <t>[chachitru] Outro (音乐)</t>
+          <t>[chachitru] 尾奏；结尾乐段 (명사)</t>
         </is>
       </c>
       <c r="C935" s="1" t="inlineStr">
@@ -30333,7 +30333,7 @@
       </c>
       <c r="D935" s="1" t="inlineStr">
         <is>
-          <t>Outro (音乐)</t>
+          <t>尾奏；结尾乐段 (명사)</t>
         </is>
       </c>
       <c r="E935" s="1" t="inlineStr">
@@ -30355,7 +30355,7 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>[minichempong] EP (音乐)</t>
+          <t>[minichempong] 迷你专辑；EP (명사)</t>
         </is>
       </c>
       <c r="C936" s="1" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="D936" s="1" t="inlineStr">
         <is>
-          <t>EP (音乐)</t>
+          <t>迷你专辑；EP (명사)</t>
         </is>
       </c>
       <c r="E936" s="1" t="inlineStr">
@@ -30579,7 +30579,7 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>[[tid͡ʑe̞i]] DJ (音乐)</t>
+          <t>[[tid͡ʑe̞i]] DJ；唱片骑师 (명사)</t>
         </is>
       </c>
       <c r="C943" s="1" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="D943" s="1" t="inlineStr">
         <is>
-          <t>DJ (音乐)</t>
+          <t>DJ；唱片骑师 (명사)</t>
         </is>
       </c>
       <c r="E943" s="1" t="inlineStr">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="B967" s="1" t="inlineStr">
         <is>
-          <t>[[pibida̠]] Bibim Mixing (烹饪)</t>
+          <t>[[pibida̠]] 拌；揉搓；摩擦 (동사)</t>
         </is>
       </c>
       <c r="C967" s="1" t="inlineStr">
@@ -31357,7 +31357,7 @@
       </c>
       <c r="D967" s="1" t="inlineStr">
         <is>
-          <t>Bibim Mixing (烹饪)</t>
+          <t>拌；揉搓；摩擦 (동사)</t>
         </is>
       </c>
       <c r="E967" s="1" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="B968" s="1" t="inlineStr">
         <is>
-          <t>[[ɸʷo̞nba̠p̚]] Honbap (俚语)</t>
+          <t>[[ɸʷo̞nba̠p̚]] 独食；一个人吃饭 (명사)</t>
         </is>
       </c>
       <c r="C968" s="1" t="inlineStr">
@@ -31389,7 +31389,7 @@
       </c>
       <c r="D968" s="1" t="inlineStr">
         <is>
-          <t>Honbap (俚语)</t>
+          <t>独食；一个人吃饭 (명사)</t>
         </is>
       </c>
       <c r="E968" s="1" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɛ(ː)in]] Gaesaeng (俚语)</t>
+          <t>[[ˈkɛ(ː)in]] 个人；私人 (명사)</t>
         </is>
       </c>
       <c r="C969" s="1" t="inlineStr">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="D969" s="1" t="inlineStr">
         <is>
-          <t>Gaesaeng (俚语)</t>
+          <t>个人；私人 (명사)</t>
         </is>
       </c>
       <c r="E969" s="1" t="inlineStr">
@@ -34355,7 +34355,7 @@
       </c>
       <c r="B1061" s="1" t="inlineStr">
         <is>
-          <t>[[jutʰjubɯ]] YouTube (科技)</t>
+          <t>[[jutʰjubɯ]] YouTube；油管 (명사)</t>
         </is>
       </c>
       <c r="C1061" s="1" t="inlineStr">
@@ -34365,7 +34365,7 @@
       </c>
       <c r="D1061" s="1" t="inlineStr">
         <is>
-          <t>YouTube (科技)</t>
+          <t>YouTube；油管 (명사)</t>
         </is>
       </c>
       <c r="E1061" s="1" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>[[insʰɯtʰa̠ɡɯɾɛm]] Instagram (科技)</t>
+          <t>[[insʰɯtʰa̠ɡɯɾɛm]] Instagram；照片墙 (명사)</t>
         </is>
       </c>
       <c r="C1062" s="1" t="inlineStr">
@@ -34397,7 +34397,7 @@
       </c>
       <c r="D1062" s="1" t="inlineStr">
         <is>
-          <t>Instagram (科技)</t>
+          <t>Instagram；照片墙 (명사)</t>
         </is>
       </c>
       <c r="E1062" s="1" t="inlineStr">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>[[kʰa̠kʰa̠o̞tʰo̞k̚]] KakaoTalk (科技)</t>
+          <t>[[kʰa̠kʰa̠o̞tʰo̞k̚]] KakaoTalk (韩国即时通讯软件) (명사)</t>
         </is>
       </c>
       <c r="C1063" s="1" t="inlineStr">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="D1063" s="1" t="inlineStr">
         <is>
-          <t>KakaoTalk (科技)</t>
+          <t>KakaoTalk (韩国即时通讯软件) (명사)</t>
         </is>
       </c>
       <c r="E1063" s="1" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="B1064" s="1" t="inlineStr">
         <is>
-          <t>[nechipo] Naver (科技)</t>
+          <t>[nechipo] Naver；韩国搜索引擎 (명사)</t>
         </is>
       </c>
       <c r="C1064" s="1" t="inlineStr">
@@ -34461,7 +34461,7 @@
       </c>
       <c r="D1064" s="1" t="inlineStr">
         <is>
-          <t>Naver (科技)</t>
+          <t>Naver；韩国搜索引擎 (명사)</t>
         </is>
       </c>
       <c r="E1064" s="1" t="inlineStr">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="B1162" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠sʰɯkʰa̠ɾa̠]] Mascara (美容与护肤)</t>
+          <t>[[ma̠sʰɯkʰa̠ɾa̠]] 睫毛膏 (명사)</t>
         </is>
       </c>
       <c r="C1162" s="1" t="inlineStr">
@@ -37597,7 +37597,7 @@
       </c>
       <c r="D1162" s="1" t="inlineStr">
         <is>
-          <t>Mascara (美容与护肤)</t>
+          <t>睫毛膏 (명사)</t>
         </is>
       </c>
       <c r="E1162" s="1" t="inlineStr">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="B1303" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɘ(ː)nɕʰi]] Exhibition (艺术与设计)</t>
+          <t>[[ˈt͡ɕɘ(ː)nɕʰi]] 展览；展出 (명사)</t>
         </is>
       </c>
       <c r="C1303" s="1" t="inlineStr">
@@ -42109,7 +42109,7 @@
       </c>
       <c r="D1303" s="1" t="inlineStr">
         <is>
-          <t>Exhibition (艺术与设计)</t>
+          <t>展览；展出 (명사)</t>
         </is>
       </c>
       <c r="E1303" s="1" t="inlineStr">
@@ -43475,7 +43475,7 @@
       </c>
       <c r="B1346" s="1" t="inlineStr">
         <is>
-          <t>[mungot] 母亲的身份 (eomeoni-ui sinbun) (育儿与家庭生活)</t>
+          <t>[mungot] 母性；母亲的身份 (명사)</t>
         </is>
       </c>
       <c r="C1346" s="1" t="inlineStr">
@@ -43485,7 +43485,7 @@
       </c>
       <c r="D1346" s="1" t="inlineStr">
         <is>
-          <t>母亲的身份 (eomeoni-ui sinbun) (育儿与家庭生活)</t>
+          <t>母性；母亲的身份 (명사)</t>
         </is>
       </c>
       <c r="E1346" s="1" t="inlineStr">
@@ -43507,7 +43507,7 @@
       </c>
       <c r="B1347" s="1" t="inlineStr">
         <is>
-          <t>[pingot] 父亲的身份 (abeoji-ui sinbun) (育儿与家庭生活)</t>
+          <t>[pingot] 父性；父亲的身份 (명사)</t>
         </is>
       </c>
       <c r="C1347" s="1" t="inlineStr">
@@ -43517,7 +43517,7 @@
       </c>
       <c r="D1347" s="1" t="inlineStr">
         <is>
-          <t>父亲的身份 (abeoji-ui sinbun) (育儿与家庭生活)</t>
+          <t>父性；父亲的身份 (명사)</t>
         </is>
       </c>
       <c r="E1347" s="1" t="inlineStr">
@@ -43539,7 +43539,7 @@
       </c>
       <c r="B1348" s="1" t="inlineStr">
         <is>
-          <t>[[puɲu]] 配方奶粉 (pyeong-ga naepul) (育儿与家庭生活)</t>
+          <t>[[puɲu]] 配方奶粉 (명사)</t>
         </is>
       </c>
       <c r="C1348" s="1" t="inlineStr">
@@ -43549,7 +43549,7 @@
       </c>
       <c r="D1348" s="1" t="inlineStr">
         <is>
-          <t>配方奶粉 (pyeong-ga naepul) (育儿与家庭生活)</t>
+          <t>配方奶粉 (명사)</t>
         </is>
       </c>
       <c r="E1348" s="1" t="inlineStr">
@@ -43571,7 +43571,7 @@
       </c>
       <c r="B1349" s="1" t="inlineStr">
         <is>
-          <t>[[kid͡ʑʌ̹ɡɥi]] 尿布 (naebuk) (育儿与家庭生活)</t>
+          <t>[[kid͡ʑʌ̹ɡɥi]] 尿布；纸尿裤 (명사)</t>
         </is>
       </c>
       <c r="C1349" s="1" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="D1349" s="1" t="inlineStr">
         <is>
-          <t>尿布 (naebuk) (育儿与家庭生活)</t>
+          <t>尿布；纸尿裤 (명사)</t>
         </is>
       </c>
       <c r="E1349" s="1" t="inlineStr">
@@ -45139,7 +45139,7 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>[riechet] Retweet (媒体与新闻学)</t>
+          <t>[riechet] 转推；转发 (명사)</t>
         </is>
       </c>
       <c r="C1398" s="1" t="inlineStr">
@@ -45149,7 +45149,7 @@
       </c>
       <c r="D1398" s="1" t="inlineStr">
         <is>
-          <t>Retweet (媒体与新闻学)</t>
+          <t>转推；转发 (명사)</t>
         </is>
       </c>
       <c r="E1398" s="1" t="inlineStr">
@@ -45171,7 +45171,7 @@
       </c>
       <c r="B1399" s="1" t="inlineStr">
         <is>
-          <t>[[hɛɕʰitʰɛɡɯ]] Hashtag (媒体与新闻学)</t>
+          <t>[[hɛɕʰitʰɛɡɯ]] 话题标签；标签 (명사)</t>
         </is>
       </c>
       <c r="C1399" s="1" t="inlineStr">
@@ -45181,7 +45181,7 @@
       </c>
       <c r="D1399" s="1" t="inlineStr">
         <is>
-          <t>Hashtag (媒体与新闻学)</t>
+          <t>话题标签；标签 (명사)</t>
         </is>
       </c>
       <c r="E1399" s="1" t="inlineStr">
@@ -45299,7 +45299,7 @@
       </c>
       <c r="B1403" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚p͈a̠p̚]] 汤饭(Gukbap) (韩式饮食)</t>
+          <t>[[kuk̚p͈a̠p̚]] 汤饭 (명사)</t>
         </is>
       </c>
       <c r="C1403" s="1" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="D1403" s="1" t="inlineStr">
         <is>
-          <t>汤饭(Gukbap) (韩式饮食)</t>
+          <t>汤饭 (명사)</t>
         </is>
       </c>
       <c r="E1403" s="1" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="B1404" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠(ː)ŋ]] 汤/炖汤(Tang) (韩式饮食)</t>
+          <t>[[tʰa̠(ː)ŋ]] 汤；炖汤 (명사)</t>
         </is>
       </c>
       <c r="C1404" s="1" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="D1404" s="1" t="inlineStr">
         <is>
-          <t>汤/炖汤(Tang) (韩式饮食)</t>
+          <t>汤；炖汤 (명사)</t>
         </is>
       </c>
       <c r="E1404" s="1" t="inlineStr">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="B1405" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕ͈a̠d͡ʑa̠ŋmjʌ̹n]] 炸酱面(Jjajangmyeon) (韩式饮食)</t>
+          <t>[[t͡ɕ͈a̠d͡ʑa̠ŋmjʌ̹n]] 炸酱面 (명사)</t>
         </is>
       </c>
       <c r="C1405" s="1" t="inlineStr">
@@ -45373,7 +45373,7 @@
       </c>
       <c r="D1405" s="1" t="inlineStr">
         <is>
-          <t>炸酱面(Jjajangmyeon) (韩式饮食)</t>
+          <t>炸酱面 (명사)</t>
         </is>
       </c>
       <c r="E1405" s="1" t="inlineStr">
@@ -45395,7 +45395,7 @@
       </c>
       <c r="B1406" s="1" t="inlineStr">
         <is>
-          <t>[[s͈a̠m]] 包饭(Ssam) (韩式饮食)</t>
+          <t>[[s͈a̠m]] 菜包饭；包饭 (명사)</t>
         </is>
       </c>
       <c r="C1406" s="1" t="inlineStr">
@@ -45405,7 +45405,7 @@
       </c>
       <c r="D1406" s="1" t="inlineStr">
         <is>
-          <t>包饭(Ssam) (韩式饮食)</t>
+          <t>菜包饭；包饭 (명사)</t>
         </is>
       </c>
       <c r="E1406" s="1" t="inlineStr">
@@ -45427,7 +45427,7 @@
       </c>
       <c r="B1407" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimɛk̚]] 炸鸡啤酒(Chimaek) (韩式饮食)</t>
+          <t>[[t͡ɕʰimɛk̚]] 炸鸡配啤酒 (명사)</t>
         </is>
       </c>
       <c r="C1407" s="1" t="inlineStr">
@@ -45437,7 +45437,7 @@
       </c>
       <c r="D1407" s="1" t="inlineStr">
         <is>
-          <t>炸鸡啤酒(Chimaek) (韩式饮食)</t>
+          <t>炸鸡配啤酒 (명사)</t>
         </is>
       </c>
       <c r="E1407" s="1" t="inlineStr">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="B1409" s="1" t="inlineStr">
         <is>
-          <t>[hutnamimkik] 豆芽汤 (Kongnamul Guk) (韩国饮食)</t>
+          <t>[hutnamimkik] 豆芽汤 (명사)</t>
         </is>
       </c>
       <c r="C1409" s="1" t="inlineStr">
@@ -45501,7 +45501,7 @@
       </c>
       <c r="D1409" s="1" t="inlineStr">
         <is>
-          <t>豆芽汤 (Kongnamul Guk) (韩国饮食)</t>
+          <t>豆芽汤 (명사)</t>
         </is>
       </c>
       <c r="E1409" s="1" t="inlineStr">
@@ -45523,7 +45523,7 @@
       </c>
       <c r="B1410" s="1" t="inlineStr">
         <is>
-          <t>[[o̞de̞ŋ]] 鱼饼 (Odeng) (韩国饮食)</t>
+          <t>[[o̞de̞ŋ]] 鱼饼；鱼糕 (명사)</t>
         </is>
       </c>
       <c r="C1410" s="1" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="D1410" s="1" t="inlineStr">
         <is>
-          <t>鱼饼 (Odeng) (韩国饮食)</t>
+          <t>鱼饼；鱼糕 (명사)</t>
         </is>
       </c>
       <c r="E1410" s="1" t="inlineStr">
@@ -45555,7 +45555,7 @@
       </c>
       <c r="B1411" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuk̚]] 粥 (Juk) (韩国饮食)</t>
+          <t>[[t͡ɕuk̚]] 粥 (명사)</t>
         </is>
       </c>
       <c r="C1411" s="1" t="inlineStr">
@@ -45565,7 +45565,7 @@
       </c>
       <c r="D1411" s="1" t="inlineStr">
         <is>
-          <t>粥 (Juk) (韩国饮食)</t>
+          <t>粥 (명사)</t>
         </is>
       </c>
       <c r="E1411" s="1" t="inlineStr">
@@ -45587,7 +45587,7 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰik̚t͡ɕʰo̞]] 醋 (Shikcho) (韩国饮食)</t>
+          <t>[[ɕʰik̚t͡ɕʰo̞]] 食醋；醋 (명사)</t>
         </is>
       </c>
       <c r="C1412" s="1" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="D1412" s="1" t="inlineStr">
         <is>
-          <t>醋 (Shikcho) (韩国饮食)</t>
+          <t>食醋；醋 (명사)</t>
         </is>
       </c>
       <c r="E1412" s="1" t="inlineStr">
@@ -45619,7 +45619,7 @@
       </c>
       <c r="B1413" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋpʰa̠]] 洋葱 (Yangpa) (韩国饮食)</t>
+          <t>[[ja̠ŋpʰa̠]] 洋葱 (명사)</t>
         </is>
       </c>
       <c r="C1413" s="1" t="inlineStr">
@@ -45629,7 +45629,7 @@
       </c>
       <c r="D1413" s="1" t="inlineStr">
         <is>
-          <t>洋葱 (Yangpa) (韩国饮食)</t>
+          <t>洋葱 (명사)</t>
         </is>
       </c>
       <c r="E1413" s="1" t="inlineStr">
@@ -45651,7 +45651,7 @@
       </c>
       <c r="B1414" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ŋsʰujuk̚]] 糖醋肉 (Tangsuyuk) (韩国饮食)</t>
+          <t>[[tʰa̠ŋsʰujuk̚]] 糖醋肉 (명사)</t>
         </is>
       </c>
       <c r="C1414" s="1" t="inlineStr">
@@ -45661,7 +45661,7 @@
       </c>
       <c r="D1414" s="1" t="inlineStr">
         <is>
-          <t>糖醋肉 (Tangsuyuk) (韩国饮食)</t>
+          <t>糖醋肉 (명사)</t>
         </is>
       </c>
       <c r="E1414" s="1" t="inlineStr">
@@ -45683,7 +45683,7 @@
       </c>
       <c r="B1415" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠p̚k͈o̞k̚p͈a̠p̚]] 杂谷饭 (Japgok Bap) (韩国饮食)</t>
+          <t>[[t͡ɕa̠p̚k͈o̞k̚p͈a̠p̚]] 杂粮饭；杂谷饭 (명사)</t>
         </is>
       </c>
       <c r="C1415" s="1" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="D1415" s="1" t="inlineStr">
         <is>
-          <t>杂谷饭 (Japgok Bap) (韩国饮食)</t>
+          <t>杂粮饭；杂谷饭 (명사)</t>
         </is>
       </c>
       <c r="E1415" s="1" t="inlineStr">
@@ -45715,7 +45715,7 @@
       </c>
       <c r="B1416" s="1" t="inlineStr">
         <is>
-          <t>[chomikat] 鱼饼汤 (Eomuk Tang) (韩国饮食)</t>
+          <t>[chomikat] 鱼糕汤；鱼饼汤 (명사)</t>
         </is>
       </c>
       <c r="C1416" s="1" t="inlineStr">
@@ -45725,7 +45725,7 @@
       </c>
       <c r="D1416" s="1" t="inlineStr">
         <is>
-          <t>鱼饼汤 (Eomuk Tang) (韩国饮食)</t>
+          <t>鱼糕汤；鱼饼汤 (명사)</t>
         </is>
       </c>
       <c r="E1416" s="1" t="inlineStr">
@@ -45747,7 +45747,7 @@
       </c>
       <c r="B1417" s="1" t="inlineStr">
         <is>
-          <t>[[kje̞ɾa̠ɲt͡ɕ͈im]] 蒸蛋 (Gyeran Jjim) (韩国饮食)</t>
+          <t>[[kje̞ɾa̠ɲt͡ɕ͈im]] 蒸蛋；鸡蛋羹 (명사)</t>
         </is>
       </c>
       <c r="C1417" s="1" t="inlineStr">
@@ -45757,7 +45757,7 @@
       </c>
       <c r="D1417" s="1" t="inlineStr">
         <is>
-          <t>蒸蛋 (Gyeran Jjim) (韩国饮食)</t>
+          <t>蒸蛋；鸡蛋羹 (명사)</t>
         </is>
       </c>
       <c r="E1417" s="1" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>[mechin] 辣 (Maeun) (韩国饮食)</t>
+          <t>[mechin] 辣的；辛辣的 (형용사)</t>
         </is>
       </c>
       <c r="C1418" s="1" t="inlineStr">
@@ -45789,7 +45789,7 @@
       </c>
       <c r="D1418" s="1" t="inlineStr">
         <is>
-          <t>辣 (Maeun) (韩国饮食)</t>
+          <t>辣的；辛辣的 (형용사)</t>
         </is>
       </c>
       <c r="E1418" s="1" t="inlineStr">
@@ -45811,7 +45811,7 @@
       </c>
       <c r="B1419" s="1" t="inlineStr">
         <is>
-          <t>[[twe̞ɲd͡ʑa̠ŋɡuk̚]] 大酱汤 (Doenjang Guk) (韩国饮食)</t>
+          <t>[[twe̞ɲd͡ʑa̠ŋɡuk̚]] 大酱汤 (명사)</t>
         </is>
       </c>
       <c r="C1419" s="1" t="inlineStr">
@@ -45821,7 +45821,7 @@
       </c>
       <c r="D1419" s="1" t="inlineStr">
         <is>
-          <t>大酱汤 (Doenjang Guk) (韩国饮食)</t>
+          <t>大酱汤 (명사)</t>
         </is>
       </c>
       <c r="E1419" s="1" t="inlineStr">
@@ -45843,7 +45843,7 @@
       </c>
       <c r="B1420" s="1" t="inlineStr">
         <is>
-          <t>[[po̞ɾiba̠p̚]] Boribap (韩国饮食文化)</t>
+          <t>[[po̞ɾiba̠p̚]] 大麦饭；麦饭 (명사)</t>
         </is>
       </c>
       <c r="C1420" s="1" t="inlineStr">
@@ -45853,7 +45853,7 @@
       </c>
       <c r="D1420" s="1" t="inlineStr">
         <is>
-          <t>Boribap (韩国饮食文化)</t>
+          <t>大麦饭；麦饭 (명사)</t>
         </is>
       </c>
       <c r="E1420" s="1" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="B1424" s="1" t="inlineStr">
         <is>
-          <t>[[puŋʌ̹p͈a̠ŋ]] Bungeoppang (韩国饮食文化)</t>
+          <t>[[puŋʌ̹p͈a̠ŋ]] 鲫鱼饼；鲷鱼烧 (명사)</t>
         </is>
       </c>
       <c r="C1424" s="1" t="inlineStr">
@@ -45981,7 +45981,7 @@
       </c>
       <c r="D1424" s="1" t="inlineStr">
         <is>
-          <t>Bungeoppang (韩国饮食文化)</t>
+          <t>鲫鱼饼；鲷鱼烧 (명사)</t>
         </is>
       </c>
       <c r="E1424" s="1" t="inlineStr">
@@ -46003,7 +46003,7 @@
       </c>
       <c r="B1425" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠t̚p͈iŋsʰu]] Patbingsu (韩国饮食文化)</t>
+          <t>[[pʰa̠t̚p͈iŋsʰu]] 红豆刨冰；红豆冰 (명사)</t>
         </is>
       </c>
       <c r="C1425" s="1" t="inlineStr">
@@ -46013,7 +46013,7 @@
       </c>
       <c r="D1425" s="1" t="inlineStr">
         <is>
-          <t>Patbingsu (韩国饮食文化)</t>
+          <t>红豆刨冰；红豆冰 (명사)</t>
         </is>
       </c>
       <c r="E1425" s="1" t="inlineStr">
@@ -46035,7 +46035,7 @@
       </c>
       <c r="B1426" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋsʰʌ̹nɡui]] Ganjang Gui Fish (韩国饮食文化)</t>
+          <t>[[sʰɛŋsʰʌ̹nɡui]] 烤鱼 (명사)</t>
         </is>
       </c>
       <c r="C1426" s="1" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="D1426" s="1" t="inlineStr">
         <is>
-          <t>Ganjang Gui Fish (韩国饮食文化)</t>
+          <t>烤鱼 (명사)</t>
         </is>
       </c>
       <c r="E1426" s="1" t="inlineStr">
@@ -46387,7 +46387,7 @@
       </c>
       <c r="B1437" s="1" t="inlineStr">
         <is>
-          <t>[[we̞ɭbiŋ]] 健康幸福(Well-being) (心理健康与身心保健)</t>
+          <t>[[we̞ɭbiŋ]] 身心健康；福祉 (명사)</t>
         </is>
       </c>
       <c r="C1437" s="1" t="inlineStr">
@@ -46397,7 +46397,7 @@
       </c>
       <c r="D1437" s="1" t="inlineStr">
         <is>
-          <t>健康幸福(Well-being) (心理健康与身心保健)</t>
+          <t>身心健康；福祉 (명사)</t>
         </is>
       </c>
       <c r="E1437" s="1" t="inlineStr">
@@ -46675,7 +46675,7 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>[hahachuerenke] Kakao Friends (韩国流行文化)</t>
+          <t>[hahachuerenke] Kakao Friends (韩国卡通IP形象) (명사)</t>
         </is>
       </c>
       <c r="C1446" s="1" t="inlineStr">
@@ -46685,7 +46685,7 @@
       </c>
       <c r="D1446" s="1" t="inlineStr">
         <is>
-          <t>Kakao Friends (韩国流行文化)</t>
+          <t>Kakao Friends (韩国卡通IP形象) (명사)</t>
         </is>
       </c>
       <c r="E1446" s="1" t="inlineStr">
@@ -47571,7 +47571,7 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>[rek] 延迟(Lag) (游戏与电竞)</t>
+          <t>[rek] 游戏延迟；网络卡顿 (명사)</t>
         </is>
       </c>
       <c r="C1474" s="1" t="inlineStr">
@@ -47581,7 +47581,7 @@
       </c>
       <c r="D1474" s="1" t="inlineStr">
         <is>
-          <t>延迟(Lag) (游戏与电竞)</t>
+          <t>游戏延迟；网络卡顿 (명사)</t>
         </is>
       </c>
       <c r="E1474" s="1" t="inlineStr">
@@ -47635,7 +47635,7 @@
       </c>
       <c r="B1476" s="1" t="inlineStr">
         <is>
-          <t>[ringeun] 重生(Respawn) (游戏与电竞)</t>
+          <t>[ringeun] 复活；重生 (명사)</t>
         </is>
       </c>
       <c r="C1476" s="1" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="D1476" s="1" t="inlineStr">
         <is>
-          <t>重生(Respawn) (游戏与电竞)</t>
+          <t>复活；重生 (명사)</t>
         </is>
       </c>
       <c r="E1476" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK1.xlsx
+++ b/languages/ko/output/import/韩语TOPIK1.xlsx
@@ -27283,7 +27283,7 @@
       </c>
       <c r="B840" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰe̞juk̚p͈o̞k̚]] PE制服 (校园生活)</t>
+          <t>[[t͡ɕʰe̞juk̚p͈o̞k̚]] 体操服；运动校服 (校园生活)</t>
         </is>
       </c>
       <c r="C840" s="1" t="inlineStr">
@@ -27293,7 +27293,7 @@
       </c>
       <c r="D840" s="1" t="inlineStr">
         <is>
-          <t>PE制服 (校园生活)</t>
+          <t>体操服；运动校服 (校园生活)</t>
         </is>
       </c>
       <c r="E840" s="1" t="inlineStr">
@@ -46867,7 +46867,7 @@
       </c>
       <c r="B1452" s="1" t="inlineStr">
         <is>
-          <t>[[ɸʷo̞ŋdɛ]] 弘大区（Hongdae）。 (韩国流行文化)</t>
+          <t>[[ɸʷo̞ŋdɛ]] 弘大（弘益大学周边商圈） (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1452" s="1" t="inlineStr">
@@ -46877,7 +46877,7 @@
       </c>
       <c r="D1452" s="1" t="inlineStr">
         <is>
-          <t>弘大区（Hongdae）。 (韩国流行文化)</t>
+          <t>弘大（弘益大学周边商圈） (韩国流行文化)</t>
         </is>
       </c>
       <c r="E1452" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK1.xlsx
+++ b/languages/ko/output/import/韩语TOPIK1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,12 +531,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[kwingutangnita] 对不起 (表达)</t>
+          <t>[[t͡ɕwe̞sʰo̞ŋɦa̠mnida̠]] 对不起 (表达)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>kwingutangnita</t>
+          <t>[t͡ɕwe̞sʰo̞ŋɦa̠mnida̠]</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠d͡ʑa̠ŋɕʰiɭ]] 浴室 (旅行)</t>
+          <t>[[ɸwa̠d͡ʑa̠ŋɕʰiɭ]] 厕所 (旅行)</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>浴室 (旅行)</t>
+          <t>厕所 (旅行)</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>[ngimryeangnita] 麻烦 (表达)</t>
+          <t>[[ɕiɭɭje̞ɦa̠mnida̠]] 麻烦 (表达)</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ngimryeangnita</t>
+          <t>[ɕiɭɭje̞ɦa̠mnida̠]</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[murekelchochy] 我不知道 (表达)</t>
+          <t>[[muɾɯɡe̞s͈ʌ̹jo]] 我不知道 (表达)</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>murekelchochy</t>
+          <t>[muɾɯɡe̞s͈ʌ̹jo]</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕo̞(ː)a̠jo]] 我喜欢 (表达)</t>
+          <t>[[ˈt͡ɕo̞(ː)a̠jo]] 好；可以 (表达)</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>我喜欢 (表达)</t>
+          <t>好；可以 (表达)</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰiɾʌ̹jo]] 我不喜欢 (表达)</t>
+          <t>[[ɕʰiɾʌ̹jo]] 不要；讨厌 (表达)</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>我不喜欢 (表达)</t>
+          <t>不要；讨厌 (表达)</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>[kingechy] 请 (基础)</t>
+          <t>[[t͡ɕusɛ̝jo]] 请 (基础)</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>kingechy</t>
+          <t>[t͡ɕusɛ̝jo]</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>[kangkanmanchy] 等一下 (表达)</t>
+          <t>[[t͡ɕamk͈anmanjo]] 等一下 (表达)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>kangkanmanchy</t>
+          <t>[t͡ɕamk͈anmanjo]</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>[pikaangnita] 恭喜 (表达)</t>
+          <t>[[t͡ɕʰuka̠hamnida]] 恭喜 (表达)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>pikaangnita</t>
+          <t>[t͡ɕʰuka̠hamnida]</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>[tuchwkingechy] 帮助 (基础)</t>
+          <t>[[to̞wa̠t͡ɕusɛ̝jo]] 帮助 (基础)</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>tuchwkingechy</t>
+          <t>[to̞wa̠t͡ɕusɛ̝jo]</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>[hechipwi] K-Beauty（韩国美妆） (文化)</t>
+          <t>[[kʰe̞ipʰjutʰi]] 韩式美妆 (文化)</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>hechipwi</t>
+          <t>[kʰe̞ipʰjutʰi]</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>K-Beauty（韩国美妆） (文化)</t>
+          <t>韩式美妆 (文化)</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>[[ˈma̠(ː)nβwa̠]] 韩国漫画 (文化)</t>
+          <t>[[ˈma̠(ː)nβwa̠]] 漫画 (文化)</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>韩国漫画 (文化)</t>
+          <t>漫画 (文化)</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɘ(ː)mɕʰimɕʰiɡa̠n]] 午休 (日常生活)</t>
+          <t>[[ˈt͡ɕɘ(ː)mɕʰimɕʰiɡa̠n]] 午餐时间 (日常生活)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>午休 (日常生活)</t>
+          <t>午餐时间 (日常生活)</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>[katpuki] 买菜 (日常生活)</t>
+          <t>[[t͡ɕa̠mboɡi]] 买菜 (日常生活)</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>katpuki</t>
+          <t>[t͡ɕa̠mboɡi]</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>[[sʰuʌ̹p̚]] 纲 (教育)</t>
+          <t>[[sʰuʌ̹p̚]] 课 (教育)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>纲 (教育)</t>
+          <t>课 (教育)</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>[rengen] 课程 (教育)</t>
+          <t>[[ɾe.s͈ʌn]] 课程 (教育)</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>rengen</t>
+          <t>[ɾe.s͈ʌn]</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠mo̞k̚]] 主题 (教育)</t>
+          <t>[[kwa̠mo̞k̚]] 科目 (教育)</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>主题 (教育)</t>
+          <t>科目 (教育)</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋʌ̹]] 中文 (教育)</t>
+          <t>[[jʌ̹ŋʌ̹]] 英语 (教育)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>中文 (教育)</t>
+          <t>英语 (教育)</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰe̞juk̚]] 教育选修课 (教育)</t>
+          <t>[[t͡ɕʰe̞juk̚]] 体育 (教育)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>教育选修课 (教育)</t>
+          <t>体育 (教育)</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkjo(ː)ɕʰiɭ]] 课桌式 (教育)</t>
+          <t>[[ˈkjo(ː)ɕʰiɭ]] 教室 (教育)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>课桌式 (教育)</t>
+          <t>教室 (教育)</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠kʰʌ̹]] 刻度线标志 (教育)</t>
+          <t>[[ma̠kʰʌ̹]] 马克笔 (教育)</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>刻度线标志 (教育)</t>
+          <t>马克笔 (教育)</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkjo(ː)ɡwa̠sʰʌ̹]] 考证 (教育)</t>
+          <t>[[ˈkjo(ː)ɡwa̠sʰʌ̹]] 教科书 (教育)</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>考证 (教育)</t>
+          <t>教科书 (教育)</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[[to̞ŋɡi]] 同学 (教育)</t>
+          <t>[[to̞ŋɡi]] 动机；同期 (教育)</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>同学 (教育)</t>
+          <t>动机；同期 (教育)</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰiɭma̠ŋɦa̠da̠]] 失望的脸 (情感)</t>
+          <t>[[ɕʰiɭma̠ŋɦa̠da̠]] 失望 (情感)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>失望的脸 (情感)</t>
+          <t>失望 (情感)</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>[[uuɾɦa̠da̠]] 压低 (情感)</t>
+          <t>[[uuɾɦa̠da̠]] 忧郁 (情感)</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>压低 (情感)</t>
+          <t>忧郁 (情感)</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>[myotratata] 开朗 (情感)</t>
+          <t>[[mjʌ̹ŋɾa̠ɦa̠da̠]] 开朗 (情感)</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>myotratata</t>
+          <t>[mjʌ̹ŋɾa̠ɦa̠da̠]</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>[kangtutpakta] 感动 (情感)</t>
+          <t>[[ka̠ŋto̞ŋpa̠t̚t͈a̠]] 感动 (情感)</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>kangtutpakta</t>
+          <t>[ka̠ŋto̞ŋpa̠t̚t͈a̠]</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>[pirocheata] 羡慕 (情绪)</t>
+          <t>[[puɾʌ̹wʌ̹ɦa̠da̠]] 羡慕 (情绪)</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>pirocheata</t>
+          <t>[puɾʌ̹wʌ̹ɦa̠da̠]</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>[ngeerengepakta] 压力大 (情绪)</t>
+          <t>[[sɨ.tʰɨ.ɾe.sɨp̚.t͈a.da]] 压力大 (情绪)</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>ngeerengepakta</t>
+          <t>[sɨ.tʰɨ.ɾe.sɨp̚.t͈a.da]</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>[taketnata] 恼怒 (情绪)</t>
+          <t>[[t͈a.dʑɯŋ.na.da]] 恼怒 (情绪)</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>taketnata</t>
+          <t>[t͈a.dʑɯŋ.na.da]</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>[sipita] 闷闷不乐 (情感)</t>
+          <t>[[p͈i.tɕʰi.da]] 闹别扭；使性子 (情感)</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>sipita</t>
+          <t>[p͈i.tɕʰi.da]</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>闷闷不乐 (情感)</t>
+          <t>闹别扭；使性子 (情感)</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>[katnanngerongta] 顽皮 (情感)</t>
+          <t>[[tɕaŋ.nan.sɨ.ɾʌp̚.t͈a.da]] 顽皮 (情感)</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>katnanngerongta</t>
+          <t>[tɕaŋ.nan.sɨ.ɾʌp̚.t͈a.da]</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɘ(ː)sʰɛkʰa̠da̠]] 不安 (情感)</t>
+          <t>[[ˈɘ(ː)sʰɛkʰa̠da̠]] 尴尬 (情感)</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>不安 (情感)</t>
+          <t>尴尬 (情感)</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>[[pudɯɾʌ̹p̚t͈a̠]] 招标 (情感)</t>
+          <t>[[pudɯɾʌ̹p̚t͈a̠]] 柔软 (情感)</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>招标 (情感)</t>
+          <t>柔软 (情感)</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰa̠(ː)ŋkʰwɛɦa̠da̠]] 刷新完成 (情感)</t>
+          <t>[[ˈsʰa̠(ː)ŋkʰwɛɦa̠da̠]] 清爽 (情感)</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>刷新完成 (情感)</t>
+          <t>清爽 (情感)</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>[chyatnyongpihin] 韩式炸鸡 (食物)</t>
+          <t>[[jaŋ.ɲʌm.tɕʰi.kʰin]] 韩式炸鸡 (食物)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>chyatnyongpihin</t>
+          <t>[jaŋ.ɲʌm.tɕʰi.kʰin]</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠nɯɭ]] 放了大蒜的 (食物)</t>
+          <t>[[ma̠nɯɭ]] 大蒜 (食物)</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>放了大蒜的 (食物)</t>
+          <t>大蒜 (食物)</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕu(ː)mun]] 货物运载 (食物)</t>
+          <t>[[ˈt͡ɕu(ː)mun]] 点餐 (食物)</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>货物运载 (食物)</t>
+          <t>点餐 (食物)</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>[churenmanchichechy] 好久不见... (问候)</t>
+          <t>[[o.ɾɛn.ma.ni.e.jo]] 好久不见... (问候)</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>churenmanchichechy</t>
+          <t>[o.ɾɛn.ma.ni.e.jo]</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>[temchochungechy] 请进 (问候)</t>
+          <t>[[tɯ.ɾʌ.o.se.jo]] 请进 (问候)</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>temchochungechy</t>
+          <t>[tɯ.ɾʌ.o.se.jo]</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>[ngikuangyolchochy] 辛苦了 (问候语)</t>
+          <t>[[su.ɡo.ha.ɕjʌ.s͈ʌ.jo]] 辛苦了 (问候语)</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>ngikuangyolchochy</t>
+          <t>[su.ɡo.ha.ɕjʌ.s͈ʌ.jo]</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>[ingnengechy] 打起精神来 (问候语)</t>
+          <t>[[çim.nɛ.se.jo]] 打起精神来 (问候语)</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>ingnengechy</t>
+          <t>[çim.nɛ.se.jo]</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[kwenpalchachy] 没关系 (问候语)</t>
+          <t>[[kwɛn.tɕʰa.na.jo]] 没关系 (问候语)</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>kwenpalchachy</t>
+          <t>[kwɛn.tɕʰa.na.jo]</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>[mimrunchiky] 当然 (问候语)</t>
+          <t>[[mul.lo.ɲi.tɕjo]] 当然 (问候语)</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>mimrunchiky</t>
+          <t>[mul.lo.ɲi.tɕjo]</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>[minkechotchochy] 没问题 (问候语)</t>
+          <t>[[mun.dʑe.ʌp̚.s͈ʌ.jo]] 没问题 (问候语)</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>minkechotchochy</t>
+          <t>[mun.dʑe.ʌp̚.s͈ʌ.jo]</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>[chonketenkichy] 随时 (问候语)</t>
+          <t>[[ʌn.dʑe.tɯn.dʑi.jo]] 随时 (问候语)</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>chonketenkichy</t>
+          <t>[ʌn.dʑe.tɯn.dʑi.jo]</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>[chamkelchochy] 我明白了 (问候语)</t>
+          <t>[[al.ɡʌ.s͈ʌ.jo]] 我明白了 (问候语)</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>chamkelchochy</t>
+          <t>[al.ɡʌ.s͈ʌ.jo]</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>[kotmamchy] 真的吗？ (问候语)</t>
+          <t>[[tɕʌŋ.ma.ɾjo]] 真的吗？ (问候语)</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>kotmamchy</t>
+          <t>[tɕʌŋ.ma.ɾjo]</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>[tetanechy] 太棒了 (问候语)</t>
+          <t>[[tɛ.da.nɛ.jo]] 太棒了 (问候语)</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>tetanechy</t>
+          <t>[tɛ.da.nɛ.jo]</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>[pasachy] 我很忙 (问候语)</t>
+          <t>[[pa.p͈a.jo]] 我很忙 (问候语)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>pasachy</t>
+          <t>[pa.p͈a.jo]</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>[ikunechy] 我累了 (问候语)</t>
+          <t>[[pʰi.ɡon.hɛ.jo]] 我累了 (问候语)</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>ikunechy</t>
+          <t>[pʰi.ɡon.hɛ.jo]</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>[mannachy] 见个面吧 (问候语)</t>
+          <t>[[man͈ajo]] 见个面吧 (问候语)</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>mannachy</t>
+          <t>[man͈ajo]</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>[kungingangechy] 小心 (问候语)</t>
+          <t>[[t͡ɕo̞ɕʰi.ma̠.sʰe̞.jo]] 小心 (问候语)</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>kungingangechy</t>
+          <t>[t͡ɕo̞ɕʰi.ma̠.sʰe̞.jo]</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>[kemkochelchochy] 我玩得很开心 (问候语)</t>
+          <t>[[t͡ɕɯɭ.ɡʌ̹.wʌ̹.s͈ʌ̹.jo]] 我玩得很开心 (问候语)</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>kemkochelchochy</t>
+          <t>[t͡ɕɯɭ.ɡʌ̹.wʌ̹.s͈ʌ̹.jo]</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>[imrwtechy] 做得好 (问候语)</t>
+          <t>[[çjuɭ.ɭjuŋ.ɦɛ̝.jo]] 做得好 (问候语)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>imrwtechy</t>
+          <t>[çjuɭ.ɭjuŋ.ɦɛ̝.jo]</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>[amkachy] 我们一起…好吗？ (问候语)</t>
+          <t>[[ha̠ɭ.ɡ͈a̠.jo]] 我们一起…好吗？ (问候语)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>amkachy</t>
+          <t>[ha̠ɭ.ɡ͈a̠.jo]</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[kokkotelchochy] 我很担心你 (问候语)</t>
+          <t>[[kʌ̹k̚.t͡ɕʌ̹ŋ.ɦɛ̝.s͈ʌ̹.jo]] 我很担心你 (问候语)</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>kokkotelchochy</t>
+          <t>[kʌ̹k̚.t͡ɕʌ̹ŋ.ɦɛ̝.s͈ʌ̹.jo]</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>[kerongchy] 当然 (问候语)</t>
+          <t>[[kɯ.ɾʌ̹m.jo]] 当然 (问候语)</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>kerongchy</t>
+          <t>[kɯ.ɾʌ̹m.jo]</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>[mikchochy] 我相信你 (问候语)</t>
+          <t>[[mi.ɾʌ̹.jo]] 我相信你 (问候语)</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>mikchochy</t>
+          <t>[mi.ɾʌ̹.jo]</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>[chimmum] 日落 (自然)</t>
+          <t>[[iɭ.moɭ]] 日落 (自然)</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>chimmum</t>
+          <t>[iɭ.moɭ]</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>[kyomunelchochy] 结婚 (人际关系)</t>
+          <t>[[kʲʌ̹.ɾo̞n.ɦɛ̝.s͈ʌ̹.jo]] 结婚 (人际关系)</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t>kyomunelchochy</t>
+          <t>[kʲʌ̹.ɾo̞n.ɦɛ̝.s͈ʌ̹.jo]</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>[ngaratechy] 我爱你 (人际关系)</t>
+          <t>[[sa̠.ɾa̠ŋ.ɦɛ̝.jo]] 我爱你 (人际关系)</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>ngaratechy</t>
+          <t>[sa̠.ɾa̠ŋ.ɦɛ̝.jo]</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>[chilchochy] 有...吗？ (购物)</t>
+          <t>[[i̠t̚.s͈ʌ̹.jo]] 有...吗？ (购物)</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>chilchochy</t>
+          <t>[i̠t̚.s͈ʌ̹.jo]</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>[[s͈a̠id͡ʑɯ]] 规模​​ (购物)</t>
+          <t>[[s͈a̠id͡ʑɯ]] 尺码 (购物)</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>规模​​ (购物)</t>
+          <t>尺码 (购物)</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -9203,17 +9203,17 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>[tuttemin] 时尚区 (购物)</t>
+          <t>[[to̞ŋ.dɛ̝.mun]] 东大门（首尔地名） (购物)</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>tuttemin</t>
+          <t>[to̞ŋ.dɛ̝.mun]</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>时尚区 (购物)</t>
+          <t>东大门（首尔地名） (购物)</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
@@ -9427,17 +9427,17 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[wichenken] 职责包括︰ (购物)</t>
+          <t>[[hwe̞.wʌ̹n.ɡ͈wʌ̹n]] 会员卡 (购物)</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>wichenken</t>
+          <t>[hwe̞.wʌ̹n.ɡ͈wʌ̹n]</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>职责包括︰ (购物)</t>
+          <t>会员卡 (购物)</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>[chingchoputa] 试穿 (购物)</t>
+          <t>[[i̠.pʌ̹.bo̞.da̠]] 试穿 (购物)</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>chingchoputa</t>
+          <t>[i̠.pʌ̹.bo̞.da̠]</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
@@ -9555,17 +9555,17 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>[kyomke] 还款 (购物)</t>
+          <t>[[kʲʌ̹ɭ.t͡ɕe̞]] 付款 (购物)</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>kyomke</t>
+          <t>[kʲʌ̹ɭ.t͡ɕe̞]</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>还款 (购物)</t>
+          <t>付款 (购物)</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
@@ -9587,17 +9587,17 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>[chotichyechy] 这病房里的... (旅行)</t>
+          <t>[[ʌ̹.di.je̞.jo]] 在哪里 (旅行)</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>chotichyechy</t>
+          <t>[ʌ̹.di.je̞.jo]</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t>这病房里的... (旅行)</t>
+          <t>在哪里 (旅行)</t>
         </is>
       </c>
       <c r="E287" s="1" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>[pehechin] 签到 (旅游)</t>
+          <t>[[t͡ɕʰe̞.kʰɯ.in]] 签到 (旅游)</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>pehechin</t>
+          <t>[t͡ɕʰe̞.kʰɯ.in]</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>[[ˈje̞(ː)ja̠k̚]] 预定 (旅游)</t>
+          <t>[[ˈje̞(ː)ja̠k̚]] 预订 (旅游)</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>预定 (旅游)</t>
+          <t>预订 (旅游)</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>[kwnkwtki] 旅游点 (旅游)</t>
+          <t>[[kwa̠n.ɡwa̠ŋ.t͡ɕi]] 旅游点 (旅游)</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>kwnkwtki</t>
+          <t>[kwa̠n.ɡwa̠ŋ.t͡ɕi]</t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>[[tʰikʰe̞t̚]] 传说券 (旅游)</t>
+          <t>[[tʰikʰe̞t̚]] 门票 (旅游)</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="D296" s="1" t="inlineStr">
         <is>
-          <t>传说券 (旅游)</t>
+          <t>门票 (旅游)</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>[konutngikat] 传统市场 (명사)</t>
+          <t>[[tɕʌn.toŋ.ɕi.dʑaŋ]] 传统市场 (명사)</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>konutngikat</t>
+          <t>[tɕʌn.toŋ.ɕi.dʑaŋ]</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>[kit] 宫殿 (旅游)</t>
+          <t>[[kuŋ]] 宫殿 (旅游)</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>[kuŋ]</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɛ(ː)bjʌ̹n]] 沙滩 (旅游)</t>
+          <t>[[ˈhɛ(ː)bjʌ̹n]] 海滩 (旅游)</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>沙滩 (旅游)</t>
+          <t>海滩 (旅游)</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>[imoni] T-Money卡 (旅游)</t>
+          <t>[[tʰimʌni]] T-Money卡 (旅游)</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t>imoni</t>
+          <t>[tʰimʌni]</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
@@ -10419,17 +10419,17 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[momchochy] 远吗？；路途远吗？ (구)</t>
+          <t>[[mʌɾʌjo]] 远；很远 (구)</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>momchochy</t>
+          <t>[mʌɾʌjo]</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t>远吗？；路途远吗？ (구)</t>
+          <t>远；很远 (구)</t>
         </is>
       </c>
       <c r="E313" s="1" t="inlineStr">
@@ -10483,17 +10483,17 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[chyomcholchochy] 门开着吗？ (旅游)</t>
+          <t>[[jʌɾʌssʌjo]] 开了；打开了 (旅游)</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t>chyomcholchochy</t>
+          <t>[jʌɾʌssʌjo]</t>
         </is>
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t>门开着吗？ (旅游)</t>
+          <t>开了；打开了 (旅游)</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[chommachyechy] 大概多少钱 (旅游)</t>
+          <t>[[ʌɭmajejo]] 大概多少钱 (旅游)</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t>chommachyechy</t>
+          <t>[ʌɭmajejo]</t>
         </is>
       </c>
       <c r="D316" s="1" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>[nginchythate] 信用卡 (旅游)</t>
+          <t>[[ɕiɲoŋkʰa̠dɯ]] 信用卡 (旅游)</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t>nginchythate</t>
+          <t>[ɕiɲoŋkʰa̠dɯ]</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
@@ -10995,17 +10995,17 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>[hoemrit] 情侣戒指 (文化)</t>
+          <t>[[kʰʌpʰʌɭɭiŋ]] 情侣对戒 (文化)</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t>hoemrit</t>
+          <t>[kʰʌpʰʌɭɭiŋ]</t>
         </is>
       </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t>情侣戒指 (文化)</t>
+          <t>情侣对戒 (文化)</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>[ngeotihae] 读书咖啡厅 (文化)</t>
+          <t>[[s͈ɯtʰʌdikʰapʰe]] 读书咖啡厅 (文化)</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t>ngeotihae</t>
+          <t>[s͈ɯtʰʌdikʰapʰe]</t>
         </is>
       </c>
       <c r="D335" s="1" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>[uuhate] 写真卡 (文化)</t>
+          <t>[[pʰo̞tʰɔkʰa̠dɯ]] 写真卡 (文化)</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t>uuhate</t>
+          <t>[pʰo̞tʰɔkʰa̠dɯ]</t>
         </is>
       </c>
       <c r="D337" s="1" t="inlineStr">
@@ -11315,12 +11315,12 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>[kechymi] 可爱鬼（可爱游戏） (文化)</t>
+          <t>[[kɥjomi]] 可爱鬼（可爱游戏） (文化)</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t>kechymi</t>
+          <t>[kɥjomi]</t>
         </is>
       </c>
       <c r="D341" s="1" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰa̠wʌ̹]] 花洒 (日常生活)</t>
+          <t>[[ɕʰa̠wʌ̹]] 淋浴 (日常生活)</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D345" s="1" t="inlineStr">
         <is>
-          <t>花洒 (日常生活)</t>
+          <t>淋浴 (日常生活)</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[[pinu]] 香皂 (日常生活)</t>
+          <t>[[pinu]] 肥皂 (日常生活)</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>香皂 (日常生活)</t>
+          <t>肥皂 (日常生活)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>[ngechanke] 洗面奶 (日常生活)</t>
+          <t>[[se̞ːa̠nd͡ʑe̞]] 洗面奶 (日常生活)</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t>ngechanke</t>
+          <t>[se̞ːa̠nd͡ʑe̞]</t>
         </is>
       </c>
       <c r="D351" s="1" t="inlineStr">
@@ -11667,12 +11667,12 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>[pungengke] 保湿乳： (日常生活)</t>
+          <t>[[po̞bs͈ʌ̹d͡ʑe]] 保湿乳： (日常生活)</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t>pungengke</t>
+          <t>[po̞bs͈ʌ̹d͡ʑe]</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>[[ˈmjɘ(ː)ndo̞ɡi]] 技能-电魂 (日常生活)</t>
+          <t>[[ˈmjɘ(ː)ndo̞ɡi]] 剃须刀 (日常生活)</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
-          <t>技能-电魂 (日常生活)</t>
+          <t>剃须刀 (日常生活)</t>
         </is>
       </c>
       <c r="E353" s="1" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠ɾimi]] 铁 (日常生活)</t>
+          <t>[[ta̠ɾimi]] 熨斗 (日常生活)</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="D355" s="1" t="inlineStr">
         <is>
-          <t>铁 (日常生活)</t>
+          <t>熨斗 (日常生活)</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>[[kʌ̹ɭɭe̞]] 拖地 (日常生活)</t>
+          <t>[[kʌ̹ɭɭe̞]] 抹布 (日常生活)</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t>拖地 (日常生活)</t>
+          <t>抹布 (日常生活)</t>
         </is>
       </c>
       <c r="E358" s="1" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>[cerekiputi] 垃圾袋 (日常生活)</t>
+          <t>[[s͈ɯ.ɾe.gi.boŋ.tʰu]] 垃圾袋 (日常生活)</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
         <is>
-          <t>cerekiputi</t>
+          <t>[s͈ɯ.ɾe.gi.boŋ.tʰu]</t>
         </is>
       </c>
       <c r="D361" s="1" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰik̚k͈isʰe̞t͡ɕʰʌ̹k̚k͈i]] 洗碗工 (日常生活)</t>
+          <t>[[ɕʰik̚k͈isʰe̞t͡ɕʰʌ̹k̚k͈i]] 洗碗机 (日常生活)</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>洗碗工 (日常生活)</t>
+          <t>洗碗机 (日常生活)</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹npʰuŋɡi]] 神秘折扇 (日常生活)</t>
+          <t>[[sʰʌ̹npʰuŋɡi]] 电风扇 (日常生活)</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t>神秘折扇 (日常生活)</t>
+          <t>电风扇 (日常生活)</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>[chinoun] 对讲机 (日常生活)</t>
+          <t>[[in.tʰʌ.pʰon]] 对讲机 (日常生活)</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t>chinoun</t>
+          <t>[in.tʰʌ.pʰon]</t>
         </is>
       </c>
       <c r="D376" s="1" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠md͡ʑa̠tʰa̠ŋ]] 马铃薯排骨汤 (食物)</t>
+          <t>[[ka̠md͡ʑa̠tʰa̠ŋ]] 土豆脊骨汤 (食物)</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>马铃薯排骨汤 (食物)</t>
+          <t>土豆脊骨汤 (食物)</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>[puripa] 大麦茶 (食物)</t>
+          <t>[[po.ɾi.tɕʰa]] 大麦茶 (食物)</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t>puripa</t>
+          <t>[po.ɾi.tɕʰa]</t>
         </is>
       </c>
       <c r="D390" s="1" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[pananachichw] 香蕉牛奶 (食物)</t>
+          <t>[[panana‿uju]] 香蕉牛奶 (食物)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t>pananachichw</t>
+          <t>[panana‿uju]</t>
         </is>
       </c>
       <c r="D391" s="1" t="inlineStr">
@@ -12947,12 +12947,12 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>[kukimarate] 地瓜拿铁 (食物)</t>
+          <t>[[kukʰimarate]] 地瓜拿铁 (食物)</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t>kukimarate</t>
+          <t>[kukʰimarate]</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
@@ -12979,17 +12979,17 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>[kyeranaree] 蛋塔 (食物)</t>
+          <t>[[keɾantʰaɾɯtʰɯ]] 蛋挞 (食物)</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t>kyeranaree</t>
+          <t>[keɾantʰaɾɯtʰɯ]</t>
         </is>
       </c>
       <c r="D393" s="1" t="inlineStr">
         <is>
-          <t>蛋塔 (食物)</t>
+          <t>蛋挞 (食物)</t>
         </is>
       </c>
       <c r="E393" s="1" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>[onipooping] 蜂蜜奶油洋芋片 (食物)</t>
+          <t>[[hʌnibʌtʰʌtɕʰip]] 蜂蜜奶油洋芋片 (食物)</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t>onipooping</t>
+          <t>[hʌnibʌtʰʌtɕʰip]</t>
         </is>
       </c>
       <c r="D395" s="1" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>[kichita] 烤 (食物)</t>
+          <t>[[kuːda]] 烤 (食物)</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
         <is>
-          <t>kichita</t>
+          <t>[kuːda]</t>
         </is>
       </c>
       <c r="D399" s="1" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>[tinta] 蒸 (食物)</t>
+          <t>[[t͈inda]] 蒸 (食物)</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
         <is>
-          <t>tinta</t>
+          <t>[t͈inda]</t>
         </is>
       </c>
       <c r="D400" s="1" t="inlineStr">
@@ -13235,12 +13235,12 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>[kengchinta] 煮 (食物)</t>
+          <t>[[k͈ɯɾinda]] 煮 (食物)</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t>kengchinta</t>
+          <t>[k͈ɯɾinda]</t>
         </is>
       </c>
       <c r="D401" s="1" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>[ekinta] 炸 (食物)</t>
+          <t>[[tʰwiginda]] 炸 (食物)</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
         <is>
-          <t>ekinta</t>
+          <t>[tʰwiginda]</t>
         </is>
       </c>
       <c r="D402" s="1" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>[ngetkot] 生 (食物)</t>
+          <t>[[sɛŋɡʌt]] 生 (食物)</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
         <is>
-          <t>ngetkot</t>
+          <t>[sɛŋɡʌt]</t>
         </is>
       </c>
       <c r="D403" s="1" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>[kechinta] 腌制 (食物)</t>
+          <t>[[tɕɛwunda]] 腌制 (食物)</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t>kechinta</t>
+          <t>[tɕɛwunda]</t>
         </is>
       </c>
       <c r="D404" s="1" t="inlineStr">
@@ -13459,12 +13459,12 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>[ngikki] 豆芽 (食物)</t>
+          <t>[[sukdʑu]] 豆芽 (食物)</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t>ngikki</t>
+          <t>[sukdʑu]</t>
         </is>
       </c>
       <c r="D408" s="1" t="inlineStr">
@@ -13747,12 +13747,12 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>[tanyochwlchochy] 我回来了 (问候语)</t>
+          <t>[[tanjʌwassʌjo]] 我回来了 (问候语)</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t>tanyochwlchochy</t>
+          <t>[tanjʌwassʌjo]</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>[katmapom] 雨季 (自然)</t>
+          <t>[[tɕaŋmatɕʰʌl]] 雨季 (自然)</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t>katmapom</t>
+          <t>[tɕaŋmatɕʰʌl]</t>
         </is>
       </c>
       <c r="D419" s="1" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸʷo̞(ː)ɾa̠ŋi]] 虎式 (自然)</t>
+          <t>[[ˈɸʷo̞(ː)ɾa̠ŋi]] 老虎 (自然)</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="D435" s="1" t="inlineStr">
         <is>
-          <t>虎式 (自然)</t>
+          <t>老虎 (自然)</t>
         </is>
       </c>
       <c r="E435" s="1" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠m]] 褐色 (自然)</t>
+          <t>[[pa̠m]] 栗子 (自然)</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t>褐色 (自然)</t>
+          <t>栗子 (自然)</t>
         </is>
       </c>
       <c r="E438" s="1" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>[kangkwm] 橘子；柑橘 (自然)</t>
+          <t>[[ka̠mɡjul]] 橘子；柑橘 (自然)</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
         <is>
-          <t>kangkwm</t>
+          <t>[ka̠mɡjul]</t>
         </is>
       </c>
       <c r="D439" s="1" t="inlineStr">
@@ -14483,12 +14483,12 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t>[kikringkutchen] 国家公园 (自然)</t>
+          <t>[[kuŋlip̚ko̞ŋwʌn]] 国家公园 (自然)</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t>kikringkutchen</t>
+          <t>[kuŋlip̚ko̞ŋwʌn]</t>
         </is>
       </c>
       <c r="D440" s="1" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠ɭɡo̞na̠]] 焦糖饼干（达尔戈纳） (食物)</t>
+          <t>[[ta̠ɭɡo̞na̠]] 焦糖饼（达尔戈纳） (食物)</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t>焦糖饼干（达尔戈纳） (食物)</t>
+          <t>焦糖饼（达尔戈纳） (食物)</t>
         </is>
       </c>
       <c r="E441" s="1" t="inlineStr">
@@ -14771,12 +14771,12 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[kutatponge] 机场巴士 (旅游)</t>
+          <t>[[ko̞ŋha̠ŋbʌ̹sʰʌ̹]] 机场巴士 (旅游)</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t>kutatponge</t>
+          <t>[ko̞ŋha̠ŋbʌ̹sʰʌ̹]</t>
         </is>
       </c>
       <c r="D449" s="1" t="inlineStr">
@@ -14835,17 +14835,17 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>[pangpikingpang] 鲔鱼饭卷 (食物)</t>
+          <t>[[t͡ɕʰa̠mt͡ɕʰikimbap̚]] 金枪鱼紫菜包饭 (食物)</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
         <is>
-          <t>pangpikingpang</t>
+          <t>[t͡ɕʰa̠mt͡ɕʰikimbap̚]</t>
         </is>
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t>鲔鱼饭卷 (食物)</t>
+          <t>金枪鱼紫菜包饭 (食物)</t>
         </is>
       </c>
       <c r="E451" s="1" t="inlineStr">
@@ -15251,12 +15251,12 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>[tomchokyo] 分开 (人际关系)</t>
+          <t>[[t͈ʌ̹ɾʌ̹d͡ʑʌ̹]] 分开 (人际关系)</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
         <is>
-          <t>tomchokyo</t>
+          <t>[t͈ʌ̹ɾʌ̹d͡ʑʌ̹]</t>
         </is>
       </c>
       <c r="D464" s="1" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>[minkaata] 传简讯 (人际关系)</t>
+          <t>[[mund͡ʑaɦa̠da̠]] 传简讯 (人际关系)</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
         <is>
-          <t>minkaata</t>
+          <t>[mund͡ʑaɦa̠da̠]</t>
         </is>
       </c>
       <c r="D468" s="1" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpi(ː)miɭ]] 密钥 (人际关系)</t>
+          <t>[[ˈpi(ː)miɭ]] 秘密 (人际关系)</t>
         </is>
       </c>
       <c r="C472" s="1" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="D472" s="1" t="inlineStr">
         <is>
-          <t>密钥 (人际关系)</t>
+          <t>秘密 (人际关系)</t>
         </is>
       </c>
       <c r="E472" s="1" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ks͈o̞k̚]] 责任 (人际关系)</t>
+          <t>[[ja̠ks͈o̞k̚]] 约定 (人际关系)</t>
         </is>
       </c>
       <c r="C473" s="1" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="D473" s="1" t="inlineStr">
         <is>
-          <t>责任 (人际关系)</t>
+          <t>约定 (人际关系)</t>
         </is>
       </c>
       <c r="E473" s="1" t="inlineStr">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>[kikpimhate] 借记卡 (购物)</t>
+          <t>[[t͡ɕik̚p͈ulkʰa̠dɯ]] 借记卡 (购物)</t>
         </is>
       </c>
       <c r="C476" s="1" t="inlineStr">
         <is>
-          <t>kikpimhate</t>
+          <t>[t͡ɕik̚p͈ulkʰa̠dɯ]</t>
         </is>
       </c>
       <c r="D476" s="1" t="inlineStr">
@@ -15731,12 +15731,12 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>[konkakeingkong] 电子商店 (购物)</t>
+          <t>[[t͡ɕʌ̹nd͡ʑa̠d͡ʑepʰɯmd͡ʑʌ̹m]] 电子商店 (购物)</t>
         </is>
       </c>
       <c r="C479" s="1" t="inlineStr">
         <is>
-          <t>konkakeingkong</t>
+          <t>[t͡ɕʌ̹nd͡ʑa̠d͡ʑepʰɯmd͡ʑʌ̹m]</t>
         </is>
       </c>
       <c r="D479" s="1" t="inlineStr">
@@ -15763,12 +15763,12 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>[chyrwkong] 服装店 (购物)</t>
+          <t>[[iɾjud͡ʑʌ̹m]] 服装店 (购物)</t>
         </is>
       </c>
       <c r="C480" s="1" t="inlineStr">
         <is>
-          <t>chyrwkong</t>
+          <t>[iɾjud͡ʑʌ̹m]</t>
         </is>
       </c>
       <c r="D480" s="1" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t>[nginpamkake] |-鞋店 (购物)</t>
+          <t>[[ɕin.bal.ka.ge]] |-鞋店 (购物)</t>
         </is>
       </c>
       <c r="C481" s="1" t="inlineStr">
         <is>
-          <t>nginpamkake</t>
+          <t>[ɕin.bal.ka.ge]</t>
         </is>
       </c>
       <c r="D481" s="1" t="inlineStr">
@@ -15827,12 +15827,12 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t>[pungokkake] 珠宝店 (购物)</t>
+          <t>[[po.sʌk̚.ka.ge]] 珠宝店 (购物)</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
         <is>
-          <t>pungokkake</t>
+          <t>[po.sʌk̚.ka.ge]</t>
         </is>
       </c>
       <c r="D482" s="1" t="inlineStr">
@@ -15859,12 +15859,12 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>[chakngengori] 配饰 (购物)</t>
+          <t>[[ak̚.s͈e.sʌ.ɾi]] 配饰 (购物)</t>
         </is>
       </c>
       <c r="C483" s="1" t="inlineStr">
         <is>
-          <t>chakngengori</t>
+          <t>[ak̚.s͈e.sʌ.ɾi]</t>
         </is>
       </c>
       <c r="D483" s="1" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>[[hɛndɯbɛk̚]] 奖金 (购物)</t>
+          <t>[[hɛndɯbɛk̚]] 手提包 (购物)</t>
         </is>
       </c>
       <c r="C485" s="1" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="D485" s="1" t="inlineStr">
         <is>
-          <t>奖金 (购物)</t>
+          <t>手提包 (购物)</t>
         </is>
       </c>
       <c r="E485" s="1" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkje̞(ː)sʰa̠ndɛ]] 结账 (购物)</t>
+          <t>[[ˈkje̞(ː)sʰa̠ndɛ]] 收银台 (购物)</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="D486" s="1" t="inlineStr">
         <is>
-          <t>结账 (购物)</t>
+          <t>收银台 (购物)</t>
         </is>
       </c>
       <c r="E486" s="1" t="inlineStr">
@@ -16051,12 +16051,12 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t>[nginngating] 新品 (购物)</t>
+          <t>[[ɕin.saŋ.pʰum]] 新品 (购物)</t>
         </is>
       </c>
       <c r="C489" s="1" t="inlineStr">
         <is>
-          <t>nginngating</t>
+          <t>[ɕin.saŋ.pʰum]</t>
         </is>
       </c>
       <c r="D489" s="1" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>[katpakini] 购物车 (购物)</t>
+          <t>[[tɕaŋ.ba.gu.ni]] 购物车 (购物)</t>
         </is>
       </c>
       <c r="C490" s="1" t="inlineStr">
         <is>
-          <t>katpakini</t>
+          <t>[tɕaŋ.ba.gu.ni]</t>
         </is>
       </c>
       <c r="D490" s="1" t="inlineStr">
@@ -16115,12 +16115,12 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>[eri] 渡轮 (旅游)</t>
+          <t>[[pʰe.ɾi]] 渡轮 (旅游)</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
         <is>
-          <t>eri</t>
+          <t>[pʰe.ɾi]</t>
         </is>
       </c>
       <c r="D491" s="1" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>[[ɾe̞ntʰʌ̹kʰa̠]] 汽车租赁 (旅游)</t>
+          <t>[[ɾe̞ntʰʌ̹kʰa̠]] 租赁汽车 (旅游)</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="D493" s="1" t="inlineStr">
         <is>
-          <t>汽车租赁 (旅游)</t>
+          <t>租赁汽车 (旅游)</t>
         </is>
       </c>
       <c r="E493" s="1" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>[kungukturu] 高速公路 (旅游)</t>
+          <t>[[ko.sok̚.to.ɾo]] 高速公路 (旅游)</t>
         </is>
       </c>
       <c r="C496" s="1" t="inlineStr">
         <is>
-          <t>kungukturu</t>
+          <t>[ko.sok̚.to.ɾo]</t>
         </is>
       </c>
       <c r="D496" s="1" t="inlineStr">
@@ -16307,12 +16307,12 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>[emaahe] 主题乐园 (旅游)</t>
+          <t>[[tʰe.ma.pʰa.kʰɯ]] 主题乐园 (旅游)</t>
         </is>
       </c>
       <c r="C497" s="1" t="inlineStr">
         <is>
-          <t>emaahe</t>
+          <t>[tʰe.ma.pʰa.kʰɯ]</t>
         </is>
       </c>
       <c r="D497" s="1" t="inlineStr">
@@ -16531,12 +16531,12 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>[anchukmachem] 韩屋村 (旅游)</t>
+          <t>[[ha.noŋ.ma.ɯl]] 韩屋村 (旅游)</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
         <is>
-          <t>anchukmachem</t>
+          <t>[ha.noŋ.ma.ɯl]</t>
         </is>
       </c>
       <c r="D504" s="1" t="inlineStr">
@@ -16563,12 +16563,12 @@
       </c>
       <c r="B505" s="1" t="inlineStr">
         <is>
-          <t>[konutmachem] 传统村落 (旅游)</t>
+          <t>[[tɕʌn.toŋ.ma.ɯl]] 传统村落 (旅游)</t>
         </is>
       </c>
       <c r="C505" s="1" t="inlineStr">
         <is>
-          <t>konutmachem</t>
+          <t>[tɕʌn.toŋ.ma.ɯl]</t>
         </is>
       </c>
       <c r="D505" s="1" t="inlineStr">
@@ -16691,12 +16691,12 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>[kemremoit] 豪华露营 (旅游)</t>
+          <t>[[kɯl.le.mʌ.pʰiŋ]] 豪华露营 (旅游)</t>
         </is>
       </c>
       <c r="C509" s="1" t="inlineStr">
         <is>
-          <t>kemremoit</t>
+          <t>[kɯl.le.mʌ.pʰiŋ]</t>
         </is>
       </c>
       <c r="D509" s="1" t="inlineStr">
@@ -16755,12 +16755,12 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>[chechopichenpi] 爱彼迎；Airbnb民宿 (명사)</t>
+          <t>[[ɛːʌbiɛnbi]] 爱彼迎；Airbnb民宿 (명사)</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
         <is>
-          <t>chechopichenpi</t>
+          <t>[ɛːʌbiɛnbi]</t>
         </is>
       </c>
       <c r="D511" s="1" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>[honngichoki] 礼宾部 (旅游)</t>
+          <t>[[kʰʌnɕʰiʌdʑi]] 礼宾部 (旅游)</t>
         </is>
       </c>
       <c r="C515" s="1" t="inlineStr">
         <is>
-          <t>honngichoki</t>
+          <t>[kʰʌnɕʰiʌdʑi]</t>
         </is>
       </c>
       <c r="D515" s="1" t="inlineStr">
@@ -16915,12 +16915,12 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>[pempuchi] 行李员 (旅游)</t>
+          <t>[[pɛlboi]] 行李员 (旅游)</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
         <is>
-          <t>pempuchi</t>
+          <t>[pɛlboi]</t>
         </is>
       </c>
       <c r="D516" s="1" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕimk͈un]] 搬运行李人员 (旅游)</t>
+          <t>[[t͡ɕimk͈un]] 搬运工；行李搬运夫 (旅游)</t>
         </is>
       </c>
       <c r="C517" s="1" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="D517" s="1" t="inlineStr">
         <is>
-          <t>搬运行李人员 (旅游)</t>
+          <t>搬运工；行李搬运夫 (旅游)</t>
         </is>
       </c>
       <c r="E517" s="1" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>[[muɭk͈o̞ɡi]] 鱼肉 (动物)</t>
+          <t>[[muɭk͈o̞ɡi]] 鱼 (动物)</t>
         </is>
       </c>
       <c r="C525" s="1" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="D525" s="1" t="inlineStr">
         <is>
-          <t>鱼肉 (动物)</t>
+          <t>鱼 (动物)</t>
         </is>
       </c>
       <c r="E525" s="1" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="B612" s="1" t="inlineStr">
         <is>
-          <t>[[cçi]] 飞行高度 (身体部位)</t>
+          <t>[[cçi]] 身高 (身体部位)</t>
         </is>
       </c>
       <c r="C612" s="1" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="D612" s="1" t="inlineStr">
         <is>
-          <t>飞行高度 (身体部位)</t>
+          <t>身高 (身体部位)</t>
         </is>
       </c>
       <c r="E612" s="1" t="inlineStr">
@@ -20051,12 +20051,12 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>[namcinan] 修 身 (身体部位)</t>
+          <t>[[naɭɕ͈inɦan]] 修 身 (身体部位)</t>
         </is>
       </c>
       <c r="C614" s="1" t="inlineStr">
         <is>
-          <t>namcinan</t>
+          <t>[naɭɕ͈inɦan]</t>
         </is>
       </c>
       <c r="D614" s="1" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>[ututan] 肉嘟嘟 (身体部位)</t>
+          <t>[[tʰoŋtʰoŋɦan]] 肉嘟嘟 (身体部位)</t>
         </is>
       </c>
       <c r="C615" s="1" t="inlineStr">
         <is>
-          <t>ututan</t>
+          <t>[tʰoŋtʰoŋɦan]</t>
         </is>
       </c>
       <c r="D615" s="1" t="inlineStr">
@@ -20211,12 +20211,12 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>[kiwt] 橙色 (颜色和形状)</t>
+          <t>[[t͡ɕuɦwaŋ]] 橙色 (颜色和形状)</t>
         </is>
       </c>
       <c r="C619" s="1" t="inlineStr">
         <is>
-          <t>kiwt</t>
+          <t>[t͡ɕuɦwaŋ]</t>
         </is>
       </c>
       <c r="D619" s="1" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="B627" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞sʰɛk̚]] 布赖 (颜色与形状)</t>
+          <t>[[ɸwe̞sʰɛk̚]] 灰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C627" s="1" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="D627" s="1" t="inlineStr">
         <is>
-          <t>布赖 (颜色与形状)</t>
+          <t>灰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E627" s="1" t="inlineStr">
@@ -20531,12 +20531,12 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>[pechiki] 米色 (颜色与形状)</t>
+          <t>[[pe̞id͡ʑi]] 米色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C629" s="1" t="inlineStr">
         <is>
-          <t>pechiki</t>
+          <t>[pe̞id͡ʑi]</t>
         </is>
       </c>
       <c r="D629" s="1" t="inlineStr">
@@ -20563,12 +20563,12 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>[nechipi] 藏青色 (颜色与形状)</t>
+          <t>[[ne̞ibi]] 藏青色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C630" s="1" t="inlineStr">
         <is>
-          <t>nechipi</t>
+          <t>[ne̞ibi]</t>
         </is>
       </c>
       <c r="D630" s="1" t="inlineStr">
@@ -21107,17 +21107,17 @@
       </c>
       <c r="B647" s="1" t="inlineStr">
         <is>
-          <t>[titken] 圆形 (颜色与形状)</t>
+          <t>[[tuŋɡɯn]] 圆的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C647" s="1" t="inlineStr">
         <is>
-          <t>titken</t>
+          <t>[tuŋɡɯn]</t>
         </is>
       </c>
       <c r="D647" s="1" t="inlineStr">
         <is>
-          <t>圆形 (颜色与形状)</t>
+          <t>圆的 (颜色与形状)</t>
         </is>
       </c>
       <c r="E647" s="1" t="inlineStr">
@@ -21139,12 +21139,12 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>[yotyotan] 平坦 (颜色与形状)</t>
+          <t>[[pʰjʌ̹mpʰjo̞pʰa̠n]] 平坦 (颜色与形状)</t>
         </is>
       </c>
       <c r="C648" s="1" t="inlineStr">
         <is>
-          <t>yotyotan</t>
+          <t>[pʰjʌ̹mpʰjo̞pʰa̠n]</t>
         </is>
       </c>
       <c r="D648" s="1" t="inlineStr">
@@ -21299,12 +21299,12 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>[nolchen] 宽的 (颜色与形状)</t>
+          <t>[[nʌ̹lbɯn]] 宽的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
         <is>
-          <t>nolchen</t>
+          <t>[nʌ̹lbɯn]</t>
         </is>
       </c>
       <c r="D653" s="1" t="inlineStr">
@@ -21331,12 +21331,12 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>[kungchen] 窄的 (颜色与形状)</t>
+          <t>[[t͡ɕa̠pɯn]] 窄的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C654" s="1" t="inlineStr">
         <is>
-          <t>kungchen</t>
+          <t>[t͡ɕa̠pɯn]</t>
         </is>
       </c>
       <c r="D654" s="1" t="inlineStr">
@@ -21395,12 +21395,12 @@
       </c>
       <c r="B656" s="1" t="inlineStr">
         <is>
-          <t>[talchen] 短的 (颜色与形状)</t>
+          <t>[[t͈a̠lbɯn]] 短的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C656" s="1" t="inlineStr">
         <is>
-          <t>talchen</t>
+          <t>[t͈a̠lbɯn]</t>
         </is>
       </c>
       <c r="D656" s="1" t="inlineStr">
@@ -21427,12 +21427,12 @@
       </c>
       <c r="B657" s="1" t="inlineStr">
         <is>
-          <t>[nuchen] 高的 (颜色与形状)</t>
+          <t>[[noːpʰɯn]] 高的 (颜色与形状)</t>
         </is>
       </c>
       <c r="C657" s="1" t="inlineStr">
         <is>
-          <t>nuchen</t>
+          <t>[noːpʰɯn]</t>
         </is>
       </c>
       <c r="D657" s="1" t="inlineStr">
@@ -21459,12 +21459,12 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>[[muni]] 图案 (颜色与形状)</t>
+          <t>[[muɲi]] 图案 (颜色与形状)</t>
         </is>
       </c>
       <c r="C658" s="1" t="inlineStr">
         <is>
-          <t>[muni]</t>
+          <t>[muɲi]</t>
         </is>
       </c>
       <c r="D658" s="1" t="inlineStr">
@@ -21875,12 +21875,12 @@
       </c>
       <c r="B671" s="1" t="inlineStr">
         <is>
-          <t>[chyoman] 十一 (数字与时间)</t>
+          <t>[[jʌ̹ɾan]] 十一 (数字与时间)</t>
         </is>
       </c>
       <c r="C671" s="1" t="inlineStr">
         <is>
-          <t>chyoman</t>
+          <t>[jʌ̹ɾan]</t>
         </is>
       </c>
       <c r="D671" s="1" t="inlineStr">
@@ -21907,12 +21907,12 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>[chyomti] 十二 (数字与时间)</t>
+          <t>[[jʌ̹du]] 十二 (数字与时间)</t>
         </is>
       </c>
       <c r="C672" s="1" t="inlineStr">
         <is>
-          <t>chyomti</t>
+          <t>[jʌ̹du]</t>
         </is>
       </c>
       <c r="D672" s="1" t="inlineStr">
@@ -22835,12 +22835,12 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>[nakitche] 稍后 (数字与时间)</t>
+          <t>[[nadʑuŋe]] 稍后 (数字与时间)</t>
         </is>
       </c>
       <c r="C701" s="1" t="inlineStr">
         <is>
-          <t>nakitche</t>
+          <t>[nadʑuŋe]</t>
         </is>
       </c>
       <c r="D701" s="1" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="B703" s="1" t="inlineStr">
         <is>
-          <t>[konche] 之前 (数字与时间)</t>
+          <t>[[t͡ɕʌne]] 之前 (数字与时间)</t>
         </is>
       </c>
       <c r="C703" s="1" t="inlineStr">
         <is>
-          <t>konche</t>
+          <t>[t͡ɕʌne]</t>
         </is>
       </c>
       <c r="D703" s="1" t="inlineStr">
@@ -22931,12 +22931,12 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>[iche] 之后 (数字与时间)</t>
+          <t>[[ɸue]] 之后 (数字与时间)</t>
         </is>
       </c>
       <c r="C704" s="1" t="inlineStr">
         <is>
-          <t>iche</t>
+          <t>[ɸue]</t>
         </is>
       </c>
       <c r="D704" s="1" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="B706" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ɭt͈ɛ]] 从不 (数字与时间)</t>
+          <t>[[t͡ɕʌ̹ɭt͈ɛ]] 绝对 (数字与时间)</t>
         </is>
       </c>
       <c r="C706" s="1" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="D706" s="1" t="inlineStr">
         <is>
-          <t>从不 (数字与时间)</t>
+          <t>绝对 (数字与时间)</t>
         </is>
       </c>
       <c r="E706" s="1" t="inlineStr">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>[pwikenche] 最近 (数字与时间)</t>
+          <t>[[t͡ɕʰøɡɯne]] 最近 (数字与时间)</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
         <is>
-          <t>pwikenche</t>
+          <t>[t͡ɕʰøɡɯne]</t>
         </is>
       </c>
       <c r="D709" s="1" t="inlineStr">
@@ -23251,12 +23251,12 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>[nepke] 晚 (数字与时间)</t>
+          <t>[[nɯt̚k͈e]] 晚 (数字与时间)</t>
         </is>
       </c>
       <c r="C714" s="1" t="inlineStr">
         <is>
-          <t>nepke</t>
+          <t>[nɯt̚k͈e]</t>
         </is>
       </c>
       <c r="D714" s="1" t="inlineStr">
@@ -23763,12 +23763,12 @@
       </c>
       <c r="B730" s="1" t="inlineStr">
         <is>
-          <t>[kykang] 副校长 (校园生活)</t>
+          <t>[[kjoŋam]] 副校长 (校园生活)</t>
         </is>
       </c>
       <c r="C730" s="1" t="inlineStr">
         <is>
-          <t>kykang</t>
+          <t>[kjoŋam]</t>
         </is>
       </c>
       <c r="D730" s="1" t="inlineStr">
@@ -23795,12 +23795,12 @@
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>[tangchingngonngetning] 级任老师 (校园生活)</t>
+          <t>[[tamimsʰʌnsʰɛŋɲim]] 级任老师 (校园生活)</t>
         </is>
       </c>
       <c r="C731" s="1" t="inlineStr">
         <is>
-          <t>tangchingngonngetning</t>
+          <t>[tamimsʰʌnsʰɛŋɲim]</t>
         </is>
       </c>
       <c r="D731" s="1" t="inlineStr">
@@ -23827,12 +23827,12 @@
       </c>
       <c r="B732" s="1" t="inlineStr">
         <is>
-          <t>[kwmukngonngetning] 科目老师 (校园生活)</t>
+          <t>[[kwamoksʰʌnsʰɛŋɲim]] 科目老师 (校园生活)</t>
         </is>
       </c>
       <c r="C732" s="1" t="inlineStr">
         <is>
-          <t>kwmukngonngetning</t>
+          <t>[kwamoksʰʌnsʰɛŋɲim]</t>
         </is>
       </c>
       <c r="D732" s="1" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="B735" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpɛ(ː)na̠ŋ]] 书包 (校园生活)</t>
+          <t>[[ˈpɛ(ː)na̠ŋ]] 背包 (校园生活)</t>
         </is>
       </c>
       <c r="C735" s="1" t="inlineStr">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="D735" s="1" t="inlineStr">
         <is>
-          <t>书包 (校园生活)</t>
+          <t>背包 (校园生活)</t>
         </is>
       </c>
       <c r="E735" s="1" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ɭs͈ʌ̹k̚]] 无 (校园生活)</t>
+          <t>[[kjʌ̹ɭs͈ʌ̹k̚]] 缺席 (校园生活)</t>
         </is>
       </c>
       <c r="C741" s="1" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="D741" s="1" t="inlineStr">
         <is>
-          <t>无 (校园生活)</t>
+          <t>缺席 (校园生活)</t>
         </is>
       </c>
       <c r="E741" s="1" t="inlineStr">
@@ -24179,12 +24179,12 @@
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>[malchen] 晴 (天气)</t>
+          <t>[[maɭɡɯn]] 晴 (天气)</t>
         </is>
       </c>
       <c r="C743" s="1" t="inlineStr">
         <is>
-          <t>malchen</t>
+          <t>[maɭɡɯn]</t>
         </is>
       </c>
       <c r="D743" s="1" t="inlineStr">
@@ -24211,12 +24211,12 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>[erin] 阴的；阴沉的；模糊的 (형용사)</t>
+          <t>[[ɸɯɾin]] 阴的；阴沉的；模糊的 (형용사)</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
         <is>
-          <t>erin</t>
+          <t>[ɸɯɾin]</t>
         </is>
       </c>
       <c r="D744" s="1" t="inlineStr">
@@ -24243,17 +24243,17 @@
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t>[pichunen] 多雨 (天气)</t>
+          <t>[[pi.onɯn]] 下雨的 (天气)</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
         <is>
-          <t>pichunen</t>
+          <t>[pi.onɯn]</t>
         </is>
       </c>
       <c r="D745" s="1" t="inlineStr">
         <is>
-          <t>多雨 (天气)</t>
+          <t>下雨的 (天气)</t>
         </is>
       </c>
       <c r="E745" s="1" t="inlineStr">
@@ -24275,12 +24275,12 @@
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t>[ngengan] 湿气重的 (天气)</t>
+          <t>[[sɯpʰan]] 湿气重的 (天气)</t>
         </is>
       </c>
       <c r="C746" s="1" t="inlineStr">
         <is>
-          <t>ngengan</t>
+          <t>[sɯpʰan]</t>
         </is>
       </c>
       <c r="D746" s="1" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t>[konkuan] 干燥的 (天气)</t>
+          <t>[[kʌnd͡ʑoɦan]] 干燥的 (天气)</t>
         </is>
       </c>
       <c r="C747" s="1" t="inlineStr">
         <is>
-          <t>konkuan</t>
+          <t>[kʌnd͡ʑoɦan]</t>
         </is>
       </c>
       <c r="D747" s="1" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtɘ(ː)p̚t͈a̠]] 热门 (天气)</t>
+          <t>[[ˈtɘ(ː)p̚t͈a̠]] 炎热 (天气)</t>
         </is>
       </c>
       <c r="C748" s="1" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="D748" s="1" t="inlineStr">
         <is>
-          <t>热门 (天气)</t>
+          <t>炎热 (天气)</t>
         </is>
       </c>
       <c r="E748" s="1" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>[ngichenan] 凉爽 (天气)</t>
+          <t>[[ɕiwʌnɦan]] 凉爽 (天气)</t>
         </is>
       </c>
       <c r="C750" s="1" t="inlineStr">
         <is>
-          <t>ngichenan</t>
+          <t>[ɕiwʌnɦan]</t>
         </is>
       </c>
       <c r="D750" s="1" t="inlineStr">
@@ -24595,12 +24595,12 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>[rechinhue] 雨衣 (天气)</t>
+          <t>[[ɾe̞inkʰo̞tʰɯ]] 雨衣 (天气)</t>
         </is>
       </c>
       <c r="C756" s="1" t="inlineStr">
         <is>
-          <t>rechinhue</t>
+          <t>[ɾe̞inkʰo̞tʰɯ]</t>
         </is>
       </c>
       <c r="D756" s="1" t="inlineStr">
@@ -24755,12 +24755,12 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>[netpat] 冷却 (天气)</t>
+          <t>[[nɛŋpa̠ŋ]] 冷却 (天气)</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
         <is>
-          <t>netpat</t>
+          <t>[nɛŋpa̠ŋ]</t>
         </is>
       </c>
       <c r="D761" s="1" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>[[tɯɾe̞s͈ɯ]] 衣着 (服饰)</t>
+          <t>[[tɯɾe̞s͈ɯ]] 连衣裙 (服饰)</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="D768" s="1" t="inlineStr">
         <is>
-          <t>衣着 (服饰)</t>
+          <t>连衣裙 (服饰)</t>
         </is>
       </c>
       <c r="E768" s="1" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="B769" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯkʰʌ̹tʰɯ]] 裙摆 (服饰)</t>
+          <t>[[sʰɯkʰʌ̹tʰɯ]] 裙子 (服饰)</t>
         </is>
       </c>
       <c r="C769" s="1" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="D769" s="1" t="inlineStr">
         <is>
-          <t>裙摆 (服饰)</t>
+          <t>裙子 (服饰)</t>
         </is>
       </c>
       <c r="E769" s="1" t="inlineStr">
@@ -25235,12 +25235,12 @@
       </c>
       <c r="B776" s="1" t="inlineStr">
         <is>
-          <t>[aha] 派克大衣 (服饰)</t>
+          <t>[[pʰa̠kʰa̠]] 派克大衣 (服饰)</t>
         </is>
       </c>
       <c r="C776" s="1" t="inlineStr">
         <is>
-          <t>aha</t>
+          <t>[pʰa̠kʰa̠]</t>
         </is>
       </c>
       <c r="D776" s="1" t="inlineStr">
@@ -25331,12 +25331,12 @@
       </c>
       <c r="B779" s="1" t="inlineStr">
         <is>
-          <t>[itei] 连帽衫 (服饰)</t>
+          <t>[[hudɯtʰi]] 连帽衫 (服饰)</t>
         </is>
       </c>
       <c r="C779" s="1" t="inlineStr">
         <is>
-          <t>itei</t>
+          <t>[hudɯtʰi]</t>
         </is>
       </c>
       <c r="D779" s="1" t="inlineStr">
@@ -25363,12 +25363,12 @@
       </c>
       <c r="B780" s="1" t="inlineStr">
         <is>
-          <t>[menimen] 运动衫 (服饰)</t>
+          <t>[[mɛntʰumɛn]] 运动衫 (服饰)</t>
         </is>
       </c>
       <c r="C780" s="1" t="inlineStr">
         <is>
-          <t>menimen</t>
+          <t>[mɛntʰumɛn]</t>
         </is>
       </c>
       <c r="D780" s="1" t="inlineStr">
@@ -25779,12 +25779,12 @@
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
-          <t>[[pini]] 毛帽 (服饰)</t>
+          <t>[[piɲi]] 毛帽 (服饰)</t>
         </is>
       </c>
       <c r="C793" s="1" t="inlineStr">
         <is>
-          <t>[pini]</t>
+          <t>[piɲi]</t>
         </is>
       </c>
       <c r="D793" s="1" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>[hekichompuk] 休闲服 (服饰)</t>
+          <t>[[kʰɛt͡ɕwa̠ɭbok̚]] 休闲服 (服饰)</t>
         </is>
       </c>
       <c r="C803" s="1" t="inlineStr">
         <is>
-          <t>hekichompuk</t>
+          <t>[kʰɛt͡ɕwa̠ɭbok̚]</t>
         </is>
       </c>
       <c r="D803" s="1" t="inlineStr">
@@ -26259,12 +26259,12 @@
       </c>
       <c r="B808" s="1" t="inlineStr">
         <is>
-          <t>[tanngek] 纯色 (服装)</t>
+          <t>[[ta̠ns͈ɛk̚]] 纯色 (服装)</t>
         </is>
       </c>
       <c r="C808" s="1" t="inlineStr">
         <is>
-          <t>tanngek</t>
+          <t>[ta̠ns͈ɛk̚]</t>
         </is>
       </c>
       <c r="D808" s="1" t="inlineStr">
@@ -26323,12 +26323,12 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>[pukungicho] 我好想你 (韩剧表达)</t>
+          <t>[[po̞ɡo̞ɕipʰʌ̹]] 我好想你 (韩剧表达)</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
         <is>
-          <t>pukungicho</t>
+          <t>[po̞ɡo̞ɕipʰʌ̹]</t>
         </is>
       </c>
       <c r="D810" s="1" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>[michane] 对不起 (韩剧表达)</t>
+          <t>[[mianɛ]] 对不起 (韩剧表达)</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
         <is>
-          <t>michane</t>
+          <t>[mianɛ]</t>
         </is>
       </c>
       <c r="D811" s="1" t="inlineStr">
@@ -26387,12 +26387,12 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>[kwenpalcha] 没关系 (韩剧表达)</t>
+          <t>[[kwɛnt͡ɕʰana]] 没关系 (韩剧表达)</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
         <is>
-          <t>kwenpalcha</t>
+          <t>[kwɛnt͡ɕʰana]</t>
         </is>
       </c>
       <c r="D812" s="1" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B814" s="1" t="inlineStr">
         <is>
-          <t>[[a̠iɡo̞]] 诶 (韩剧表达)</t>
+          <t>[[a̠iɡo̞]] 哎呀 (韩剧表达)</t>
         </is>
       </c>
       <c r="C814" s="1" t="inlineStr">
@@ -26461,7 +26461,7 @@
       </c>
       <c r="D814" s="1" t="inlineStr">
         <is>
-          <t>诶 (韩剧表达)</t>
+          <t>哎呀 (韩剧表达)</t>
         </is>
       </c>
       <c r="E814" s="1" t="inlineStr">
@@ -26483,12 +26483,12 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>[chachiki] 哎哟；哎呀 (韩剧表达)</t>
+          <t>[[aːiɡu]] 哎哟；哎呀 (韩剧表达)</t>
         </is>
       </c>
       <c r="C815" s="1" t="inlineStr">
         <is>
-          <t>chachiki</t>
+          <t>[aːiɡu]</t>
         </is>
       </c>
       <c r="D815" s="1" t="inlineStr">
@@ -26515,7 +26515,7 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠itʰiŋ]] 争夺中 (韩剧表达)</t>
+          <t>[[ɸwa̠itʰiŋ]] 加油 (韩剧表达)</t>
         </is>
       </c>
       <c r="C816" s="1" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="D816" s="1" t="inlineStr">
         <is>
-          <t>争夺中 (韩剧表达)</t>
+          <t>加油 (韩剧表达)</t>
         </is>
       </c>
       <c r="E816" s="1" t="inlineStr">
@@ -26611,12 +26611,12 @@
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>[chantwe] 不该做的事 (韩剧表达)</t>
+          <t>[[anːdwɛ]] 不该做的事 (韩剧表达)</t>
         </is>
       </c>
       <c r="C819" s="1" t="inlineStr">
         <is>
-          <t>chantwe</t>
+          <t>[anːdwɛ]</t>
         </is>
       </c>
       <c r="D819" s="1" t="inlineStr">
@@ -26707,17 +26707,17 @@
       </c>
       <c r="B822" s="1" t="inlineStr">
         <is>
-          <t>[matchilcho] 好好喝哦 (韩剧表达)</t>
+          <t>[[maɕin͈ʌ]] 好吃 (韩剧表达)</t>
         </is>
       </c>
       <c r="C822" s="1" t="inlineStr">
         <is>
-          <t>matchilcho</t>
+          <t>[maɕin͈ʌ]</t>
         </is>
       </c>
       <c r="D822" s="1" t="inlineStr">
         <is>
-          <t>好好喝哦 (韩剧表达)</t>
+          <t>好吃 (韩剧表达)</t>
         </is>
       </c>
       <c r="E822" s="1" t="inlineStr">
@@ -26739,17 +26739,17 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>[chyeso] 相当 (韩剧表达)</t>
+          <t>[[jep͈ʌ]] 漂亮 (韩剧表达)</t>
         </is>
       </c>
       <c r="C823" s="1" t="inlineStr">
         <is>
-          <t>chyeso</t>
+          <t>[jep͈ʌ]</t>
         </is>
       </c>
       <c r="D823" s="1" t="inlineStr">
         <is>
-          <t>相当 (韩剧表达)</t>
+          <t>漂亮 (韩剧表达)</t>
         </is>
       </c>
       <c r="E823" s="1" t="inlineStr">
@@ -26771,12 +26771,12 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>[kamngetkyolcho] 帅醒 (韩剧表达)</t>
+          <t>[[t͡ɕals͈aŋɡjʌs͈ʌ]] 帅醒 (韩剧表达)</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
         <is>
-          <t>kamngetkyolcho</t>
+          <t>[t͡ɕals͈aŋɡjʌs͈ʌ]</t>
         </is>
       </c>
       <c r="D824" s="1" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞k͈i]] 授予 (服装)</t>
+          <t>[[t͡ɕo̞k͈i]] 背心 (服装)</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>授予 (服装)</t>
+          <t>背心 (服装)</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
@@ -26963,12 +26963,12 @@
       </c>
       <c r="B830" s="1" t="inlineStr">
         <is>
-          <t>[imyotan] 透明 (颜色形状)</t>
+          <t>[[tʰuːmjʌŋɦan]] 透明 (颜色形状)</t>
         </is>
       </c>
       <c r="C830" s="1" t="inlineStr">
         <is>
-          <t>imyotan</t>
+          <t>[tʰuːmjʌŋɦan]</t>
         </is>
       </c>
       <c r="D830" s="1" t="inlineStr">
@@ -26995,7 +26995,7 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>[[ɸʷo̞ɭs͈u]] 奇数和偶数 (数字与时间)</t>
+          <t>[[ɸʷo̞ɭs͈u]] 奇数 (数字与时间)</t>
         </is>
       </c>
       <c r="C831" s="1" t="inlineStr">
@@ -27005,7 +27005,7 @@
       </c>
       <c r="D831" s="1" t="inlineStr">
         <is>
-          <t>奇数和偶数 (数字与时间)</t>
+          <t>奇数 (数字与时间)</t>
         </is>
       </c>
       <c r="E831" s="1" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕ͈a̠ks͈u]] 奇数和偶数 (数字与时间)</t>
+          <t>[[t͡ɕ͈a̠ks͈u]] 偶数 (数字与时间)</t>
         </is>
       </c>
       <c r="C832" s="1" t="inlineStr">
@@ -27037,7 +27037,7 @@
       </c>
       <c r="D832" s="1" t="inlineStr">
         <is>
-          <t>奇数和偶数 (数字与时间)</t>
+          <t>偶数 (数字与时间)</t>
         </is>
       </c>
       <c r="E832" s="1" t="inlineStr">
@@ -27123,12 +27123,12 @@
       </c>
       <c r="B835" s="1" t="inlineStr">
         <is>
-          <t>[hachinetachin] 倒计时 (数字与时间)</t>
+          <t>[[kʰauntʰdaun]] 倒计时 (数字与时间)</t>
         </is>
       </c>
       <c r="C835" s="1" t="inlineStr">
         <is>
-          <t>hachinetachin</t>
+          <t>[kʰauntʰdaun]</t>
         </is>
       </c>
       <c r="D835" s="1" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>[[sʰo̞na̠ɡi]] 突然淋浴 (天气)</t>
+          <t>[[sʰo̞na̠ɡi]] 阵雨 (天气)</t>
         </is>
       </c>
       <c r="C836" s="1" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="D836" s="1" t="inlineStr">
         <is>
-          <t>突然淋浴 (天气)</t>
+          <t>阵雨 (天气)</t>
         </is>
       </c>
       <c r="E836" s="1" t="inlineStr">
@@ -27251,12 +27251,12 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>[malcheng] 晴朗天气 (天气)</t>
+          <t>[[maɾɡɯm]] 晴朗天气 (天气)</t>
         </is>
       </c>
       <c r="C839" s="1" t="inlineStr">
         <is>
-          <t>malcheng</t>
+          <t>[maɾɡɯm]</t>
         </is>
       </c>
       <c r="D839" s="1" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>[kotkwkik] 全职 (商业)</t>
+          <t>[[t͡ɕʌ̹ŋɡjɯd͡ʑik̚]] 全职 (商业)</t>
         </is>
       </c>
       <c r="C846" s="1" t="inlineStr">
         <is>
-          <t>kotkwkik</t>
+          <t>[t͡ɕʌ̹ŋɡjɯd͡ʑik̚]</t>
         </is>
       </c>
       <c r="D846" s="1" t="inlineStr">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="B847" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɛ(ː)tʰɛk̚k͈ɯnmu]] 远端工作 (商业)</t>
+          <t>[[ˈt͡ɕɛ(ː)tʰɛk̚k͈ɯnmu]] 在家办公 (商业)</t>
         </is>
       </c>
       <c r="C847" s="1" t="inlineStr">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="D847" s="1" t="inlineStr">
         <is>
-          <t>远端工作 (商业)</t>
+          <t>在家办公 (商业)</t>
         </is>
       </c>
       <c r="E847" s="1" t="inlineStr">
@@ -27731,12 +27731,12 @@
       </c>
       <c r="B854" s="1" t="inlineStr">
         <is>
-          <t>[chyonpa] 年假 (商业)</t>
+          <t>[[jʌ̹nt͡ɕʰa̠]] 年假 (商业)</t>
         </is>
       </c>
       <c r="C854" s="1" t="inlineStr">
         <is>
-          <t>chyonpa</t>
+          <t>[jʌ̹nt͡ɕʰa̠]</t>
         </is>
       </c>
       <c r="D854" s="1" t="inlineStr">
@@ -27795,7 +27795,7 @@
       </c>
       <c r="B856" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕit͡ɕʰuɭ]] 费用 (商业)</t>
+          <t>[[t͡ɕit͡ɕʰuɭ]] 支出 (商业)</t>
         </is>
       </c>
       <c r="C856" s="1" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="D856" s="1" t="inlineStr">
         <is>
-          <t>费用 (商业)</t>
+          <t>支出 (商业)</t>
         </is>
       </c>
       <c r="E856" s="1" t="inlineStr">
@@ -27859,12 +27859,12 @@
       </c>
       <c r="B858" s="1" t="inlineStr">
         <is>
-          <t>[ngeaechong] 新创公司 (商业)</t>
+          <t>[[sʰɯtʰa̠tʰɯʌ̹p̚]] 新创公司 (商业)</t>
         </is>
       </c>
       <c r="C858" s="1" t="inlineStr">
         <is>
-          <t>ngeaechong</t>
+          <t>[sʰɯtʰa̠tʰɯʌ̹p̚]</t>
         </is>
       </c>
       <c r="D858" s="1" t="inlineStr">
@@ -28019,12 +28019,12 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>[hemrachichone] 客户 (商业)</t>
+          <t>[[kʰɯɭɭa.iʌ̹ntʰɯ]] 客户 (商业)</t>
         </is>
       </c>
       <c r="C863" s="1" t="inlineStr">
         <is>
-          <t>hemrachichone</t>
+          <t>[kʰɯɭɭa.iʌ̹ntʰɯ]</t>
         </is>
       </c>
       <c r="D863" s="1" t="inlineStr">
@@ -28051,17 +28051,17 @@
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
-          <t>[pwikukyotchyotka] 执行长 (商业)</t>
+          <t>[[t͡ɕʰwe̞ɡo̞kjʌ̹ŋjʌ̹d͡ʑa̠]] 首席执行官 (商业)</t>
         </is>
       </c>
       <c r="C864" s="1" t="inlineStr">
         <is>
-          <t>pwikukyotchyotka</t>
+          <t>[t͡ɕʰwe̞ɡo̞kjʌ̹ŋjʌ̹d͡ʑa̠]</t>
         </is>
       </c>
       <c r="D864" s="1" t="inlineStr">
         <is>
-          <t>执行长 (商业)</t>
+          <t>首席执行官 (商业)</t>
         </is>
       </c>
       <c r="E864" s="1" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠ʎʎid͡ʑa̠]] 经理 (商业)</t>
+          <t>[[kwa̠ʎʎid͡ʑa̠]] 管理者 (商业)</t>
         </is>
       </c>
       <c r="C865" s="1" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="D865" s="1" t="inlineStr">
         <is>
-          <t>经理 (商业)</t>
+          <t>管理者 (商业)</t>
         </is>
       </c>
       <c r="E865" s="1" t="inlineStr">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="B867" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkjo(ː)juk̚]] 培训 (商业)</t>
+          <t>[[ˈkjo(ː)juk̚]] 教育 (商业)</t>
         </is>
       </c>
       <c r="C867" s="1" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="D867" s="1" t="inlineStr">
         <is>
-          <t>培训 (商业)</t>
+          <t>教育 (商业)</t>
         </is>
       </c>
       <c r="E867" s="1" t="inlineStr">
@@ -28211,12 +28211,12 @@
       </c>
       <c r="B869" s="1" t="inlineStr">
         <is>
-          <t>[kikita] 平锅煎 (烹饪)</t>
+          <t>[[t͡ɕid͡ʑida̠]] 平锅煎 (烹饪)</t>
         </is>
       </c>
       <c r="C869" s="1" t="inlineStr">
         <is>
-          <t>kikita</t>
+          <t>[t͡ɕid͡ʑida̠]</t>
         </is>
       </c>
       <c r="D869" s="1" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ɾɯda̠]] 哐啷 (烹饪)</t>
+          <t>[[t͡ɕa̠ɾɯda̠]] 切 (烹饪)</t>
         </is>
       </c>
       <c r="C871" s="1" t="inlineStr">
@@ -28285,7 +28285,7 @@
       </c>
       <c r="D871" s="1" t="inlineStr">
         <is>
-          <t>哐啷 (烹饪)</t>
+          <t>切 (烹饪)</t>
         </is>
       </c>
       <c r="E871" s="1" t="inlineStr">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹mida̠]] 扇面 (烹饪)</t>
+          <t>[[t͡ɕʌ̹mida̠]] 切片 (烹饪)</t>
         </is>
       </c>
       <c r="C872" s="1" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="D872" s="1" t="inlineStr">
         <is>
-          <t>扇面 (烹饪)</t>
+          <t>切片 (烹饪)</t>
         </is>
       </c>
       <c r="E872" s="1" t="inlineStr">
@@ -28339,17 +28339,17 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>[kaktikcomkiata] 骰子 (烹饪)</t>
+          <t>[[kkaŋtuks͈ʌlɡiɦada]] 切丁 (烹饪)</t>
         </is>
       </c>
       <c r="C873" s="1" t="inlineStr">
         <is>
-          <t>kaktikcomkiata</t>
+          <t>[kkaŋtuks͈ʌlɡiɦada]</t>
         </is>
       </c>
       <c r="D873" s="1" t="inlineStr">
         <is>
-          <t>骰子 (烹饪)</t>
+          <t>切丁 (烹饪)</t>
         </is>
       </c>
       <c r="E873" s="1" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="B877" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)t̚t͈a̠]] 雨 (烹饪)</t>
+          <t>[[ˈpu(ː)t̚t͈a̠]] 倒入 (烹饪)</t>
         </is>
       </c>
       <c r="C877" s="1" t="inlineStr">
@@ -28477,7 +28477,7 @@
       </c>
       <c r="D877" s="1" t="inlineStr">
         <is>
-          <t>雨 (烹饪)</t>
+          <t>倒入 (烹饪)</t>
         </is>
       </c>
       <c r="E877" s="1" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>[[kʌ̹ɾɯda̠]] 菌株 (烹饪)</t>
+          <t>[[kʌ̹ɾɯda̠]] 过滤 (烹饪)</t>
         </is>
       </c>
       <c r="C878" s="1" t="inlineStr">
@@ -28509,7 +28509,7 @@
       </c>
       <c r="D878" s="1" t="inlineStr">
         <is>
-          <t>菌株 (烹饪)</t>
+          <t>过滤 (烹饪)</t>
         </is>
       </c>
       <c r="E878" s="1" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>[[ˈnu(ː)ɾɯda̠]] 压力机 (烹饪)</t>
+          <t>[[ˈnu(ː)ɾɯda̠]] 按压 (烹饪)</t>
         </is>
       </c>
       <c r="C879" s="1" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
-          <t>压力机 (烹饪)</t>
+          <t>按压 (烹饪)</t>
         </is>
       </c>
       <c r="E879" s="1" t="inlineStr">
@@ -28595,12 +28595,12 @@
       </c>
       <c r="B881" s="1" t="inlineStr">
         <is>
-          <t>[etkimta] 冲洗 (烹饪)</t>
+          <t>[[he̞ŋɡulda̠]] 冲洗 (烹饪)</t>
         </is>
       </c>
       <c r="C881" s="1" t="inlineStr">
         <is>
-          <t>etkimta</t>
+          <t>[he̞ŋɡulda̠]</t>
         </is>
       </c>
       <c r="D881" s="1" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>[[ɕ͈it̚t͈a̠]] 洗车场 (烹饪)</t>
+          <t>[[ɕ͈it̚t͈a̠]] 清洗 (烹饪)</t>
         </is>
       </c>
       <c r="C882" s="1" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="D882" s="1" t="inlineStr">
         <is>
-          <t>洗车场 (烹饪)</t>
+          <t>清洗 (烹饪)</t>
         </is>
       </c>
       <c r="E882" s="1" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="B883" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɛ(ː)da̠]] 措施 (烹饪)</t>
+          <t>[[ˈt͡ɕɛ(ː)da̠]] 测量 (烹饪)</t>
         </is>
       </c>
       <c r="C883" s="1" t="inlineStr">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="D883" s="1" t="inlineStr">
         <is>
-          <t>措施 (烹饪)</t>
+          <t>测量 (烹饪)</t>
         </is>
       </c>
       <c r="E883" s="1" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠t̚p͈o̞da̠]] 口感 (烹饪)</t>
+          <t>[[ma̠t̚p͈o̞da̠]] 品尝 (烹饪)</t>
         </is>
       </c>
       <c r="C884" s="1" t="inlineStr">
@@ -28701,7 +28701,7 @@
       </c>
       <c r="D884" s="1" t="inlineStr">
         <is>
-          <t>口感 (烹饪)</t>
+          <t>品尝 (烹饪)</t>
         </is>
       </c>
       <c r="E884" s="1" t="inlineStr">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="B885" s="1" t="inlineStr">
         <is>
-          <t>[[ˈta̠(ː)mt͈a̠]] 盘 (烹饪)</t>
+          <t>[[ˈta̠(ː)mt͈a̠]] 盛入 (烹饪)</t>
         </is>
       </c>
       <c r="C885" s="1" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="D885" s="1" t="inlineStr">
         <is>
-          <t>盘 (烹饪)</t>
+          <t>盛入 (烹饪)</t>
         </is>
       </c>
       <c r="E885" s="1" t="inlineStr">
@@ -28787,7 +28787,7 @@
       </c>
       <c r="B887" s="1" t="inlineStr">
         <is>
-          <t>[[te̞uda̠]] 后燃器 (烹饪)</t>
+          <t>[[te̞uda̠]] 加热 (烹饪)</t>
         </is>
       </c>
       <c r="C887" s="1" t="inlineStr">
@@ -28797,7 +28797,7 @@
       </c>
       <c r="D887" s="1" t="inlineStr">
         <is>
-          <t>后燃器 (烹饪)</t>
+          <t>加热 (烹饪)</t>
         </is>
       </c>
       <c r="E887" s="1" t="inlineStr">
@@ -28851,12 +28851,12 @@
       </c>
       <c r="B889" s="1" t="inlineStr">
         <is>
-          <t>[nettutata] 冷冻 (烹饪)</t>
+          <t>[[ne̞ŋdo̞ŋɦa̠da̠]] 冷冻 (烹饪)</t>
         </is>
       </c>
       <c r="C889" s="1" t="inlineStr">
         <is>
-          <t>nettutata</t>
+          <t>[ne̞ŋdo̞ŋɦa̠da̠]</t>
         </is>
       </c>
       <c r="D889" s="1" t="inlineStr">
@@ -28883,12 +28883,12 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>[netkatata] 冷藏 (烹饪)</t>
+          <t>[[ne̞ŋt͡ɕa̠ŋɦa̠da̠]] 冷藏 (烹饪)</t>
         </is>
       </c>
       <c r="C890" s="1" t="inlineStr">
         <is>
-          <t>netkatata</t>
+          <t>[ne̞ŋt͡ɕa̠ŋɦa̠da̠]</t>
         </is>
       </c>
       <c r="D890" s="1" t="inlineStr">
@@ -28947,12 +28947,12 @@
       </c>
       <c r="B892" s="1" t="inlineStr">
         <is>
-          <t>[tomchoneta] 分装 (烹饪)</t>
+          <t>[[tʌ̹ɾʌ̹nɛ̝da̠]] 分装 (烹饪)</t>
         </is>
       </c>
       <c r="C892" s="1" t="inlineStr">
         <is>
-          <t>tomchoneta</t>
+          <t>[tʌ̹ɾʌ̹nɛ̝da̠]</t>
         </is>
       </c>
       <c r="D892" s="1" t="inlineStr">
@@ -28979,12 +28979,12 @@
       </c>
       <c r="B893" s="1" t="inlineStr">
         <is>
-          <t>[chyripong] 食谱 (烹饪)</t>
+          <t>[[jo̞ɾiba̠p̚]] 食谱 (烹饪)</t>
         </is>
       </c>
       <c r="C893" s="1" t="inlineStr">
         <is>
-          <t>chyripong</t>
+          <t>[jo̞ɾiba̠p̚]</t>
         </is>
       </c>
       <c r="D893" s="1" t="inlineStr">
@@ -29043,7 +29043,7 @@
       </c>
       <c r="B895" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkje̞(ː)ɾja̠ŋ]] 测量 (烹饪)</t>
+          <t>[[ˈkje̞(ː)ɾja̠ŋ]] 计量 (烹饪)</t>
         </is>
       </c>
       <c r="C895" s="1" t="inlineStr">
@@ -29053,7 +29053,7 @@
       </c>
       <c r="D895" s="1" t="inlineStr">
         <is>
-          <t>测量 (烹饪)</t>
+          <t>计量 (烹饪)</t>
         </is>
       </c>
       <c r="E895" s="1" t="inlineStr">
@@ -29299,12 +29299,12 @@
       </c>
       <c r="B903" s="1" t="inlineStr">
         <is>
-          <t>[kitkiknengpi] 炒锅 (烹饪)</t>
+          <t>[[t͡ɕuŋɡuŋnɛ̝mbi]] 炒锅 (烹饪)</t>
         </is>
       </c>
       <c r="C903" s="1" t="inlineStr">
         <is>
-          <t>kitkiknengpi</t>
+          <t>[t͡ɕuŋɡuŋnɛ̝mbi]</t>
         </is>
       </c>
       <c r="D903" s="1" t="inlineStr">
@@ -29491,12 +29491,12 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>[imro] 削皮器 (烹饪)</t>
+          <t>[[pʰiɭɭʌ̹]] 削皮器 (烹饪)</t>
         </is>
       </c>
       <c r="C909" s="1" t="inlineStr">
         <is>
-          <t>imro</t>
+          <t>[pʰiɭɭʌ̹]</t>
         </is>
       </c>
       <c r="D909" s="1" t="inlineStr">
@@ -29555,12 +29555,12 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>[tekingke] 锅铲 (烹饪)</t>
+          <t>[[tɥid͡ʑip̚kɛ̝]] 锅铲 (烹饪)</t>
         </is>
       </c>
       <c r="C911" s="1" t="inlineStr">
         <is>
-          <t>tekingke</t>
+          <t>[tɥid͡ʑip̚kɛ̝]</t>
         </is>
       </c>
       <c r="D911" s="1" t="inlineStr">
@@ -29683,7 +29683,7 @@
       </c>
       <c r="B915" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰɛ]] 滤水篮 (烹饪)</t>
+          <t>[[t͡ɕʰɛ]] 筛子 (烹饪)</t>
         </is>
       </c>
       <c r="C915" s="1" t="inlineStr">
@@ -29693,7 +29693,7 @@
       </c>
       <c r="D915" s="1" t="inlineStr">
         <is>
-          <t>滤水篮 (烹饪)</t>
+          <t>筛子 (烹饪)</t>
         </is>
       </c>
       <c r="E915" s="1" t="inlineStr">
@@ -29747,12 +29747,12 @@
       </c>
       <c r="B917" s="1" t="inlineStr">
         <is>
-          <t>[mikngoki] 搅拌机 (烹饪)</t>
+          <t>[[mik͈sʌ̹ɡi]] 搅拌机 (烹饪)</t>
         </is>
       </c>
       <c r="C917" s="1" t="inlineStr">
         <is>
-          <t>mikngoki</t>
+          <t>[mik͈sʌ̹ɡi]</t>
         </is>
       </c>
       <c r="D917" s="1" t="inlineStr">
@@ -29811,17 +29811,17 @@
       </c>
       <c r="B919" s="1" t="inlineStr">
         <is>
-          <t>[pangngikkarak] 勺子 (烹饪)</t>
+          <t>[[pa̠p̚sut̚ka̠ɾa̠k̚]] 饭勺 (烹饪)</t>
         </is>
       </c>
       <c r="C919" s="1" t="inlineStr">
         <is>
-          <t>pangngikkarak</t>
+          <t>[pa̠p̚sut̚ka̠ɾa̠k̚]</t>
         </is>
       </c>
       <c r="D919" s="1" t="inlineStr">
         <is>
-          <t>勺子 (烹饪)</t>
+          <t>饭勺 (烹饪)</t>
         </is>
       </c>
       <c r="E919" s="1" t="inlineStr">
@@ -29939,12 +29939,12 @@
       </c>
       <c r="B923" s="1" t="inlineStr">
         <is>
-          <t>[chyakpim] 低温 (烹饪)</t>
+          <t>[[jaŋbul]] 低温 (烹饪)</t>
         </is>
       </c>
       <c r="C923" s="1" t="inlineStr">
         <is>
-          <t>chyakpim</t>
+          <t>[jaŋbul]</t>
         </is>
       </c>
       <c r="D923" s="1" t="inlineStr">
@@ -29971,12 +29971,12 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>[kitpim] 五成热 (烹饪)</t>
+          <t>[[t͡ɕuŋbul]] 五成热 (烹饪)</t>
         </is>
       </c>
       <c r="C924" s="1" t="inlineStr">
         <is>
-          <t>kitpim</t>
+          <t>[t͡ɕuŋbul]</t>
         </is>
       </c>
       <c r="D924" s="1" t="inlineStr">
@@ -30003,12 +30003,12 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>[ngenpim] 高温 (烹饪)</t>
+          <t>[[sʰenbul]] 高温 (烹饪)</t>
         </is>
       </c>
       <c r="C925" s="1" t="inlineStr">
         <is>
-          <t>ngenpim</t>
+          <t>[sʰenbul]</t>
         </is>
       </c>
       <c r="D925" s="1" t="inlineStr">
@@ -30035,12 +30035,12 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>[pangakan] 酥脆的；松脆的 (형용사)</t>
+          <t>[[paɕakʰan]] 酥脆的；松脆的 (형용사)</t>
         </is>
       </c>
       <c r="C926" s="1" t="inlineStr">
         <is>
-          <t>pangakan</t>
+          <t>[paɕakʰan]</t>
         </is>
       </c>
       <c r="D926" s="1" t="inlineStr">
@@ -30067,17 +30067,17 @@
       </c>
       <c r="B927" s="1" t="inlineStr">
         <is>
-          <t>[tangtaman] 菜谱 (烹饪)</t>
+          <t>[[t͡ɕap̚t͡ɕ͈aɾan]] 咸的 (烹饪)</t>
         </is>
       </c>
       <c r="C927" s="1" t="inlineStr">
         <is>
-          <t>tangtaman</t>
+          <t>[t͡ɕap̚t͡ɕ͈aɾan]</t>
         </is>
       </c>
       <c r="D927" s="1" t="inlineStr">
         <is>
-          <t>菜谱 (烹饪)</t>
+          <t>咸的 (烹饪)</t>
         </is>
       </c>
       <c r="E927" s="1" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="B930" s="1" t="inlineStr">
         <is>
-          <t>[[ɾidɯm]] 节律 (音乐)</t>
+          <t>[[ɾidɯm]] 节奏 (音乐)</t>
         </is>
       </c>
       <c r="C930" s="1" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="D930" s="1" t="inlineStr">
         <is>
-          <t>节律 (音乐)</t>
+          <t>节奏 (音乐)</t>
         </is>
       </c>
       <c r="E930" s="1" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="B931" s="1" t="inlineStr">
         <is>
-          <t>[[pitʰɯ]] 打 (音乐)</t>
+          <t>[[pitʰɯ]] 节拍 (音乐)</t>
         </is>
       </c>
       <c r="C931" s="1" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="D931" s="1" t="inlineStr">
         <is>
-          <t>打 (音乐)</t>
+          <t>节拍 (音乐)</t>
         </is>
       </c>
       <c r="E931" s="1" t="inlineStr">
@@ -30291,12 +30291,12 @@
       </c>
       <c r="B934" s="1" t="inlineStr">
         <is>
-          <t>[chineru] 引子 (音乐)</t>
+          <t>[[intʰɯɾo]] 引子 (音乐)</t>
         </is>
       </c>
       <c r="C934" s="1" t="inlineStr">
         <is>
-          <t>chineru</t>
+          <t>[intʰɯɾo]</t>
         </is>
       </c>
       <c r="D934" s="1" t="inlineStr">
@@ -30323,12 +30323,12 @@
       </c>
       <c r="B935" s="1" t="inlineStr">
         <is>
-          <t>[chachitru] 尾奏；结尾乐段 (명사)</t>
+          <t>[[a̠utʰɯɾo]] 尾奏；结尾乐段 (명사)</t>
         </is>
       </c>
       <c r="C935" s="1" t="inlineStr">
         <is>
-          <t>chachitru</t>
+          <t>[a̠utʰɯɾo]</t>
         </is>
       </c>
       <c r="D935" s="1" t="inlineStr">
@@ -30355,12 +30355,12 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>[minichempong] 迷你专辑；EP (명사)</t>
+          <t>[[minia̠jɛlbʌ̹m]] 迷你专辑；EP (명사)</t>
         </is>
       </c>
       <c r="C936" s="1" t="inlineStr">
         <is>
-          <t>minichempong</t>
+          <t>[minia̠jɛlbʌ̹m]</t>
         </is>
       </c>
       <c r="D936" s="1" t="inlineStr">
@@ -30611,12 +30611,12 @@
       </c>
       <c r="B944" s="1" t="inlineStr">
         <is>
-          <t>[puhom] 主唱 (音乐)</t>
+          <t>[[pokʰʌ̹l]] 主唱 (音乐)</t>
         </is>
       </c>
       <c r="C944" s="1" t="inlineStr">
         <is>
-          <t>puhom</t>
+          <t>[pokʰʌ̹l]</t>
         </is>
       </c>
       <c r="D944" s="1" t="inlineStr">
@@ -30803,12 +30803,12 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>[chyonngengngim] 练习室 (音乐)</t>
+          <t>[[jʌ̹nsʰɯpɕʰiɭ]] 练习室 (音乐)</t>
         </is>
       </c>
       <c r="C950" s="1" t="inlineStr">
         <is>
-          <t>chyonngengngim</t>
+          <t>[jʌ̹nsʰɯpɕʰiɭ]</t>
         </is>
       </c>
       <c r="D950" s="1" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="B954" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾɛnbi]] R&amp;B (音乐)</t>
+          <t>[[a̠ɾɛnbi]] 节奏布鲁斯 (音乐)</t>
         </is>
       </c>
       <c r="C954" s="1" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="D954" s="1" t="inlineStr">
         <is>
-          <t>R&amp;B (音乐)</t>
+          <t>节奏布鲁斯 (音乐)</t>
         </is>
       </c>
       <c r="E954" s="1" t="inlineStr">
@@ -31475,12 +31475,12 @@
       </c>
       <c r="B971" s="1" t="inlineStr">
         <is>
-          <t>[hopokuk] 翻唱 (音乐)</t>
+          <t>[[kʰʌ̹bo̞ɡo̞k̚]] 翻唱 (音乐)</t>
         </is>
       </c>
       <c r="C971" s="1" t="inlineStr">
         <is>
-          <t>hopokuk</t>
+          <t>[kʰʌ̹bo̞ɡo̞k̚]</t>
         </is>
       </c>
       <c r="D971" s="1" t="inlineStr">
@@ -31571,12 +31571,12 @@
       </c>
       <c r="B974" s="1" t="inlineStr">
         <is>
-          <t>[kimkim] 大笑 (俚语)</t>
+          <t>[[k͈iɭɭk͈iɭɭ]] 大笑 (俚语)</t>
         </is>
       </c>
       <c r="C974" s="1" t="inlineStr">
         <is>
-          <t>kimkim</t>
+          <t>[k͈iɭɭk͈iɭɭ]</t>
         </is>
       </c>
       <c r="D974" s="1" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="B975" s="1" t="inlineStr">
         <is>
-          <t>[[a̠s͈a̠]] 边缘人 (俚语)</t>
+          <t>[[a̠s͈a̠]] 太好了；耶（表示高兴的欢呼声） (俚语)</t>
         </is>
       </c>
       <c r="C975" s="1" t="inlineStr">
@@ -31613,7 +31613,7 @@
       </c>
       <c r="D975" s="1" t="inlineStr">
         <is>
-          <t>边缘人 (俚语)</t>
+          <t>太好了；耶（表示高兴的欢呼声） (俚语)</t>
         </is>
       </c>
       <c r="E975" s="1" t="inlineStr">
@@ -31667,12 +31667,12 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>[ngimwnya] 这是真的吗 (俚语)</t>
+          <t>[[ɕiɭɦwa̠ɲa̠]] 这是真的吗 (俚语)</t>
         </is>
       </c>
       <c r="C977" s="1" t="inlineStr">
         <is>
-          <t>ngimwnya</t>
+          <t>[ɕiɭɦwa̠ɲa̠]</t>
         </is>
       </c>
       <c r="D977" s="1" t="inlineStr">
@@ -31699,12 +31699,12 @@
       </c>
       <c r="B978" s="1" t="inlineStr">
         <is>
-          <t>[pachipe] 氛围 (俚语)</t>
+          <t>[[pa̠ibɯ]] 氛围 (俚语)</t>
         </is>
       </c>
       <c r="C978" s="1" t="inlineStr">
         <is>
-          <t>pachipe</t>
+          <t>[pa̠ibɯ]</t>
         </is>
       </c>
       <c r="D978" s="1" t="inlineStr">
@@ -31731,12 +31731,12 @@
       </c>
       <c r="B979" s="1" t="inlineStr">
         <is>
-          <t>[erenti] 潮流 (俚语)</t>
+          <t>[[tʰɯɾe̞ndi]] 潮流 (俚语)</t>
         </is>
       </c>
       <c r="C979" s="1" t="inlineStr">
         <is>
-          <t>erenti</t>
+          <t>[tʰɯɾe̞ndi]</t>
         </is>
       </c>
       <c r="D979" s="1" t="inlineStr">
@@ -31795,12 +31795,12 @@
       </c>
       <c r="B981" s="1" t="inlineStr">
         <is>
-          <t>[pekinnget] 求职者 (俚语)</t>
+          <t>[[t͡ɕʰwid͡ʑuns͈ɛŋ]] 求职者 (俚语)</t>
         </is>
       </c>
       <c r="C981" s="1" t="inlineStr">
         <is>
-          <t>pekinnget</t>
+          <t>[t͡ɕʰwid͡ʑuns͈ɛŋ]</t>
         </is>
       </c>
       <c r="D981" s="1" t="inlineStr">
@@ -31891,12 +31891,12 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>[unchyot] 独自看电影 (网路用语)</t>
+          <t>[[ho̞ɲʌ̹ŋ]] 独自看电影 (网路用语)</t>
         </is>
       </c>
       <c r="C984" s="1" t="inlineStr">
         <is>
-          <t>unchyot</t>
+          <t>[ho̞ɲʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D984" s="1" t="inlineStr">
@@ -32307,12 +32307,12 @@
       </c>
       <c r="B997" s="1" t="inlineStr">
         <is>
-          <t>[ngenuchipute] 滑雪板 (运动)</t>
+          <t>[[sʰɯnoubot̚]] 滑雪板 (运动)</t>
         </is>
       </c>
       <c r="C997" s="1" t="inlineStr">
         <is>
-          <t>ngenuchipute</t>
+          <t>[sʰɯnoubot̚]</t>
         </is>
       </c>
       <c r="D997" s="1" t="inlineStr">
@@ -32339,12 +32339,12 @@
       </c>
       <c r="B998" s="1" t="inlineStr">
         <is>
-          <t>[chachingengehechiit] 溜冰 (运动)</t>
+          <t>[[aisʰɯsʰɯkʰeitiŋ]] 溜冰 (运动)</t>
         </is>
       </c>
       <c r="C998" s="1" t="inlineStr">
         <is>
-          <t>chachingengehechiit</t>
+          <t>[aisʰɯsʰɯkʰeitiŋ]</t>
         </is>
       </c>
       <c r="D998" s="1" t="inlineStr">
@@ -32371,12 +32371,12 @@
       </c>
       <c r="B999" s="1" t="inlineStr">
         <is>
-          <t>[rimrechi] 接力赛 (运动)</t>
+          <t>[[ɾiɾei]] 接力赛 (运动)</t>
         </is>
       </c>
       <c r="C999" s="1" t="inlineStr">
         <is>
-          <t>rimrechi</t>
+          <t>[ɾiɾei]</t>
         </is>
       </c>
       <c r="D999" s="1" t="inlineStr">
@@ -32467,12 +32467,12 @@
       </c>
       <c r="B1002" s="1" t="inlineStr">
         <is>
-          <t>[chechorupik] 有氧运动 (运动)</t>
+          <t>[[eːʌɾobik̚]] 有氧运动 (运动)</t>
         </is>
       </c>
       <c r="C1002" s="1" t="inlineStr">
         <is>
-          <t>chechorupik</t>
+          <t>[eːʌɾobik̚]</t>
         </is>
       </c>
       <c r="D1002" s="1" t="inlineStr">
@@ -32499,12 +32499,12 @@
       </c>
       <c r="B1003" s="1" t="inlineStr">
         <is>
-          <t>[ieninge] 健身 (运动)</t>
+          <t>[[pʰitʰɯnisʰɯ]] 健身 (运动)</t>
         </is>
       </c>
       <c r="C1003" s="1" t="inlineStr">
         <is>
-          <t>ieninge</t>
+          <t>[pʰitʰɯnisʰɯ]</t>
         </is>
       </c>
       <c r="D1003" s="1" t="inlineStr">
@@ -32531,12 +32531,12 @@
       </c>
       <c r="B1004" s="1" t="inlineStr">
         <is>
-          <t>[chemitchong] 热身 (运动)</t>
+          <t>[[wʌmiŋʌp̚]] 热身 (运动)</t>
         </is>
       </c>
       <c r="C1004" s="1" t="inlineStr">
         <is>
-          <t>chemitchong</t>
+          <t>[wʌmiŋʌp̚]</t>
         </is>
       </c>
       <c r="D1004" s="1" t="inlineStr">
@@ -32563,12 +32563,12 @@
       </c>
       <c r="B1005" s="1" t="inlineStr">
         <is>
-          <t>[himtachin] 缓和运动 (运动)</t>
+          <t>[[kʰuːldaun]] 缓和运动 (运动)</t>
         </is>
       </c>
       <c r="C1005" s="1" t="inlineStr">
         <is>
-          <t>himtachin</t>
+          <t>[kʰuːldaun]</t>
         </is>
       </c>
       <c r="D1005" s="1" t="inlineStr">
@@ -32627,17 +32627,17 @@
       </c>
       <c r="B1007" s="1" t="inlineStr">
         <is>
-          <t>[chwngannguchintut] 心肺运动 (运动)</t>
+          <t>[[jusaŋsoudoŋ]] 有氧运动 (运动)</t>
         </is>
       </c>
       <c r="C1007" s="1" t="inlineStr">
         <is>
-          <t>chwngannguchintut</t>
+          <t>[jusaŋsoudoŋ]</t>
         </is>
       </c>
       <c r="D1007" s="1" t="inlineStr">
         <is>
-          <t>心肺运动 (运动)</t>
+          <t>有氧运动 (运动)</t>
         </is>
       </c>
       <c r="E1007" s="1" t="inlineStr">
@@ -33075,17 +33075,17 @@
       </c>
       <c r="B1021" s="1" t="inlineStr">
         <is>
-          <t>[charena] 体育馆 (运动)</t>
+          <t>[[aɾeːna]] 竞技场 (运动)</t>
         </is>
       </c>
       <c r="C1021" s="1" t="inlineStr">
         <is>
-          <t>charena</t>
+          <t>[aɾeːna]</t>
         </is>
       </c>
       <c r="D1021" s="1" t="inlineStr">
         <is>
-          <t>体育馆 (运动)</t>
+          <t>竞技场 (运动)</t>
         </is>
       </c>
       <c r="E1021" s="1" t="inlineStr">
@@ -33171,7 +33171,7 @@
       </c>
       <c r="B1024" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɯ(ː)ŋwʌ̹n]] 欢呼 (运动)</t>
+          <t>[[ˈɯ(ː)ŋwʌ̹n]] 助威 (运动)</t>
         </is>
       </c>
       <c r="C1024" s="1" t="inlineStr">
@@ -33181,7 +33181,7 @@
       </c>
       <c r="D1024" s="1" t="inlineStr">
         <is>
-          <t>欢呼 (运动)</t>
+          <t>助威 (运动)</t>
         </is>
       </c>
       <c r="E1024" s="1" t="inlineStr">
@@ -33523,7 +33523,7 @@
       </c>
       <c r="B1035" s="1" t="inlineStr">
         <is>
-          <t>[[cçibo̞dɯ]] 键盘热键 (科技)</t>
+          <t>[[cçibo̞dɯ]] 键盘 (科技)</t>
         </is>
       </c>
       <c r="C1035" s="1" t="inlineStr">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="D1035" s="1" t="inlineStr">
         <is>
-          <t>键盘热键 (科技)</t>
+          <t>键盘 (科技)</t>
         </is>
       </c>
       <c r="E1035" s="1" t="inlineStr">
@@ -33587,7 +33587,7 @@
       </c>
       <c r="B1037" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞nitʰʌ̹]] 监控 (科技)</t>
+          <t>[[mo̞nitʰʌ̹]] 显示器 (科技)</t>
         </is>
       </c>
       <c r="C1037" s="1" t="inlineStr">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="D1037" s="1" t="inlineStr">
         <is>
-          <t>监控 (科技)</t>
+          <t>显示器 (科技)</t>
         </is>
       </c>
       <c r="E1037" s="1" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="B1038" s="1" t="inlineStr">
         <is>
-          <t>[[pʰɯɾintʰʌ̹]] 印表机 (科技)</t>
+          <t>[[pʰɯɾintʰʌ̹]] 打印机 (科技)</t>
         </is>
       </c>
       <c r="C1038" s="1" t="inlineStr">
@@ -33629,7 +33629,7 @@
       </c>
       <c r="D1038" s="1" t="inlineStr">
         <is>
-          <t>印表机 (科技)</t>
+          <t>打印机 (科技)</t>
         </is>
       </c>
       <c r="E1038" s="1" t="inlineStr">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯkʰɛnʌ̹]] 扫描器 (科技)</t>
+          <t>[[sʰɯkʰɛnʌ̹]] 扫描仪 (科技)</t>
         </is>
       </c>
       <c r="C1039" s="1" t="inlineStr">
@@ -33661,7 +33661,7 @@
       </c>
       <c r="D1039" s="1" t="inlineStr">
         <is>
-          <t>扫描器 (科技)</t>
+          <t>扫描仪 (科技)</t>
         </is>
       </c>
       <c r="E1039" s="1" t="inlineStr">
@@ -34003,17 +34003,17 @@
       </c>
       <c r="B1050" s="1" t="inlineStr">
         <is>
-          <t>[ngachytkamyot] 使用者名称 (科技)</t>
+          <t>[[sa̠joŋdʑamjʌ̹ŋ]] 用户名 (科技)</t>
         </is>
       </c>
       <c r="C1050" s="1" t="inlineStr">
         <is>
-          <t>ngachytkamyot</t>
+          <t>[sa̠joŋdʑamjʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D1050" s="1" t="inlineStr">
         <is>
-          <t>使用者名称 (科技)</t>
+          <t>用户名 (科技)</t>
         </is>
       </c>
       <c r="E1050" s="1" t="inlineStr">
@@ -34163,12 +34163,12 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>[chamring] 通知 (科技)</t>
+          <t>[[a̠ɭɭim]] 通知 (科技)</t>
         </is>
       </c>
       <c r="C1055" s="1" t="inlineStr">
         <is>
-          <t>chamring</t>
+          <t>[a̠ɭɭim]</t>
         </is>
       </c>
       <c r="D1055" s="1" t="inlineStr">
@@ -34291,12 +34291,12 @@
       </c>
       <c r="B1059" s="1" t="inlineStr">
         <is>
-          <t>[wngatutw] 视频通话 (科技)</t>
+          <t>[[hwa̠sa̠ŋtʰo̞ŋhwa]] 视频通话 (科技)</t>
         </is>
       </c>
       <c r="C1059" s="1" t="inlineStr">
         <is>
-          <t>wngatutw</t>
+          <t>[hwa̠sa̠ŋtʰo̞ŋhwa]</t>
         </is>
       </c>
       <c r="D1059" s="1" t="inlineStr">
@@ -34355,7 +34355,7 @@
       </c>
       <c r="B1061" s="1" t="inlineStr">
         <is>
-          <t>[[jutʰjubɯ]] YouTube；油管 (명사)</t>
+          <t>[[jutʰjubɯ]] 油管（视频网站） (명사)</t>
         </is>
       </c>
       <c r="C1061" s="1" t="inlineStr">
@@ -34365,7 +34365,7 @@
       </c>
       <c r="D1061" s="1" t="inlineStr">
         <is>
-          <t>YouTube；油管 (명사)</t>
+          <t>油管（视频网站） (명사)</t>
         </is>
       </c>
       <c r="E1061" s="1" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>[[insʰɯtʰa̠ɡɯɾɛm]] Instagram；照片墙 (명사)</t>
+          <t>[[insʰɯtʰa̠ɡɯɾɛm]] 照片墙（社交软件） (명사)</t>
         </is>
       </c>
       <c r="C1062" s="1" t="inlineStr">
@@ -34397,7 +34397,7 @@
       </c>
       <c r="D1062" s="1" t="inlineStr">
         <is>
-          <t>Instagram；照片墙 (명사)</t>
+          <t>照片墙（社交软件） (명사)</t>
         </is>
       </c>
       <c r="E1062" s="1" t="inlineStr">
@@ -34451,12 +34451,12 @@
       </c>
       <c r="B1064" s="1" t="inlineStr">
         <is>
-          <t>[nechipo] Naver；韩国搜索引擎 (명사)</t>
+          <t>[[ne̞ibʌ̹]] Naver；韩国搜索引擎 (명사)</t>
         </is>
       </c>
       <c r="C1064" s="1" t="inlineStr">
         <is>
-          <t>nechipo</t>
+          <t>[ne̞ibʌ̹]</t>
         </is>
       </c>
       <c r="D1064" s="1" t="inlineStr">
@@ -34483,12 +34483,12 @@
       </c>
       <c r="B1065" s="1" t="inlineStr">
         <is>
-          <t>[kongngekchenkin] 搜索引擎 (科技)</t>
+          <t>[[kʌ̹msʰʌ̹ɡe̞nd͡ʑin]] 搜索引擎 (科技)</t>
         </is>
       </c>
       <c r="C1065" s="1" t="inlineStr">
         <is>
-          <t>kongngekchenkin</t>
+          <t>[kʌ̹msʰʌ̹ɡe̞nd͡ʑin]</t>
         </is>
       </c>
       <c r="D1065" s="1" t="inlineStr">
@@ -34611,12 +34611,12 @@
       </c>
       <c r="B1069" s="1" t="inlineStr">
         <is>
-          <t>[chichopote] 耳塞式耳机 (科技)</t>
+          <t>[[iʌ̹bʌ̹dɯ]] 耳塞式耳机 (科技)</t>
         </is>
       </c>
       <c r="C1069" s="1" t="inlineStr">
         <is>
-          <t>chichopote</t>
+          <t>[iʌ̹bʌ̹dɯ]</t>
         </is>
       </c>
       <c r="D1069" s="1" t="inlineStr">
@@ -34643,12 +34643,12 @@
       </c>
       <c r="B1070" s="1" t="inlineStr">
         <is>
-          <t>[kechimit] 游戏 (科技)</t>
+          <t>[[ke̞imiŋ]] 游戏 (科技)</t>
         </is>
       </c>
       <c r="C1070" s="1" t="inlineStr">
         <is>
-          <t>kechimit</t>
+          <t>[ke̞imiŋ]</t>
         </is>
       </c>
       <c r="D1070" s="1" t="inlineStr">
@@ -34675,12 +34675,12 @@
       </c>
       <c r="B1071" s="1" t="inlineStr">
         <is>
-          <t>[chingeupe] 电竞 (科技)</t>
+          <t>[[iɯpʰo̞tʰɯ]] 电竞 (科技)</t>
         </is>
       </c>
       <c r="C1071" s="1" t="inlineStr">
         <is>
-          <t>chingeupe</t>
+          <t>[iɯpʰo̞tʰɯ]</t>
         </is>
       </c>
       <c r="D1071" s="1" t="inlineStr">
@@ -34739,12 +34739,12 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>[pukut] 腹痛 (健康与医疗)</t>
+          <t>[[po̞ɡtʰo̞ŋ]] 腹痛 (健康与医疗)</t>
         </is>
       </c>
       <c r="C1073" s="1" t="inlineStr">
         <is>
-          <t>pukut</t>
+          <t>[po̞ɡtʰo̞ŋ]</t>
         </is>
       </c>
       <c r="D1073" s="1" t="inlineStr">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="B1090" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰik͈wa̠]] 牙科医生 (健康医疗)</t>
+          <t>[[t͡ɕʰik͈wa̠]] 牙科 (健康医疗)</t>
         </is>
       </c>
       <c r="C1090" s="1" t="inlineStr">
@@ -35293,7 +35293,7 @@
       </c>
       <c r="D1090" s="1" t="inlineStr">
         <is>
-          <t>牙科医生 (健康医疗)</t>
+          <t>牙科 (健康医疗)</t>
         </is>
       </c>
       <c r="E1090" s="1" t="inlineStr">
@@ -35539,12 +35539,12 @@
       </c>
       <c r="B1098" s="1" t="inlineStr">
         <is>
-          <t>[sing] 扭伤 (健康与医疗)</t>
+          <t>[[s͈am]] 扭伤 (健康与医疗)</t>
         </is>
       </c>
       <c r="C1098" s="1" t="inlineStr">
         <is>
-          <t>sing</t>
+          <t>[s͈am]</t>
         </is>
       </c>
       <c r="D1098" s="1" t="inlineStr">
@@ -35859,12 +35859,12 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>[chopochinam] 父母节 (节日与庆典)</t>
+          <t>[[ʌ̹bʌ̹ina̠ɭ]] 父母节 (节日与庆典)</t>
         </is>
       </c>
       <c r="C1108" s="1" t="inlineStr">
         <is>
-          <t>chopochinam</t>
+          <t>[ʌ̹bʌ̹ina̠ɭ]</t>
         </is>
       </c>
       <c r="D1108" s="1" t="inlineStr">
@@ -35923,12 +35923,12 @@
       </c>
       <c r="B1110" s="1" t="inlineStr">
         <is>
-          <t>[hanechingyon] 康乃馨 (节日与庆典)</t>
+          <t>[[kʰa̠ne̞iɕʰjo̞n]] 康乃馨 (节日与庆典)</t>
         </is>
       </c>
       <c r="C1110" s="1" t="inlineStr">
         <is>
-          <t>hanechingyon</t>
+          <t>[kʰa̠ne̞iɕʰjo̞n]</t>
         </is>
       </c>
       <c r="D1110" s="1" t="inlineStr">
@@ -35987,7 +35987,7 @@
       </c>
       <c r="B1112" s="1" t="inlineStr">
         <is>
-          <t>[[tɯŋp͈uɭ]] 小船灯 (节日庆典)</t>
+          <t>[[tɯŋp͈uɭ]] 灯笼 (节日庆典)</t>
         </is>
       </c>
       <c r="C1112" s="1" t="inlineStr">
@@ -35997,7 +35997,7 @@
       </c>
       <c r="D1112" s="1" t="inlineStr">
         <is>
-          <t>小船灯 (节日庆典)</t>
+          <t>灯笼 (节日庆典)</t>
         </is>
       </c>
       <c r="E1112" s="1" t="inlineStr">
@@ -36211,12 +36211,12 @@
       </c>
       <c r="B1119" s="1" t="inlineStr">
         <is>
-          <t>[kyomunkinyongchim] 结婚纪念日 (节日与庆典)</t>
+          <t>[[kʲʌɾoŋinjʌmiɾ]] 结婚纪念日 (节日与庆典)</t>
         </is>
       </c>
       <c r="C1119" s="1" t="inlineStr">
         <is>
-          <t>kyomunkinyongchim</t>
+          <t>[kʲʌɾoŋinjʌmiɾ]</t>
         </is>
       </c>
       <c r="D1119" s="1" t="inlineStr">
@@ -36691,12 +36691,12 @@
       </c>
       <c r="B1134" s="1" t="inlineStr">
         <is>
-          <t>[hahachuekngi] 出租车应用 (交通)</t>
+          <t>[[kʰakʰaotʰɛk̚ɕʰi]] 出租车应用 (交通)</t>
         </is>
       </c>
       <c r="C1134" s="1" t="inlineStr">
         <is>
-          <t>hahachuekngi</t>
+          <t>[kʰakʰaotʰɛk̚ɕʰi]</t>
         </is>
       </c>
       <c r="D1134" s="1" t="inlineStr">
@@ -36883,12 +36883,12 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>[pongehate] 公交卡 (交通)</t>
+          <t>[[pʌsʰɯkʰaɾɯ]] 公交卡 (交通)</t>
         </is>
       </c>
       <c r="C1140" s="1" t="inlineStr">
         <is>
-          <t>pongehate</t>
+          <t>[pʌsʰɯkʰaɾɯ]</t>
         </is>
       </c>
       <c r="D1140" s="1" t="inlineStr">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="B1142" s="1" t="inlineStr">
         <is>
-          <t>[[tʰʌ̹nʌ̹ɭ]] 隧道腐蚀 (交通)</t>
+          <t>[[tʰʌ̹nʌ̹ɭ]] 隧道 (交通)</t>
         </is>
       </c>
       <c r="C1142" s="1" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="D1142" s="1" t="inlineStr">
         <is>
-          <t>隧道腐蚀 (交通)</t>
+          <t>隧道 (交通)</t>
         </is>
       </c>
       <c r="E1142" s="1" t="inlineStr">
@@ -37043,7 +37043,7 @@
       </c>
       <c r="B1145" s="1" t="inlineStr">
         <is>
-          <t>[[ˈu(ː)ɲd͡ʑʌ̹nɡisʰa̠]] 赛车手 (交通)</t>
+          <t>[[ˈu(ː)ɲd͡ʑʌ̹nɡisʰa̠]] 司机 (交通)</t>
         </is>
       </c>
       <c r="C1145" s="1" t="inlineStr">
@@ -37053,7 +37053,7 @@
       </c>
       <c r="D1145" s="1" t="inlineStr">
         <is>
-          <t>赛车手 (交通)</t>
+          <t>司机 (交通)</t>
         </is>
       </c>
       <c r="E1145" s="1" t="inlineStr">
@@ -37395,12 +37395,12 @@
       </c>
       <c r="B1156" s="1" t="inlineStr">
         <is>
-          <t>[ngyoemponge] 接驳车 (交通)</t>
+          <t>[[ɕʌ̹tʰɯɭbʌ̹sʰɯ]] 接驳车 (交通)</t>
         </is>
       </c>
       <c r="C1156" s="1" t="inlineStr">
         <is>
-          <t>ngyoemponge</t>
+          <t>[ɕʌ̹tʰɯɭbʌ̹sʰɯ]</t>
         </is>
       </c>
       <c r="D1156" s="1" t="inlineStr">
@@ -37427,12 +37427,12 @@
       </c>
       <c r="B1157" s="1" t="inlineStr">
         <is>
-          <t>[chwtpuky] 来回票 (交通)</t>
+          <t>[[wa̠ŋbok̚pʰjʌ̹]] 来回票 (交通)</t>
         </is>
       </c>
       <c r="C1157" s="1" t="inlineStr">
         <is>
-          <t>chwtpuky</t>
+          <t>[wa̠ŋbok̚pʰjʌ̹]</t>
         </is>
       </c>
       <c r="D1157" s="1" t="inlineStr">
@@ -37459,12 +37459,12 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>[ngehinhecho] 护肤 (美容护肤)</t>
+          <t>[[sʰɯkʰiŋkʰe̞ʌ̹]] 护肤 (美容护肤)</t>
         </is>
       </c>
       <c r="C1158" s="1" t="inlineStr">
         <is>
-          <t>ngehinhecho</t>
+          <t>[sʰɯkʰiŋkʰe̞ʌ̹]</t>
         </is>
       </c>
       <c r="D1158" s="1" t="inlineStr">
@@ -37491,12 +37491,12 @@
       </c>
       <c r="B1159" s="1" t="inlineStr">
         <is>
-          <t>[uno] 爽肤水 (美容护肤)</t>
+          <t>[[tʰo̞nʌ̹]] 爽肤水 (美容护肤)</t>
         </is>
       </c>
       <c r="C1159" s="1" t="inlineStr">
         <is>
-          <t>uno</t>
+          <t>[tʰo̞nʌ̹]</t>
         </is>
       </c>
       <c r="D1159" s="1" t="inlineStr">
@@ -37523,12 +37523,12 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>[ngiemangehe] 面膜 (美容护肤)</t>
+          <t>[[ɕitʰɯma̠sʰɯkʰɯ]] 面膜 (美容护肤)</t>
         </is>
       </c>
       <c r="C1160" s="1" t="inlineStr">
         <is>
-          <t>ngiemangehe</t>
+          <t>[ɕitʰɯma̠sʰɯkʰɯ]</t>
         </is>
       </c>
       <c r="D1160" s="1" t="inlineStr">
@@ -37555,12 +37555,12 @@
       </c>
       <c r="B1161" s="1" t="inlineStr">
         <is>
-          <t>[chachirachino] อายไลเนอร์ (美容与护肤)</t>
+          <t>[[a̠iɾa̠inʌ̹]] อายไลเนอร์ (美容与护肤)</t>
         </is>
       </c>
       <c r="C1161" s="1" t="inlineStr">
         <is>
-          <t>chachirachino</t>
+          <t>[a̠iɾa̠inʌ̹]</t>
         </is>
       </c>
       <c r="D1161" s="1" t="inlineStr">
@@ -37619,12 +37619,12 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>[chachingyetu] 眼影 (美容与护肤)</t>
+          <t>[[a̠iɕjɛːdɯ]] 眼影 (美容与护肤)</t>
         </is>
       </c>
       <c r="C1163" s="1" t="inlineStr">
         <is>
-          <t>chachingyetu</t>
+          <t>[a̠iɕjɛːdɯ]</t>
         </is>
       </c>
       <c r="D1163" s="1" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
-          <t>[[ˈjɘ(ː)msʰɛk̚]] 发色 (美容与肌肤保养)</t>
+          <t>[[ˈjɘ(ː)msʰɛk̚]] 染发 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1169" s="1" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="D1169" s="1" t="inlineStr">
         <is>
-          <t>发色 (美容与肌肤保养)</t>
+          <t>染发 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="E1169" s="1" t="inlineStr">
@@ -37875,12 +37875,12 @@
       </c>
       <c r="B1171" s="1" t="inlineStr">
         <is>
-          <t>[nechimchae] 美甲 (美容与肌肤保养)</t>
+          <t>[[neiɾatʰ]] 美甲 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1171" s="1" t="inlineStr">
         <is>
-          <t>nechimchae</t>
+          <t>[neiɾatʰ]</t>
         </is>
       </c>
       <c r="D1171" s="1" t="inlineStr">
@@ -37907,12 +37907,12 @@
       </c>
       <c r="B1172" s="1" t="inlineStr">
         <is>
-          <t>[ngea] 水疗中心 (美容与肌肤保养)</t>
+          <t>[[sʰɯpa]] 水疗中心 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1172" s="1" t="inlineStr">
         <is>
-          <t>ngea</t>
+          <t>[sʰɯpa]</t>
         </is>
       </c>
       <c r="D1172" s="1" t="inlineStr">
@@ -37971,12 +37971,12 @@
       </c>
       <c r="B1174" s="1" t="inlineStr">
         <is>
-          <t>[patirungyon] 身体乳液 (美容与肌肤保养)</t>
+          <t>[[paɣiɾoɕʰʌn]] 身体乳液 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1174" s="1" t="inlineStr">
         <is>
-          <t>patirungyon</t>
+          <t>[paɣiɾoɕʰʌn]</t>
         </is>
       </c>
       <c r="D1174" s="1" t="inlineStr">
@@ -38003,12 +38003,12 @@
       </c>
       <c r="B1175" s="1" t="inlineStr">
         <is>
-          <t>[hemrenkitung] 洁面泡沫 (美容与肌肤保养)</t>
+          <t>[[kʰɯɾent͡ɕiŋpʰom]] 洁面泡沫 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1175" s="1" t="inlineStr">
         <is>
-          <t>hemrenkitung</t>
+          <t>[kʰɯɾent͡ɕiŋpʰom]</t>
         </is>
       </c>
       <c r="D1175" s="1" t="inlineStr">
@@ -38035,12 +38035,12 @@
       </c>
       <c r="B1176" s="1" t="inlineStr">
         <is>
-          <t>[ringkemrunge] 唇蜜 (美容与肌肤保养)</t>
+          <t>[[ɾip̚kɯːlosʰɯ]] 唇蜜 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1176" s="1" t="inlineStr">
         <is>
-          <t>ringkemrunge</t>
+          <t>[ɾip̚kɯːlosʰɯ]</t>
         </is>
       </c>
       <c r="D1176" s="1" t="inlineStr">
@@ -38099,12 +38099,12 @@
       </c>
       <c r="B1178" s="1" t="inlineStr">
         <is>
-          <t>[honngimro] 遮瑕膏 (美容与肌肤保养)</t>
+          <t>[[kʰən.ɕʰil.lʌ]] 遮瑕膏 (美容与肌肤保养)</t>
         </is>
       </c>
       <c r="C1178" s="1" t="inlineStr">
         <is>
-          <t>honngimro</t>
+          <t>[kʰən.ɕʰil.lʌ]</t>
         </is>
       </c>
       <c r="D1178" s="1" t="inlineStr">
@@ -38387,12 +38387,12 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>[patampim] 密室逃脱 (嗜好与休闲)</t>
+          <t>[[paŋ.tʰal.tɕʰul]] 密室逃脱 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C1187" s="1" t="inlineStr">
         <is>
-          <t>patampim</t>
+          <t>[paŋ.tʰal.tɕʰul]</t>
         </is>
       </c>
       <c r="D1187" s="1" t="inlineStr">
@@ -38451,12 +38451,12 @@
       </c>
       <c r="B1189" s="1" t="inlineStr">
         <is>
-          <t>[ngeherengpik] 剪贴簿 (嗜好与休闲)</t>
+          <t>[[sɯ.kʰɯ.ɾɛp.puk̚]] 剪贴簿 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C1189" s="1" t="inlineStr">
         <is>
-          <t>ngeherengpik</t>
+          <t>[sɯ.kʰɯ.ɾɛp.puk̚]</t>
         </is>
       </c>
       <c r="D1189" s="1" t="inlineStr">
@@ -38515,12 +38515,12 @@
       </c>
       <c r="B1191" s="1" t="inlineStr">
         <is>
-          <t>[panryongikmim] 室内植物 (嗜好与休闲)</t>
+          <t>[[pa.ɾʎʌ.ɕiŋ.mul]] 室内植物 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C1191" s="1" t="inlineStr">
         <is>
-          <t>panryongikmim</t>
+          <t>[pa.ɾʎʌ.ɕiŋ.mul]</t>
         </is>
       </c>
       <c r="D1191" s="1" t="inlineStr">
@@ -38611,12 +38611,12 @@
       </c>
       <c r="B1194" s="1" t="inlineStr">
         <is>
-          <t>[kutkikyot] 赏花 (嗜好与休闲)</t>
+          <t>[[k͈ot̚.ku.ɡjʌŋ]] 赏花 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C1194" s="1" t="inlineStr">
         <is>
-          <t>kutkikyot</t>
+          <t>[k͈ot̚.ku.ɡjʌŋ]</t>
         </is>
       </c>
       <c r="D1194" s="1" t="inlineStr">
@@ -38643,12 +38643,12 @@
       </c>
       <c r="B1195" s="1" t="inlineStr">
         <is>
-          <t>[reku] 乐高积木 (嗜好与休闲)</t>
+          <t>[[ɾe.ɡo]] 乐高积木 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C1195" s="1" t="inlineStr">
         <is>
-          <t>reku</t>
+          <t>[ɾe.ɡo]</t>
         </is>
       </c>
       <c r="D1195" s="1" t="inlineStr">
@@ -38739,17 +38739,17 @@
       </c>
       <c r="B1198" s="1" t="inlineStr">
         <is>
-          <t>[anpakchi] 随地吐痰图像 (成语俗语)</t>
+          <t>[[pʰan.ba.ɡi]] 一个模子刻出来的 (成语俗语)</t>
         </is>
       </c>
       <c r="C1198" s="1" t="inlineStr">
         <is>
-          <t>anpakchi</t>
+          <t>[pʰan.ba.ɡi]</t>
         </is>
       </c>
       <c r="D1198" s="1" t="inlineStr">
         <is>
-          <t>随地吐痰图像 (成语俗语)</t>
+          <t>一个模子刻出来的 (成语俗语)</t>
         </is>
       </c>
       <c r="E1198" s="1" t="inlineStr">
@@ -38771,7 +38771,7 @@
       </c>
       <c r="B1199" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕiɾɯmk͈iɭ]] 使用快捷方式 (成语俗语)</t>
+          <t>[[t͡ɕiɾɯmk͈iɭ]] 捷径 (成语俗语)</t>
         </is>
       </c>
       <c r="C1199" s="1" t="inlineStr">
@@ -38781,7 +38781,7 @@
       </c>
       <c r="D1199" s="1" t="inlineStr">
         <is>
-          <t>使用快捷方式 (成语俗语)</t>
+          <t>捷径 (成语俗语)</t>
         </is>
       </c>
       <c r="E1199" s="1" t="inlineStr">
@@ -38803,7 +38803,7 @@
       </c>
       <c r="B1200" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰo̞(ː)ɡiɦa̠da̠]] 扔进毛巾 (成语俗语)</t>
+          <t>[[ˈpʰo̞(ː)ɡiɦa̠da̠]] 放弃 (成语俗语)</t>
         </is>
       </c>
       <c r="C1200" s="1" t="inlineStr">
@@ -38813,7 +38813,7 @@
       </c>
       <c r="D1200" s="1" t="inlineStr">
         <is>
-          <t>扔进毛巾 (成语俗语)</t>
+          <t>放弃 (成语俗语)</t>
         </is>
       </c>
       <c r="E1200" s="1" t="inlineStr">
@@ -38835,12 +38835,12 @@
       </c>
       <c r="B1201" s="1" t="inlineStr">
         <is>
-          <t>[pimwkngimata] 不确定的；悬而未决的 (成语俗语)</t>
+          <t>[[buɾɦwaksilɦada]] 不确定的；悬而未决的 (成语俗语)</t>
         </is>
       </c>
       <c r="C1201" s="1" t="inlineStr">
         <is>
-          <t>pimwkngimata</t>
+          <t>[buɾɦwaksilɦada]</t>
         </is>
       </c>
       <c r="D1201" s="1" t="inlineStr">
@@ -39059,7 +39059,7 @@
       </c>
       <c r="B1208" s="1" t="inlineStr">
         <is>
-          <t>[[pe̞ɡɛ]] 固定座 (家居家具)</t>
+          <t>[[pe̞ɡɛ]] 枕头 (家居家具)</t>
         </is>
       </c>
       <c r="C1208" s="1" t="inlineStr">
@@ -39069,7 +39069,7 @@
       </c>
       <c r="D1208" s="1" t="inlineStr">
         <is>
-          <t>固定座 (家居家具)</t>
+          <t>枕头 (家居家具)</t>
         </is>
       </c>
       <c r="E1208" s="1" t="inlineStr">
@@ -39091,7 +39091,7 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>[[ˈta̠(ː)mɲo]] 包层 (家居家具)</t>
+          <t>[[ˈta̠(ː)mɲo]] 毯子 (家居家具)</t>
         </is>
       </c>
       <c r="C1209" s="1" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="D1209" s="1" t="inlineStr">
         <is>
-          <t>包层 (家居家具)</t>
+          <t>毯子 (家居家具)</t>
         </is>
       </c>
       <c r="E1209" s="1" t="inlineStr">
@@ -39155,12 +39155,12 @@
       </c>
       <c r="B1211" s="1" t="inlineStr">
         <is>
-          <t>[mee] 地垫 (居家与家具)</t>
+          <t>[[mɛtʰɯ]] 地垫 (居家与家具)</t>
         </is>
       </c>
       <c r="C1211" s="1" t="inlineStr">
         <is>
-          <t>mee</t>
+          <t>[mɛtʰɯ]</t>
         </is>
       </c>
       <c r="D1211" s="1" t="inlineStr">
@@ -39283,12 +39283,12 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>[roke] 地毯 (居家与家具)</t>
+          <t>[[ɾʌɡɯ]] 地毯 (居家与家具)</t>
         </is>
       </c>
       <c r="C1215" s="1" t="inlineStr">
         <is>
-          <t>roke</t>
+          <t>[ɾʌɡɯ]</t>
         </is>
       </c>
       <c r="D1215" s="1" t="inlineStr">
@@ -39315,12 +39315,12 @@
       </c>
       <c r="B1216" s="1" t="inlineStr">
         <is>
-          <t>[ngya] 沙发 (居家与家具)</t>
+          <t>[[ɕʰopʰa]] 沙发 (居家与家具)</t>
         </is>
       </c>
       <c r="C1216" s="1" t="inlineStr">
         <is>
-          <t>ngya</t>
+          <t>[ɕʰopʰa]</t>
         </is>
       </c>
       <c r="D1216" s="1" t="inlineStr">
@@ -39347,12 +39347,12 @@
       </c>
       <c r="B1217" s="1" t="inlineStr">
         <is>
-          <t>[nginpamkat] 鞋架 (居家与家具)</t>
+          <t>[[ɕinbaɭt͡ɕaŋ]] 鞋架 (居家与家具)</t>
         </is>
       </c>
       <c r="C1217" s="1" t="inlineStr">
         <is>
-          <t>nginpamkat</t>
+          <t>[ɕinbaɭt͡ɕaŋ]</t>
         </is>
       </c>
       <c r="D1217" s="1" t="inlineStr">
@@ -39571,7 +39571,7 @@
       </c>
       <c r="B1224" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ŋsʰo̞]] 居家清洁 (居家与家具)</t>
+          <t>[[t͡ɕʰʌ̹ŋsʰo̞]] 打扫 (居家与家具)</t>
         </is>
       </c>
       <c r="C1224" s="1" t="inlineStr">
@@ -39581,7 +39581,7 @@
       </c>
       <c r="D1224" s="1" t="inlineStr">
         <is>
-          <t>居家清洁 (居家与家具)</t>
+          <t>打扫 (居家与家具)</t>
         </is>
       </c>
       <c r="E1224" s="1" t="inlineStr">
@@ -39635,12 +39635,12 @@
       </c>
       <c r="B1226" s="1" t="inlineStr">
         <is>
-          <t>[nginangang] 收纳箱 (居家与家具)</t>
+          <t>[[suna̠pʰa̠m]] 收纳箱 (居家与家具)</t>
         </is>
       </c>
       <c r="C1226" s="1" t="inlineStr">
         <is>
-          <t>nginangang</t>
+          <t>[suna̠pʰa̠m]</t>
         </is>
       </c>
       <c r="D1226" s="1" t="inlineStr">
@@ -39667,7 +39667,7 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰa̠ŋɡo̞]] 储藏室 (居家与家具)</t>
+          <t>[[t͡ɕʰa̠ŋɡo̞]] 仓库 (居家与家具)</t>
         </is>
       </c>
       <c r="C1227" s="1" t="inlineStr">
@@ -39677,7 +39677,7 @@
       </c>
       <c r="D1227" s="1" t="inlineStr">
         <is>
-          <t>储藏室 (居家与家具)</t>
+          <t>仓库 (居家与家具)</t>
         </is>
       </c>
       <c r="E1227" s="1" t="inlineStr">
@@ -39795,12 +39795,12 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>[tukngotet] 阅读灯 (居家与家具)</t>
+          <t>[[tʊks͈ʌ̹t̚t͈ʌ̹ŋ]] 阅读灯 (居家与家具)</t>
         </is>
       </c>
       <c r="C1231" s="1" t="inlineStr">
         <is>
-          <t>tukngotet</t>
+          <t>[tʊks͈ʌ̹t̚t͈ʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D1231" s="1" t="inlineStr">
@@ -39827,12 +39827,12 @@
       </c>
       <c r="B1232" s="1" t="inlineStr">
         <is>
-          <t>[emok] 吊床 (居家与家具)</t>
+          <t>[[hɛmʌ̹k̚]] 吊床 (居家与家具)</t>
         </is>
       </c>
       <c r="C1232" s="1" t="inlineStr">
         <is>
-          <t>emok</t>
+          <t>[hɛmʌ̹k̚]</t>
         </is>
       </c>
       <c r="D1232" s="1" t="inlineStr">
@@ -39987,12 +39987,12 @@
       </c>
       <c r="B1237" s="1" t="inlineStr">
         <is>
-          <t>[hepinit] 橱柜 (居家与家具)</t>
+          <t>[[kʰɛbinit̚]] 橱柜 (居家与家具)</t>
         </is>
       </c>
       <c r="C1237" s="1" t="inlineStr">
         <is>
-          <t>hepinit</t>
+          <t>[kʰɛbinit̚]</t>
         </is>
       </c>
       <c r="D1237" s="1" t="inlineStr">
@@ -40115,12 +40115,12 @@
       </c>
       <c r="B1241" s="1" t="inlineStr">
         <is>
-          <t>[chutkomchite] 衣帽架 (居家与家具)</t>
+          <t>[[o̞t̚k͈ʌ̹ɾida̠e̞]] 衣帽架 (居家与家具)</t>
         </is>
       </c>
       <c r="C1241" s="1" t="inlineStr">
         <is>
-          <t>chutkomchite</t>
+          <t>[o̞t̚k͈ʌ̹ɾida̠e̞]</t>
         </is>
       </c>
       <c r="D1241" s="1" t="inlineStr">
@@ -40147,12 +40147,12 @@
       </c>
       <c r="B1242" s="1" t="inlineStr">
         <is>
-          <t>[chyakkat] 药柜 (居家与家具)</t>
+          <t>[[ja̠k̚t͈a̠ŋ]] 药柜 (居家与家具)</t>
         </is>
       </c>
       <c r="C1242" s="1" t="inlineStr">
         <is>
-          <t>chyakkat</t>
+          <t>[ja̠k̚t͈a̠ŋ]</t>
         </is>
       </c>
       <c r="D1242" s="1" t="inlineStr">
@@ -40179,12 +40179,12 @@
       </c>
       <c r="B1243" s="1" t="inlineStr">
         <is>
-          <t>[kutchwki] 网路路由器 (居家与家具)</t>
+          <t>[[ko̞ŋjugi]] 网路路由器 (居家与家具)</t>
         </is>
       </c>
       <c r="C1243" s="1" t="inlineStr">
         <is>
-          <t>kutchwki</t>
+          <t>[ko̞ŋjugi]</t>
         </is>
       </c>
       <c r="D1243" s="1" t="inlineStr">
@@ -40467,12 +40467,12 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>[[kudu]] 正装鞋 (时尚与风格)</t>
+          <t>[[kuːdu]] 正装鞋 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1252" s="1" t="inlineStr">
         <is>
-          <t>[kudu]</t>
+          <t>[kuːdu]</t>
         </is>
       </c>
       <c r="D1252" s="1" t="inlineStr">
@@ -40499,12 +40499,12 @@
       </c>
       <c r="B1253" s="1" t="inlineStr">
         <is>
-          <t>[kwchomri] 珠宝饰品 (时尚与风格)</t>
+          <t>[[t͈jua̠ɭɭi]] 珠宝饰品 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1253" s="1" t="inlineStr">
         <is>
-          <t>kwchomri</t>
+          <t>[t͈jua̠ɭɭi]</t>
         </is>
       </c>
       <c r="D1253" s="1" t="inlineStr">
@@ -40531,12 +40531,12 @@
       </c>
       <c r="B1254" s="1" t="inlineStr">
         <is>
-          <t>[chupongachike] 超宽松版型 (时尚穿搭)</t>
+          <t>[[o̞bʌ̹sa̠id͡ʑɯ]] 超宽松版型 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C1254" s="1" t="inlineStr">
         <is>
-          <t>chupongachike</t>
+          <t>[o̞bʌ̹sa̠id͡ʑɯ]</t>
         </is>
       </c>
       <c r="D1254" s="1" t="inlineStr">
@@ -40563,17 +40563,17 @@
       </c>
       <c r="B1255" s="1" t="inlineStr">
         <is>
-          <t>[kutminy] 花卉 (时尚穿搭)</t>
+          <t>[[k͈o̞nmuni]] 碎花 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C1255" s="1" t="inlineStr">
         <is>
-          <t>kutminy</t>
+          <t>[k͈o̞nmuni]</t>
         </is>
       </c>
       <c r="D1255" s="1" t="inlineStr">
         <is>
-          <t>花卉 (时尚穿搭)</t>
+          <t>碎花 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E1255" s="1" t="inlineStr">
@@ -40595,7 +40595,7 @@
       </c>
       <c r="B1256" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰopʰiŋmo̞ɭ]] 梦幻卖场 (时尚穿搭)</t>
+          <t>[[ɕʰopʰiŋmo̞ɭ]] 购物中心 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C1256" s="1" t="inlineStr">
@@ -40605,7 +40605,7 @@
       </c>
       <c r="D1256" s="1" t="inlineStr">
         <is>
-          <t>梦幻卖场 (时尚穿搭)</t>
+          <t>购物中心 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E1256" s="1" t="inlineStr">
@@ -40627,12 +40627,12 @@
       </c>
       <c r="B1257" s="1" t="inlineStr">
         <is>
-          <t>[pohitet] 渔夫帽 (时尚与风格)</t>
+          <t>[[bʌ̹kʰit̚hɛt̚]] 渔夫帽 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1257" s="1" t="inlineStr">
         <is>
-          <t>pohitet</t>
+          <t>[bʌ̹kʰit̚hɛt̚]</t>
         </is>
       </c>
       <c r="D1257" s="1" t="inlineStr">
@@ -40659,12 +40659,12 @@
       </c>
       <c r="B1258" s="1" t="inlineStr">
         <is>
-          <t>[ungchecho] 家居服 (时尚与风格)</t>
+          <t>[[ho̞mwɛʌ̹]] 家居服 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1258" s="1" t="inlineStr">
         <is>
-          <t>ungchecho</t>
+          <t>[ho̞mwɛʌ̹]</t>
         </is>
       </c>
       <c r="D1258" s="1" t="inlineStr">
@@ -40691,12 +40691,12 @@
       </c>
       <c r="B1259" s="1" t="inlineStr">
         <is>
-          <t>[chachio] 外衣 (时尚与风格)</t>
+          <t>[[a̠utʰʌ̹]] 外衣 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1259" s="1" t="inlineStr">
         <is>
-          <t>chachio</t>
+          <t>[a̠utʰʌ̹]</t>
         </is>
       </c>
       <c r="D1259" s="1" t="inlineStr">
@@ -40723,12 +40723,12 @@
       </c>
       <c r="B1260" s="1" t="inlineStr">
         <is>
-          <t>[umranek] Polo领 (时尚与风格)</t>
+          <t>[[pʰo̞ɭɭa̠nek̚]] Polo领 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1260" s="1" t="inlineStr">
         <is>
-          <t>umranek</t>
+          <t>[pʰo̞ɭɭa̠nek̚]</t>
         </is>
       </c>
       <c r="D1260" s="1" t="inlineStr">
@@ -40755,17 +40755,17 @@
       </c>
       <c r="B1261" s="1" t="inlineStr">
         <is>
-          <t>[niechecho] 针织品 (时尚与风格)</t>
+          <t>[[ni.tʰwe.ʌ]] 针织服装 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1261" s="1" t="inlineStr">
         <is>
-          <t>niechecho</t>
+          <t>[ni.tʰwe.ʌ]</t>
         </is>
       </c>
       <c r="D1261" s="1" t="inlineStr">
         <is>
-          <t>针织品 (时尚与风格)</t>
+          <t>针织服装 (时尚与风格)</t>
         </is>
       </c>
       <c r="E1261" s="1" t="inlineStr">
@@ -40787,17 +40787,17 @@
       </c>
       <c r="B1262" s="1" t="inlineStr">
         <is>
-          <t>[umoang] 悬挂顶部 (时尚与风格)</t>
+          <t>[[hol.tʰʌ.tʰap̚]] 挂脖上衣 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1262" s="1" t="inlineStr">
         <is>
-          <t>umoang</t>
+          <t>[hol.tʰʌ.tʰap̚]</t>
         </is>
       </c>
       <c r="D1262" s="1" t="inlineStr">
         <is>
-          <t>悬挂顶部 (时尚与风格)</t>
+          <t>挂脖上衣 (时尚与风格)</t>
         </is>
       </c>
       <c r="E1262" s="1" t="inlineStr">
@@ -40819,12 +40819,12 @@
       </c>
       <c r="B1263" s="1" t="inlineStr">
         <is>
-          <t>[pohitpek] 水桶袋 (时尚与风格)</t>
+          <t>[[pʌ.kʰit.pɛk̚]] 水桶袋 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1263" s="1" t="inlineStr">
         <is>
-          <t>pohitpek</t>
+          <t>[pʌ.kʰit.pɛk̚]</t>
         </is>
       </c>
       <c r="D1263" s="1" t="inlineStr">
@@ -40851,12 +40851,12 @@
       </c>
       <c r="B1264" s="1" t="inlineStr">
         <is>
-          <t>[ingngek] 范妮礼包 (时尚与风格)</t>
+          <t>[[hip̚.s͈ɛk̚]] 范妮礼包 (时尚与风格)</t>
         </is>
       </c>
       <c r="C1264" s="1" t="inlineStr">
         <is>
-          <t>ingngek</t>
+          <t>[hip̚.s͈ɛk̚]</t>
         </is>
       </c>
       <c r="D1264" s="1" t="inlineStr">
@@ -40883,12 +40883,12 @@
       </c>
       <c r="B1265" s="1" t="inlineStr">
         <is>
-          <t>[erentian] 流行 (时尚穿搭)</t>
+          <t>[[tʰɯ.ɾen.di.han]] 流行 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C1265" s="1" t="inlineStr">
         <is>
-          <t>erentian</t>
+          <t>[tʰɯ.ɾen.di.han]</t>
         </is>
       </c>
       <c r="D1265" s="1" t="inlineStr">
@@ -41011,12 +41011,12 @@
       </c>
       <c r="B1269" s="1" t="inlineStr">
         <is>
-          <t>[ongpemro] 可重复使用杯子 (环境)</t>
+          <t>[[tʰʌm.bʌl.lʌ]] 可重复使用杯子 (环境)</t>
         </is>
       </c>
       <c r="C1269" s="1" t="inlineStr">
         <is>
-          <t>ongpemro</t>
+          <t>[tʰʌm.bʌl.lʌ]</t>
         </is>
       </c>
       <c r="D1269" s="1" t="inlineStr">
@@ -41171,12 +41171,12 @@
       </c>
       <c r="B1274" s="1" t="inlineStr">
         <is>
-          <t>[nangtemin] 南大门 (崇礼门) (韩国历史)</t>
+          <t>[[nam.dɛ.mun]] 南大门 (崇礼门) (韩国历史)</t>
         </is>
       </c>
       <c r="C1274" s="1" t="inlineStr">
         <is>
-          <t>nangtemin</t>
+          <t>[nam.dɛ.mun]</t>
         </is>
       </c>
       <c r="D1274" s="1" t="inlineStr">
@@ -41523,7 +41523,7 @@
       </c>
       <c r="B1285" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕumindɯŋno̞k̚t͡ɕ͈ɯŋ]] 国民 ID (法律与政府)</t>
+          <t>[[t͡ɕumindɯŋno̞k̚t͡ɕ͈ɯŋ]] 居民身份证 (法律与政府)</t>
         </is>
       </c>
       <c r="C1285" s="1" t="inlineStr">
@@ -41533,7 +41533,7 @@
       </c>
       <c r="D1285" s="1" t="inlineStr">
         <is>
-          <t>国民 ID (法律与政府)</t>
+          <t>居民身份证 (法律与政府)</t>
         </is>
       </c>
       <c r="E1285" s="1" t="inlineStr">
@@ -41715,12 +41715,12 @@
       </c>
       <c r="B1291" s="1" t="inlineStr">
         <is>
-          <t>[amree] 调色盘 (艺术与设计)</t>
+          <t>[[pʰaɭɭetʰɯ]] 调色盘 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1291" s="1" t="inlineStr">
         <is>
-          <t>amree</t>
+          <t>[pʰaɭɭetʰɯ]</t>
         </is>
       </c>
       <c r="D1291" s="1" t="inlineStr">
@@ -41811,7 +41811,7 @@
       </c>
       <c r="B1294" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹mtʰo̞]] 粘土模式（渲染白模） (艺术与设计)</t>
+          <t>[[t͡ɕʌ̹mtʰo̞]] 粘土 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1294" s="1" t="inlineStr">
@@ -41821,7 +41821,7 @@
       </c>
       <c r="D1294" s="1" t="inlineStr">
         <is>
-          <t>粘土模式（渲染白模） (艺术与设计)</t>
+          <t>粘土 (艺术与设计)</t>
         </is>
       </c>
       <c r="E1294" s="1" t="inlineStr">
@@ -42067,7 +42067,7 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>[[kɛɭɭʌ̹ɾi]] 大厅 (艺术与设计)</t>
+          <t>[[kɛɭɭʌ̹ɾi]] 画廊 (艺术与设计)</t>
         </is>
       </c>
       <c r="C1302" s="1" t="inlineStr">
@@ -42077,7 +42077,7 @@
       </c>
       <c r="D1302" s="1" t="inlineStr">
         <is>
-          <t>大厅 (艺术与设计)</t>
+          <t>画廊 (艺术与设计)</t>
         </is>
       </c>
       <c r="E1302" s="1" t="inlineStr">
@@ -42131,7 +42131,7 @@
       </c>
       <c r="B1304" s="1" t="inlineStr">
         <is>
-          <t>[[ˈje̞(ː)sʰuɭɡa̠]] 美编 (艺术设计)</t>
+          <t>[[ˈje̞(ː)sʰuɭɡa̠]] 艺术家 (艺术设计)</t>
         </is>
       </c>
       <c r="C1304" s="1" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="D1304" s="1" t="inlineStr">
         <is>
-          <t>美编 (艺术设计)</t>
+          <t>艺术家 (艺术设计)</t>
         </is>
       </c>
       <c r="E1304" s="1" t="inlineStr">
@@ -42483,7 +42483,7 @@
       </c>
       <c r="B1315" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯnim]] 武僧 (宗教)</t>
+          <t>[[sʰɯnim]] 师父 (宗教)</t>
         </is>
       </c>
       <c r="C1315" s="1" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="D1315" s="1" t="inlineStr">
         <is>
-          <t>武僧 (宗教)</t>
+          <t>师父 (宗教)</t>
         </is>
       </c>
       <c r="E1315" s="1" t="inlineStr">
@@ -42835,12 +42835,12 @@
       </c>
       <c r="B1326" s="1" t="inlineStr">
         <is>
-          <t>[panngutka] 圣歌 (宗教)</t>
+          <t>[[t͡ɕʰa̠nsʰo̞ŋɡa̠]] 圣歌 (宗教)</t>
         </is>
       </c>
       <c r="C1326" s="1" t="inlineStr">
         <is>
-          <t>panngutka</t>
+          <t>[t͡ɕʰa̠nsʰo̞ŋɡa̠]</t>
         </is>
       </c>
       <c r="D1326" s="1" t="inlineStr">
@@ -43059,7 +43059,7 @@
       </c>
       <c r="B1333" s="1" t="inlineStr">
         <is>
-          <t>[[ip̚k͈ɯm]] 存款 (金融与银行)</t>
+          <t>[[ip̚k͈ɯm]] 入账；汇入 (金融与银行)</t>
         </is>
       </c>
       <c r="C1333" s="1" t="inlineStr">
@@ -43069,7 +43069,7 @@
       </c>
       <c r="D1333" s="1" t="inlineStr">
         <is>
-          <t>存款 (金融与银行)</t>
+          <t>入账；汇入 (金融与银行)</t>
         </is>
       </c>
       <c r="E1333" s="1" t="inlineStr">
@@ -43443,12 +43443,12 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>[chyatchwk] 育儿 (育儿与家庭生活)</t>
+          <t>[[ja̠ŋjuk̚]] 育儿 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1345" s="1" t="inlineStr">
         <is>
-          <t>chyatchwk</t>
+          <t>[ja̠ŋjuk̚]</t>
         </is>
       </c>
       <c r="D1345" s="1" t="inlineStr">
@@ -43475,12 +43475,12 @@
       </c>
       <c r="B1346" s="1" t="inlineStr">
         <is>
-          <t>[mungot] 母性；母亲的身份 (명사)</t>
+          <t>[[mo̞sʌ̹ŋ]] 母性；母亲的身份 (명사)</t>
         </is>
       </c>
       <c r="C1346" s="1" t="inlineStr">
         <is>
-          <t>mungot</t>
+          <t>[mo̞sʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D1346" s="1" t="inlineStr">
@@ -43507,12 +43507,12 @@
       </c>
       <c r="B1347" s="1" t="inlineStr">
         <is>
-          <t>[pingot] 父性；父亲的身份 (명사)</t>
+          <t>[[pusʌ̹ŋ]] 父性；父亲的身份 (명사)</t>
         </is>
       </c>
       <c r="C1347" s="1" t="inlineStr">
         <is>
-          <t>pingot</t>
+          <t>[pusʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D1347" s="1" t="inlineStr">
@@ -43603,17 +43603,17 @@
       </c>
       <c r="B1350" s="1" t="inlineStr">
         <is>
-          <t>[chichwngik] 婴儿食品 (育儿与家庭生活)</t>
+          <t>[[ijusʰik̚]] 婴儿辅食 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1350" s="1" t="inlineStr">
         <is>
-          <t>chichwngik</t>
+          <t>[ijusʰik̚]</t>
         </is>
       </c>
       <c r="D1350" s="1" t="inlineStr">
         <is>
-          <t>婴儿食品 (育儿与家庭生活)</t>
+          <t>婴儿辅食 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="E1350" s="1" t="inlineStr">
@@ -43699,12 +43699,12 @@
       </c>
       <c r="B1353" s="1" t="inlineStr">
         <is>
-          <t>[chakiti] 婴儿背带 (育儿与家庭生活)</t>
+          <t>[[a̠ɡit͈i]] 婴儿背带 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1353" s="1" t="inlineStr">
         <is>
-          <t>chakiti</t>
+          <t>[a̠ɡit͈i]</t>
         </is>
       </c>
       <c r="D1353" s="1" t="inlineStr">
@@ -43891,12 +43891,12 @@
       </c>
       <c r="B1359" s="1" t="inlineStr">
         <is>
-          <t>[chwitutchi] 独生子女 (育儿与家庭生活)</t>
+          <t>[[wʌ̹do̞ŋi]] 独生子女 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1359" s="1" t="inlineStr">
         <is>
-          <t>chwitutchi</t>
+          <t>[wʌ̹do̞ŋi]</t>
         </is>
       </c>
       <c r="D1359" s="1" t="inlineStr">
@@ -44179,12 +44179,12 @@
       </c>
       <c r="B1368" s="1" t="inlineStr">
         <is>
-          <t>[pomkat] 钢铁 (建筑)</t>
+          <t>[[t͡ɕʰʌ̹lɡa̠ŋ]] 钢铁 (建筑)</t>
         </is>
       </c>
       <c r="C1368" s="1" t="inlineStr">
         <is>
-          <t>pomkat</t>
+          <t>[t͡ɕʰʌ̹lɡa̠ŋ]</t>
         </is>
       </c>
       <c r="D1368" s="1" t="inlineStr">
@@ -44211,12 +44211,12 @@
       </c>
       <c r="B1369" s="1" t="inlineStr">
         <is>
-          <t>[rimutemrit] 翻新 (建筑)</t>
+          <t>[[ɾimo̞dɛliŋ]] 翻新 (建筑)</t>
         </is>
       </c>
       <c r="C1369" s="1" t="inlineStr">
         <is>
-          <t>rimutemrit</t>
+          <t>[ɾimo̞dɛliŋ]</t>
         </is>
       </c>
       <c r="D1369" s="1" t="inlineStr">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>[[uɭtʰa̠ɾi]] 围墙 (建筑)</t>
+          <t>[[uɭtʰa̠ɾi]] 篱笆；栅栏 (建筑)</t>
         </is>
       </c>
       <c r="C1372" s="1" t="inlineStr">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="D1372" s="1" t="inlineStr">
         <is>
-          <t>围墙 (建筑)</t>
+          <t>篱笆；栅栏 (建筑)</t>
         </is>
       </c>
       <c r="E1372" s="1" t="inlineStr">
@@ -44627,12 +44627,12 @@
       </c>
       <c r="B1382" s="1" t="inlineStr">
         <is>
-          <t>[chyotcha] 婴儿 (育儿与家庭生活)</t>
+          <t>[[jʌ̹ŋa̠]] 婴儿 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1382" s="1" t="inlineStr">
         <is>
-          <t>chyotcha</t>
+          <t>[jʌ̹ŋa̠]</t>
         </is>
       </c>
       <c r="D1382" s="1" t="inlineStr">
@@ -44659,7 +44659,7 @@
       </c>
       <c r="B1383" s="1" t="inlineStr">
         <is>
-          <t>[[jua̠wʌ̹n]] 学前班 (育儿与家庭生活)</t>
+          <t>[[jua̠wʌ̹n]] 幼儿园 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="C1383" s="1" t="inlineStr">
@@ -44669,7 +44669,7 @@
       </c>
       <c r="D1383" s="1" t="inlineStr">
         <is>
-          <t>学前班 (育儿与家庭生活)</t>
+          <t>幼儿园 (育儿与家庭生活)</t>
         </is>
       </c>
       <c r="E1383" s="1" t="inlineStr">
@@ -44755,12 +44755,12 @@
       </c>
       <c r="B1386" s="1" t="inlineStr">
         <is>
-          <t>[minwngeno] 文化中心 (建筑)</t>
+          <t>[[munhwa̠sʰe̞ntʰʌ̹]] 文化中心 (建筑)</t>
         </is>
       </c>
       <c r="C1386" s="1" t="inlineStr">
         <is>
-          <t>minwngeno</t>
+          <t>[munhwa̠sʰe̞ntʰʌ̹]</t>
         </is>
       </c>
       <c r="D1386" s="1" t="inlineStr">
@@ -44851,12 +44851,12 @@
       </c>
       <c r="B1389" s="1" t="inlineStr">
         <is>
-          <t>[eterachin] 头条 (媒体与新闻)</t>
+          <t>[[he̞dɯɾailin]] 头条 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C1389" s="1" t="inlineStr">
         <is>
-          <t>eterachin</t>
+          <t>[he̞dɯɾailin]</t>
         </is>
       </c>
       <c r="D1389" s="1" t="inlineStr">
@@ -44915,12 +44915,12 @@
       </c>
       <c r="B1391" s="1" t="inlineStr">
         <is>
-          <t>[riuo] 现场记者 (媒体与新闻)</t>
+          <t>[[ɾipʰo̞tʰʌ̹]] 现场记者 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C1391" s="1" t="inlineStr">
         <is>
-          <t>riuo</t>
+          <t>[ɾipʰo̞tʰʌ̹]</t>
         </is>
       </c>
       <c r="D1391" s="1" t="inlineStr">
@@ -45139,12 +45139,12 @@
       </c>
       <c r="B1398" s="1" t="inlineStr">
         <is>
-          <t>[riechet] 转推；转发 (명사)</t>
+          <t>[[ɾitɯwit̚]] 转推；转发 (명사)</t>
         </is>
       </c>
       <c r="C1398" s="1" t="inlineStr">
         <is>
-          <t>riechet</t>
+          <t>[ɾitɯwit̚]</t>
         </is>
       </c>
       <c r="D1398" s="1" t="inlineStr">
@@ -45235,7 +45235,7 @@
       </c>
       <c r="B1401" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠p̚t͡ɕ͈i]] 弹匣 (媒体与新闻学)</t>
+          <t>[[t͡ɕa̠p̚t͡ɕ͈i]] 杂志 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C1401" s="1" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="D1401" s="1" t="inlineStr">
         <is>
-          <t>弹匣 (媒体与新闻学)</t>
+          <t>杂志 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E1401" s="1" t="inlineStr">
@@ -45491,12 +45491,12 @@
       </c>
       <c r="B1409" s="1" t="inlineStr">
         <is>
-          <t>[hutnamimkik] 豆芽汤 (명사)</t>
+          <t>[[ko̞ŋna̠muɭɡuk̚]] 豆芽汤 (명사)</t>
         </is>
       </c>
       <c r="C1409" s="1" t="inlineStr">
         <is>
-          <t>hutnamimkik</t>
+          <t>[ko̞ŋna̠muɭɡuk̚]</t>
         </is>
       </c>
       <c r="D1409" s="1" t="inlineStr">
@@ -45715,12 +45715,12 @@
       </c>
       <c r="B1416" s="1" t="inlineStr">
         <is>
-          <t>[chomikat] 鱼糕汤；鱼饼汤 (명사)</t>
+          <t>[[ʌ̹muk̚tʰa̠ŋ]] 鱼糕汤；鱼饼汤 (명사)</t>
         </is>
       </c>
       <c r="C1416" s="1" t="inlineStr">
         <is>
-          <t>chomikat</t>
+          <t>[ʌ̹muk̚tʰa̠ŋ]</t>
         </is>
       </c>
       <c r="D1416" s="1" t="inlineStr">
@@ -45779,12 +45779,12 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>[mechin] 辣的；辛辣的 (형용사)</t>
+          <t>[[mɛ̝un]] 辣的；辛辣的 (형용사)</t>
         </is>
       </c>
       <c r="C1418" s="1" t="inlineStr">
         <is>
-          <t>mechin</t>
+          <t>[mɛ̝un]</t>
         </is>
       </c>
       <c r="D1418" s="1" t="inlineStr">
@@ -45875,12 +45875,12 @@
       </c>
       <c r="B1421" s="1" t="inlineStr">
         <is>
-          <t>[ngetmekki] 扎啤 (韩国饮食文化)</t>
+          <t>[[sɛ̝ŋmɛ̝k̚t͡ɕ͈u]] 扎啤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1421" s="1" t="inlineStr">
         <is>
-          <t>ngetmekki</t>
+          <t>[sɛ̝ŋmɛ̝k̚t͡ɕ͈u]</t>
         </is>
       </c>
       <c r="D1421" s="1" t="inlineStr">
@@ -45907,12 +45907,12 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>[[tuju]] 豆乳 (韩国饮食文化)</t>
+          <t>[[tuːju]] 豆乳 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1422" s="1" t="inlineStr">
         <is>
-          <t>[tuju]</t>
+          <t>[tuːju]</t>
         </is>
       </c>
       <c r="D1422" s="1" t="inlineStr">
@@ -46067,12 +46067,12 @@
       </c>
       <c r="B1427" s="1" t="inlineStr">
         <is>
-          <t>[pukankat] 葱酱油 (韩国饮食文化)</t>
+          <t>[[t͡ɕʰo̞ɡa̠nd͡ʑa̠ŋ]] 葱酱油 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1427" s="1" t="inlineStr">
         <is>
-          <t>pukankat</t>
+          <t>[t͡ɕʰo̞ɡa̠nd͡ʑa̠ŋ]</t>
         </is>
       </c>
       <c r="D1427" s="1" t="inlineStr">
@@ -46163,12 +46163,12 @@
       </c>
       <c r="B1430" s="1" t="inlineStr">
         <is>
-          <t>[mikik] 萝卜汤 (韩国饮食文化)</t>
+          <t>[[muɡuk̚]] 萝卜汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1430" s="1" t="inlineStr">
         <is>
-          <t>mikik</t>
+          <t>[muɡuk̚]</t>
         </is>
       </c>
       <c r="D1430" s="1" t="inlineStr">
@@ -46227,12 +46227,12 @@
       </c>
       <c r="B1432" s="1" t="inlineStr">
         <is>
-          <t>[ngukukikik] 牛肉汤 (韩国饮食文化)</t>
+          <t>[[so̞ɡo̞ɡiɡuk̚]] 牛肉汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1432" s="1" t="inlineStr">
         <is>
-          <t>ngukukikik</t>
+          <t>[so̞ɡo̞ɡiɡuk̚]</t>
         </is>
       </c>
       <c r="D1432" s="1" t="inlineStr">
@@ -46259,12 +46259,12 @@
       </c>
       <c r="B1433" s="1" t="inlineStr">
         <is>
-          <t>[chomikpukcheng] 炒鱼糕 (韩国饮食文化)</t>
+          <t>[[ʌ̹muk̚po̞k͈ɯm]] 炒鱼糕 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C1433" s="1" t="inlineStr">
         <is>
-          <t>chomikpukcheng</t>
+          <t>[ʌ̹muk̚po̞k͈ɯm]</t>
         </is>
       </c>
       <c r="D1433" s="1" t="inlineStr">
@@ -46675,12 +46675,12 @@
       </c>
       <c r="B1446" s="1" t="inlineStr">
         <is>
-          <t>[hahachuerenke] Kakao Friends (韩国卡通IP形象) (명사)</t>
+          <t>[[kʰa.ka.o.pʰɯ.ɾen.jɯ]] Kakao Friends (韩国卡通IP形象) (명사)</t>
         </is>
       </c>
       <c r="C1446" s="1" t="inlineStr">
         <is>
-          <t>hahachuerenke</t>
+          <t>[kʰa.ka.o.pʰɯ.ɾen.jɯ]</t>
         </is>
       </c>
       <c r="D1446" s="1" t="inlineStr">
@@ -46707,12 +46707,12 @@
       </c>
       <c r="B1447" s="1" t="inlineStr">
         <is>
-          <t>[oumonnge] 表演 (韩国流行文化)</t>
+          <t>[[pʰʌ.pʰo.mʌn.sɯ]] 表演 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1447" s="1" t="inlineStr">
         <is>
-          <t>oumonnge</t>
+          <t>[pʰʌ.pʰo.mʌn.sɯ]</t>
         </is>
       </c>
       <c r="D1447" s="1" t="inlineStr">
@@ -46899,12 +46899,12 @@
       </c>
       <c r="B1453" s="1" t="inlineStr">
         <is>
-          <t>[herichechio] 内容创建者 (韩国流行文化)</t>
+          <t>[[kʰɯ.ɾi.e.i.tʰʌ]] 内容创建者 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1453" s="1" t="inlineStr">
         <is>
-          <t>herichechio</t>
+          <t>[kʰɯ.ɾi.e.i.tʰʌ]</t>
         </is>
       </c>
       <c r="D1453" s="1" t="inlineStr">
@@ -46963,12 +46963,12 @@
       </c>
       <c r="B1455" s="1" t="inlineStr">
         <is>
-          <t>[pachirom] 病毒性 (韩国流行文化)</t>
+          <t>[[pa.i.ɾʌl]] 病毒性 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C1455" s="1" t="inlineStr">
         <is>
-          <t>pachirom</t>
+          <t>[pa.i.ɾʌl]</t>
         </is>
       </c>
       <c r="D1455" s="1" t="inlineStr">
@@ -47059,7 +47059,7 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠ɾjo]] 宠物食品 (宠物照护与动物)</t>
+          <t>[[sʰa̠ɾjo]] 饲料 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1458" s="1" t="inlineStr">
@@ -47069,7 +47069,7 @@
       </c>
       <c r="D1458" s="1" t="inlineStr">
         <is>
-          <t>宠物食品 (宠物照护与动物)</t>
+          <t>饲料 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="E1458" s="1" t="inlineStr">
@@ -47251,12 +47251,12 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>[etngeakereng] 宠物帐号 (宠物护理与动物)</t>
+          <t>[[pʰɛts͈ɯtʰaɡɯɾam]] 宠物帐号 (宠物护理与动物)</t>
         </is>
       </c>
       <c r="C1464" s="1" t="inlineStr">
         <is>
-          <t>etngeakereng</t>
+          <t>[pʰɛts͈ɯtʰaɡɯɾam]</t>
         </is>
       </c>
       <c r="D1464" s="1" t="inlineStr">
@@ -47347,17 +47347,17 @@
       </c>
       <c r="B1467" s="1" t="inlineStr">
         <is>
-          <t>[anenge] 宠物安全带 (宠物与动物)</t>
+          <t>[[hanes͈ɯ]] 胸背带 (宠物与动物)</t>
         </is>
       </c>
       <c r="C1467" s="1" t="inlineStr">
         <is>
-          <t>anenge</t>
+          <t>[hanes͈ɯ]</t>
         </is>
       </c>
       <c r="D1467" s="1" t="inlineStr">
         <is>
-          <t>宠物安全带 (宠物与动物)</t>
+          <t>胸背带 (宠物与动物)</t>
         </is>
       </c>
       <c r="E1467" s="1" t="inlineStr">
@@ -47379,12 +47379,12 @@
       </c>
       <c r="B1468" s="1" t="inlineStr">
         <is>
-          <t>[hetache] 猫跳台 (宠物照护与动物)</t>
+          <t>[[kʰɛt͈awʌ]] 猫跳台 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1468" s="1" t="inlineStr">
         <is>
-          <t>hetache</t>
+          <t>[kʰɛt͈awʌ]</t>
         </is>
       </c>
       <c r="D1468" s="1" t="inlineStr">
@@ -47443,12 +47443,12 @@
       </c>
       <c r="B1470" s="1" t="inlineStr">
         <is>
-          <t>[ngeherepo] 猫抓板 (宠物照护与动物)</t>
+          <t>[[sɨkʰɯɾɛtɕʰʌ]] 猫抓板 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C1470" s="1" t="inlineStr">
         <is>
-          <t>ngeherepo</t>
+          <t>[sɨkʰɯɾɛtɕʰʌ]</t>
         </is>
       </c>
       <c r="D1470" s="1" t="inlineStr">
@@ -47507,12 +47507,12 @@
       </c>
       <c r="B1472" s="1" t="inlineStr">
         <is>
-          <t>[erukechimo] 职业电竞选手 (游戏与电竞)</t>
+          <t>[[pʰɯɾoɡeimʌ]] 职业电竞选手 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1472" s="1" t="inlineStr">
         <is>
-          <t>erukechimo</t>
+          <t>[pʰɯɾoɡeimʌ]</t>
         </is>
       </c>
       <c r="D1472" s="1" t="inlineStr">
@@ -47539,12 +47539,12 @@
       </c>
       <c r="B1473" s="1" t="inlineStr">
         <is>
-          <t>[heri] Carry(带飞) (游戏与电竞)</t>
+          <t>[[kʰɛɾi]] Carry(带飞) (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1473" s="1" t="inlineStr">
         <is>
-          <t>heri</t>
+          <t>[kʰɛɾi]</t>
         </is>
       </c>
       <c r="D1473" s="1" t="inlineStr">
@@ -47571,12 +47571,12 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>[rek] 游戏延迟；网络卡顿 (명사)</t>
+          <t>[[ɾe̞k̚]] 游戏延迟；网络卡顿 (명사)</t>
         </is>
       </c>
       <c r="C1474" s="1" t="inlineStr">
         <is>
-          <t>rek</t>
+          <t>[ɾe̞k̚]</t>
         </is>
       </c>
       <c r="D1474" s="1" t="inlineStr">
@@ -47635,12 +47635,12 @@
       </c>
       <c r="B1476" s="1" t="inlineStr">
         <is>
-          <t>[ringeun] 复活；重生 (명사)</t>
+          <t>[[ɾis͈pʰon]] 复活；重生 (명사)</t>
         </is>
       </c>
       <c r="C1476" s="1" t="inlineStr">
         <is>
-          <t>ringeun</t>
+          <t>[ɾis͈pʰon]</t>
         </is>
       </c>
       <c r="D1476" s="1" t="inlineStr">
@@ -47667,12 +47667,12 @@
       </c>
       <c r="B1477" s="1" t="inlineStr">
         <is>
-          <t>[peemruchyam] 大逃杀 (游戏与电竞)</t>
+          <t>[[pɛt͈ɯɭɭojal]] 大逃杀 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1477" s="1" t="inlineStr">
         <is>
-          <t>peemruchyam</t>
+          <t>[pɛt͈ɯɭɭojal]</t>
         </is>
       </c>
       <c r="D1477" s="1" t="inlineStr">
@@ -47731,7 +47731,7 @@
       </c>
       <c r="B1479" s="1" t="inlineStr">
         <is>
-          <t>[[pʰiŋ]] 延迟（Ping） (游戏与电竞)</t>
+          <t>[[pʰiŋ]] 网络延迟 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1479" s="1" t="inlineStr">
@@ -47741,7 +47741,7 @@
       </c>
       <c r="D1479" s="1" t="inlineStr">
         <is>
-          <t>延迟（Ping） (游戏与电竞)</t>
+          <t>网络延迟 (游戏与电竞)</t>
         </is>
       </c>
       <c r="E1479" s="1" t="inlineStr">
@@ -47795,12 +47795,12 @@
       </c>
       <c r="B1481" s="1" t="inlineStr">
         <is>
-          <t>[kechingete] 游戏手把 (游戏与电竞)</t>
+          <t>[[ɡeimpʰɛt̚]] 游戏手把 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1481" s="1" t="inlineStr">
         <is>
-          <t>kechingete</t>
+          <t>[ɡeimpʰɛt̚]</t>
         </is>
       </c>
       <c r="D1481" s="1" t="inlineStr">
@@ -47827,12 +47827,12 @@
       </c>
       <c r="B1482" s="1" t="inlineStr">
         <is>
-          <t>[kutryakking] 游戏攻略 (游戏与电竞)</t>
+          <t>[[koŋɲaːk̚t͈ɕip̚]] 游戏攻略 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1482" s="1" t="inlineStr">
         <is>
-          <t>kutryakking</t>
+          <t>[koŋɲaːk̚t͈ɕip̚]</t>
         </is>
       </c>
       <c r="D1482" s="1" t="inlineStr">
@@ -47923,12 +47923,12 @@
       </c>
       <c r="B1485" s="1" t="inlineStr">
         <is>
-          <t>[peemkerachinte] PUBG (绝地求生) (游戏与电竞)</t>
+          <t>[[pɛt͈ɯɡɯɾaunɯ]] PUBG (绝地求生) (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1485" s="1" t="inlineStr">
         <is>
-          <t>peemkerachinte</t>
+          <t>[pɛt͈ɯɡɯɾaunɯ]</t>
         </is>
       </c>
       <c r="D1485" s="1" t="inlineStr">
@@ -47955,12 +47955,12 @@
       </c>
       <c r="B1486" s="1" t="inlineStr">
         <is>
-          <t>[ngehin] 游戏造型 (游戏与电竞)</t>
+          <t>[[sɨɡin]] 游戏造型 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1486" s="1" t="inlineStr">
         <is>
-          <t>ngehin</t>
+          <t>[sɨɡin]</t>
         </is>
       </c>
       <c r="D1486" s="1" t="inlineStr">
@@ -48019,12 +48019,12 @@
       </c>
       <c r="B1488" s="1" t="inlineStr">
         <is>
-          <t>[poe] 增强 (游戏与电竞)</t>
+          <t>[[pʌpʰ]] 增强 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1488" s="1" t="inlineStr">
         <is>
-          <t>poe</t>
+          <t>[pʌpʰ]</t>
         </is>
       </c>
       <c r="D1488" s="1" t="inlineStr">
@@ -48083,12 +48083,12 @@
       </c>
       <c r="B1490" s="1" t="inlineStr">
         <is>
-          <t>[kwnkon] 观看电竞比赛 (游戏与电竞)</t>
+          <t>[[kwan͈tɕʌn]] 观看电竞比赛 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1490" s="1" t="inlineStr">
         <is>
-          <t>kwnkon</t>
+          <t>[kwan͈tɕʌn]</t>
         </is>
       </c>
       <c r="D1490" s="1" t="inlineStr">
@@ -48115,12 +48115,12 @@
       </c>
       <c r="B1491" s="1" t="inlineStr">
         <is>
-          <t>[tonkon] 地下城 (游戏与电竞)</t>
+          <t>[[tʌnt͈ɕʌn]] 地下城 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1491" s="1" t="inlineStr">
         <is>
-          <t>tonkon</t>
+          <t>[tʌnt͈ɕʌn]</t>
         </is>
       </c>
       <c r="D1491" s="1" t="inlineStr">
@@ -48179,12 +48179,12 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>[chinpenuri] 物品栏 (游戏与电竞)</t>
+          <t>[[inbɛntʰoɾi]] 物品栏 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1493" s="1" t="inlineStr">
         <is>
-          <t>chinpenuri</t>
+          <t>[inbɛntʰoɾi]</t>
         </is>
       </c>
       <c r="D1493" s="1" t="inlineStr">
@@ -48243,12 +48243,12 @@
       </c>
       <c r="B1495" s="1" t="inlineStr">
         <is>
-          <t>[kyomngetkon] 决赛 (游戏与电竞)</t>
+          <t>[[kjʌls͈ɯŋt͈ɕʌn]] 决赛 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C1495" s="1" t="inlineStr">
         <is>
-          <t>kyomngetkon</t>
+          <t>[kjʌls͈ɯŋt͈ɕʌn]</t>
         </is>
       </c>
       <c r="D1495" s="1" t="inlineStr">
